--- a/현대_트랜스폰더_칩코드_DB.xlsx
+++ b/현대_트랜스폰더_칩코드_DB.xlsx
@@ -46,11 +46,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="FF9C0006"/>
       <sz val="10"/>
@@ -64,6 +59,11 @@
     <font>
       <name val="Arial"/>
       <color rgb="FF9C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -86,17 +86,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFD599"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD599"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,18 +138,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -657,9 +657,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>ID60[일부 자료]</t>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ID60[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>81996-38010[해외 공용 품번]</t>
+          <t>81996-38010[이모빌라이저키]</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -680,17 +680,13 @@
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
-      <c r="N2" s="4" t="n"/>
+      <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>carisyou 2000 EF 쏘나타, abkeys 81996-38010</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr">
-        <is>
-          <t>국내 EF 이모빌라이저 적용 트림 원문 없음 — 해외 상위 트림 키(81996-38010, 4D60) 기준</t>
-        </is>
-      </c>
+          <t>partsro·hyundaipartsdeal 81996-38010 key-blanking immobilizer, abkeys 81996-38010 4D60</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -723,9 +719,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID60[일부 자료]</t>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>ID60[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -735,7 +731,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>81996-38010[해외 공용 품번]</t>
+          <t>81996-38010[이모빌라이저키]</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -746,17 +742,13 @@
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
-      <c r="N3" s="4" t="n"/>
+      <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>abkeys 81996-38010, hyundai-forums "Transponder Chip In Key?"</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>국내 EF 이모빌라이저 적용 트림 원문 없음 — 해외 상위 트림 키(81996-38010, 4D60) 기준</t>
-        </is>
-      </c>
+          <t>partsro·hyundaipartsdeal 81996-38010 key-blanking immobilizer, abkeys 81996-38010 4D60</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -789,9 +781,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>ID60[일부 자료]</t>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>ID60[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -801,7 +793,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81996-38010[해외 공용 품번]</t>
+          <t>81996-38010[이모빌라이저키]</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -812,17 +804,13 @@
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
-      <c r="N4" s="4" t="n"/>
+      <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>열쇠 카페(sunmikey), autokey.kr</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>국내 EF 이모빌라이저 적용 트림 원문 없음 — 해외 상위 트림 키(81996-38010, 4D60) 기준</t>
-        </is>
-      </c>
+          <t>partsro·hyundaipartsdeal 81996-38010 key-blanking immobilizer, abkeys 81996-38010 4D60</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -855,9 +843,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>ID60[일부 자료]</t>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ID60[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -867,7 +855,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81996-38010[해외 공용 품번]</t>
+          <t>81996-38010[이모빌라이저키]</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,17 +866,13 @@
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
-      <c r="N5" s="4" t="n"/>
+      <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>carisyou 2002 뉴 EF, wikicar 2004년형 가격표</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>국내 EF 이모빌라이저 적용 트림 원문 없음 — 해외 상위 트림 키(81996-38010, 4D60) 기준</t>
-        </is>
-      </c>
+          <t>partsro·hyundaipartsdeal 81996-38010 key-blanking immobilizer, abkeys 81996-38010 4D60</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -921,9 +905,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>ID60[일부 자료]</t>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ID60[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -933,7 +917,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81996-38010[해외 공용 품번]</t>
+          <t>81996-38010[이모빌라이저키]</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -944,17 +928,13 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="4" t="n"/>
+      <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>abkeys 81996-38010, ebay</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>국내 EF 이모빌라이저 적용 트림 원문 없음 — 해외 상위 트림 키(81996-38010, 4D60) 기준</t>
-        </is>
-      </c>
+          <t>partsro·hyundaipartsdeal 81996-38010 key-blanking immobilizer, abkeys 81996-38010 4D60</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1788,12 +1768,12 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -1854,12 +1834,12 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -1920,12 +1900,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -1986,12 +1966,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -2052,12 +2032,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -2118,12 +2098,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -2184,12 +2164,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -2246,12 +2226,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -2308,12 +2288,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -2370,12 +2350,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -2432,12 +2412,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -2494,12 +2474,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -2556,12 +2536,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -2618,12 +2598,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -2695,9 +2675,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>ID60[일부 자료]</t>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>ID60</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2707,7 +2687,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>81996-38010[해외 공용 품번]</t>
+          <t>81996-38010</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2717,18 +2697,18 @@
       </c>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="4" t="n"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>95430-39311, 95430-39050, 95430-39021</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>reidsremotes "Grandeur XG Santa Fe Sonata Trajet transponder", abkeys 81996-38010</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>국내 XG 이모빌라이저 적용 트림 원문 없음 — 해외 XG(2001-2006) 4D60 키 기준</t>
-        </is>
-      </c>
+          <t>hellowcar 그랜저XG 블랭킹키 8199638010, hellowcar 그랜저XG 리모콘, abkeys 81996-38010 4D60</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2761,9 +2741,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>ID60[일부 자료]</t>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>ID60</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2773,7 +2753,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>81996-38010[해외 공용 품번]</t>
+          <t>81996-38010</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2783,18 +2763,18 @@
       </c>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="4" t="n"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>95430-39311, 95430-39050, 95430-39021</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>remokeys "2001-2006 Hyundai HY021 transponder key tex 4D-60"</t>
-        </is>
-      </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>국내 XG 이모빌라이저 적용 트림 원문 없음 — 해외 XG(2001-2006) 4D60 키 기준</t>
-        </is>
-      </c>
+          <t>hellowcar 그랜저XG 블랭킹키 8199638010, hellowcar 그랜저XG 리모콘, abkeys 81996-38010 4D60</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2827,9 +2807,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>ID60[일부 자료]</t>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>ID60</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2839,7 +2819,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>81996-38010[해외 공용 품번]</t>
+          <t>81996-38010</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2849,18 +2829,18 @@
       </c>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="4" t="n"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>95430-39311, 95430-39050, 95430-39021</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>remokeys, hyundai-forums Grandeur XG keys</t>
-        </is>
-      </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>국내 XG 이모빌라이저 적용 트림 원문 없음 — 해외 XG(2001-2006) 4D60 키 기준</t>
-        </is>
-      </c>
+          <t>hellowcar 그랜저XG 블랭킹키 8199638010, hellowcar 그랜저XG 리모콘, abkeys 81996-38010 4D60</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2893,9 +2873,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>ID60[일부 자료]</t>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>ID60</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2905,7 +2885,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>81996-38010[해외 공용 품번]</t>
+          <t>81996-38010</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2915,18 +2895,18 @@
       </c>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="4" t="n"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>95430-39311, 95430-39050, 95430-39021</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>remokeys</t>
-        </is>
-      </c>
-      <c r="P36" s="4" t="inlineStr">
-        <is>
-          <t>국내 XG 이모빌라이저 적용 트림 원문 없음 — 해외 XG(2001-2006) 4D60 키 기준</t>
-        </is>
-      </c>
+          <t>hellowcar 그랜저XG 블랭킹키 8199638010, hellowcar 그랜저XG 리모콘, abkeys 81996-38010 4D60</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2959,9 +2939,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>ID60[일부 자료]</t>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>ID60</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2971,7 +2951,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>81996-38010[해외 공용 품번]</t>
+          <t>81996-38010</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2981,18 +2961,18 @@
       </c>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="4" t="n"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>95430-39311, 95430-39050, 95430-39021</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>remokeys</t>
-        </is>
-      </c>
-      <c r="P37" s="4" t="inlineStr">
-        <is>
-          <t>국내 XG 이모빌라이저 적용 트림 원문 없음 — 해외 XG(2001-2006) 4D60 키 기준</t>
-        </is>
-      </c>
+          <t>hellowcar 그랜저XG 블랭킹키 8199638010, hellowcar 그랜저XG 리모콘, abkeys 81996-38010 4D60</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3025,9 +3005,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>ID60[일부 자료]</t>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>ID60</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3037,7 +3017,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>81996-38010[해외 공용 품번]</t>
+          <t>81996-38010</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -3047,18 +3027,18 @@
       </c>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="4" t="n"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>95430-39311, 95430-39050, 95430-39021</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>remokeys, 나무위키 그랜저/4세대</t>
-        </is>
-      </c>
-      <c r="P38" s="4" t="inlineStr">
-        <is>
-          <t>국내 XG 이모빌라이저 적용 트림 원문 없음 — 해외 XG(2001-2006) 4D60 키 기준</t>
-        </is>
-      </c>
+          <t>hellowcar 그랜저XG 블랭킹키 8199638010, hellowcar 그랜저XG 리모콘, abkeys 81996-38010 4D60</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3091,9 +3071,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[이모빌라이저키], ID46(PCF7952A)[스마트키, 자료 상충], ID6E-MA[스마트키, 자료 상충]</t>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저키], ID6E-MA[스마트키]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3118,17 +3098,13 @@
           <t>95430-3L002, 95430-3L110, 95430-3L500, 95430-3L600</t>
         </is>
       </c>
-      <c r="N39" s="4" t="n"/>
+      <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>나무위키 그랜저/4세대, hellowcar 그랜저TG 블랭킹키·리모콘·스마트키</t>
-        </is>
-      </c>
-      <c r="P39" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 95440-3L100 칩 자료 상충 — auto-keys.eu는 TIRIS DST80, 동급 해외 Azera 스마트키는 PCF7952A ID46</t>
-        </is>
-      </c>
+          <t>auto-keys.eu 95440-3L100 TIRIS DST80, mk3 Equus Grandeur 2005 3L100, hellowcar 그랜저TG 819963L010, amazon Azera 2006-2011 46 chip</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3161,9 +3137,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[이모빌라이저키], ID46(PCF7952A)[스마트키, 자료 상충], ID6E-MA[스마트키, 자료 상충]</t>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저키], ID6E-MA[스마트키]</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3188,17 +3164,13 @@
           <t>95430-3L002, 95430-3L110, 95430-3L500, 95430-3L600</t>
         </is>
       </c>
-      <c r="N40" s="4" t="n"/>
+      <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>partsro 819963L010, hellowcar 그랜저TG 리모컨</t>
-        </is>
-      </c>
-      <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 95440-3L100 칩 자료 상충 — auto-keys.eu는 TIRIS DST80, 동급 해외 Azera 스마트키는 PCF7952A ID46</t>
-        </is>
-      </c>
+          <t>auto-keys.eu 95440-3L100 TIRIS DST80, mk3 Equus Grandeur 2005 3L100, hellowcar 그랜저TG 819963L010, amazon Azera 2006-2011 46 chip</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3231,9 +3203,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[이모빌라이저키], ID46(PCF7952A)[스마트키, 자료 상충], ID6E-MA[스마트키, 자료 상충]</t>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저키], ID6E-MA[스마트키]</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3258,17 +3230,13 @@
           <t>95430-3L002, 95430-3L110, 95430-3L500, 95430-3L600</t>
         </is>
       </c>
-      <c r="N41" s="4" t="n"/>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>carisyou 2007 뉴 그랜저 TG, carwiki 그랜저 TG 2007년형</t>
-        </is>
-      </c>
-      <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 95440-3L100 칩 자료 상충 — auto-keys.eu는 TIRIS DST80, 동급 해외 Azera 스마트키는 PCF7952A ID46</t>
-        </is>
-      </c>
+          <t>auto-keys.eu 95440-3L100 TIRIS DST80, mk3 Equus Grandeur 2005 3L100, hellowcar 그랜저TG 819963L010, amazon Azera 2006-2011 46 chip</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3301,9 +3269,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[이모빌라이저키], ID46(PCF7952A)[스마트키, 자료 상충], ID6E-MA[스마트키, 자료 상충]</t>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저키], ID6E-MA[스마트키]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3328,17 +3296,13 @@
           <t>95430-3L002, 95430-3L110, 95430-3L500, 95430-3L600</t>
         </is>
       </c>
-      <c r="N42" s="4" t="n"/>
+      <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 그랜저TG 스마트키</t>
-        </is>
-      </c>
-      <c r="P42" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 95440-3L100 칩 자료 상충 — auto-keys.eu는 TIRIS DST80, 동급 해외 Azera 스마트키는 PCF7952A ID46</t>
-        </is>
-      </c>
+          <t>auto-keys.eu 95440-3L100 TIRIS DST80, mk3 Equus Grandeur 2005 3L100, hellowcar 그랜저TG 819963L010, amazon Azera 2006-2011 46 chip</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3371,9 +3335,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[이모빌라이저키], ID46(PCF7952A)[스마트키, 자료 상충], ID6E-MA[스마트키, 자료 상충]</t>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저키], ID6E-MA[스마트키]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3398,17 +3362,13 @@
           <t>95430-3L002, 95430-3L110, 95430-3L500, 95430-3L600</t>
         </is>
       </c>
-      <c r="N43" s="4" t="n"/>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>wikicar 2009년형 가격표, hellowcar 그랜저TG 스마트키, mr-key Hyundai 433MHz ID46 PCF7952</t>
-        </is>
-      </c>
-      <c r="P43" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 95440-3L100 칩 자료 상충 — auto-keys.eu는 TIRIS DST80, 동급 해외 Azera 스마트키는 PCF7952A ID46</t>
-        </is>
-      </c>
+          <t>auto-keys.eu 95440-3L100 TIRIS DST80, mk3 Equus Grandeur 2005 3L100, hellowcar 그랜저TG 819963L010, amazon Azera 2006-2011 46 chip</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3441,9 +3401,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[이모빌라이저키], ID46(PCF7952A)[스마트키, 자료 상충], ID6E-MA[스마트키, 자료 상충]</t>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저키], ID6E-MA[스마트키]</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3468,17 +3428,13 @@
           <t>95430-3L002, 95430-3L110, 95430-3L500, 95430-3L600</t>
         </is>
       </c>
-      <c r="N44" s="4" t="n"/>
+      <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 그랜저TG 스마트키</t>
-        </is>
-      </c>
-      <c r="P44" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 95440-3L100 칩 자료 상충 — auto-keys.eu는 TIRIS DST80, 동급 해외 Azera 스마트키는 PCF7952A ID46</t>
-        </is>
-      </c>
+          <t>auto-keys.eu 95440-3L100 TIRIS DST80, mk3 Equus Grandeur 2005 3L100, hellowcar 그랜저TG 819963L010, amazon Azera 2006-2011 46 chip</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3511,9 +3467,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[이모빌라이저키], ID46(PCF7952A)[스마트키, 자료 상충], ID6E-MA[스마트키, 자료 상충]</t>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저키], ID6E-MA[스마트키]</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3538,17 +3494,13 @@
           <t>95430-3L002, 95430-3L110, 95430-3L500, 95430-3L600</t>
         </is>
       </c>
-      <c r="N45" s="4" t="n"/>
+      <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 그랜저TG 리모콘</t>
-        </is>
-      </c>
-      <c r="P45" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 95440-3L100 칩 자료 상충 — auto-keys.eu는 TIRIS DST80, 동급 해외 Azera 스마트키는 PCF7952A ID46</t>
-        </is>
-      </c>
+          <t>auto-keys.eu 95440-3L100 TIRIS DST80, mk3 Equus Grandeur 2005 3L100, hellowcar 그랜저TG 819963L010, amazon Azera 2006-2011 46 chip</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3950,12 +3902,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4016,12 +3968,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4082,12 +4034,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4148,12 +4100,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4214,12 +4166,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4280,12 +4232,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4346,12 +4298,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4412,12 +4364,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4474,12 +4426,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4536,12 +4488,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4598,12 +4550,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4660,12 +4612,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -4722,10 +4674,10 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr"/>
-      <c r="E64" s="7" t="inlineStr"/>
-      <c r="F64" s="7" t="inlineStr"/>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr"/>
+      <c r="E64" s="6" t="inlineStr"/>
+      <c r="F64" s="6" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -4740,13 +4692,13 @@
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="n"/>
-      <c r="N64" s="8" t="n"/>
+      <c r="N64" s="7" t="n"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
           <t>나무위키 아반떼/2세대</t>
         </is>
       </c>
-      <c r="P64" s="8" t="inlineStr">
+      <c r="P64" s="7" t="inlineStr">
         <is>
           <t>J2 이모빌라이저 적용 원문 없음</t>
         </is>
@@ -4768,9 +4720,9 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr"/>
-      <c r="E65" s="7" t="inlineStr"/>
-      <c r="F65" s="7" t="inlineStr"/>
+      <c r="D65" s="6" t="inlineStr"/>
+      <c r="E65" s="6" t="inlineStr"/>
+      <c r="F65" s="6" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -4810,9 +4762,9 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr"/>
-      <c r="E66" s="7" t="inlineStr"/>
-      <c r="F66" s="7" t="inlineStr"/>
+      <c r="D66" s="6" t="inlineStr"/>
+      <c r="E66" s="6" t="inlineStr"/>
+      <c r="F66" s="6" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -4852,9 +4804,9 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr"/>
-      <c r="E67" s="7" t="inlineStr"/>
-      <c r="F67" s="7" t="inlineStr"/>
+      <c r="D67" s="6" t="inlineStr"/>
+      <c r="E67" s="6" t="inlineStr"/>
+      <c r="F67" s="6" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -4894,9 +4846,9 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr"/>
-      <c r="E68" s="7" t="inlineStr"/>
-      <c r="F68" s="7" t="inlineStr"/>
+      <c r="D68" s="6" t="inlineStr"/>
+      <c r="E68" s="6" t="inlineStr"/>
+      <c r="F68" s="6" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -5824,12 +5776,12 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -5890,12 +5842,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -5956,12 +5908,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E85" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6022,12 +5974,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6088,12 +6040,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6154,12 +6106,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6220,12 +6172,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6282,12 +6234,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6344,12 +6296,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E91" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6406,12 +6358,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6421,9 +6373,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>ID6A[~2023.2], ID6A[더 뉴 아반떼, 자료 상충], ID4A[더 뉴 아반떼, 자료 상충]</t>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -6444,17 +6396,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n"/>
-      <c r="N92" s="4" t="n"/>
+      <c r="N92" s="2" t="n"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 아반떼CN7 페이스리프트, remotesandkeys 2023 Elantra AA500, keyshop-online "ID6A AA500"</t>
-        </is>
-      </c>
-      <c r="P92" s="4" t="inlineStr">
-        <is>
-          <t>더 뉴 아반떼 스마트키(95440-AA500) 칩 표기 상충 — ID6A(keyshop-online) vs HITAG-AES 4A(일부 판매처)</t>
-        </is>
-      </c>
+          <t>auto-keys.eu 95440-AA501 ATMEL AES 6A, keyshop-online AA500 ID6A, remotesandkeys AA500·IB500 표기 불일치</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -6472,12 +6420,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6487,9 +6435,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>ID6A[자료 상충], ID4A[자료 상충]</t>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6510,17 +6458,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n"/>
-      <c r="N93" s="4" t="n"/>
+      <c r="N93" s="2" t="n"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>abkeys 95440-AA500, adlhardware 2024 Elantra</t>
-        </is>
-      </c>
-      <c r="P93" s="4" t="inlineStr">
-        <is>
-          <t>스마트키(95440-AA500) 칩 표기 상충 — ID6A vs HITAG-AES 4A</t>
-        </is>
-      </c>
+          <t>auto-keys.eu 95440-AA501 ATMEL AES 6A, keyshop-online AA500 ID6A, remotesandkeys AA500·IB500 표기 불일치</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6538,12 +6482,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6553,9 +6497,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>ID6A[자료 상충], ID4A[자료 상충]</t>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -6576,17 +6520,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n"/>
-      <c r="N94" s="4" t="n"/>
+      <c r="N94" s="2" t="n"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>transponderisland 95440-AA501, yourcarkeyguys 2024-2026</t>
-        </is>
-      </c>
-      <c r="P94" s="4" t="inlineStr">
-        <is>
-          <t>스마트키(95440-AA500) 칩 표기 상충 — ID6A vs HITAG-AES 4A</t>
-        </is>
-      </c>
+          <t>auto-keys.eu 95440-AA501 ATMEL AES 6A, keyshop-online AA500 ID6A, remotesandkeys AA500·IB500 표기 불일치</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6604,12 +6544,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E95" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6619,9 +6559,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>ID6A[자료 상충], ID4A[자료 상충]</t>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -6642,17 +6582,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n"/>
-      <c r="N95" s="4" t="n"/>
+      <c r="N95" s="2" t="n"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>나무위키 아반떼/7세대, hellowcar 아반떼CN7 페이스리프트</t>
-        </is>
-      </c>
-      <c r="P95" s="4" t="inlineStr">
-        <is>
-          <t>스마트키(95440-AA500) 칩 표기 상충 — ID6A vs HITAG-AES 4A</t>
-        </is>
-      </c>
+          <t>auto-keys.eu 95440-AA501 ATMEL AES 6A, keyshop-online AA500 ID6A, remotesandkeys AA500·IB500 표기 불일치</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6670,12 +6606,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6728,12 +6664,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6786,12 +6722,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6844,12 +6780,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D99" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6859,9 +6795,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G99" s="4" t="inlineStr">
-        <is>
-          <t>ID6A[자료 상충], ID4A[자료 상충]</t>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6882,17 +6818,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n"/>
-      <c r="N99" s="4" t="n"/>
+      <c r="N99" s="2" t="n"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware 2024 Elantra N IB500YPN, hellowcar 아반떼CN7 N 페이스리프트</t>
-        </is>
-      </c>
-      <c r="P99" s="4" t="inlineStr">
-        <is>
-          <t>페이스리프트 스마트키(NYOMBEC7FOB2208, 아반떼 AA500과 같은 키) 칩 표기 상충 — 6A vs HITAG-AES 4A</t>
-        </is>
-      </c>
+          <t>uhs-hardware IB500YPN 6A, remotesandkeys 2024-2025 Elantra N IB500 6A</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6910,12 +6842,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D100" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6925,9 +6857,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G100" s="4" t="inlineStr">
-        <is>
-          <t>ID6A[자료 상충], ID4A[자료 상충]</t>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6948,17 +6880,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n"/>
-      <c r="N100" s="4" t="n"/>
+      <c r="N100" s="2" t="n"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2025 Elantra N</t>
-        </is>
-      </c>
-      <c r="P100" s="4" t="inlineStr">
-        <is>
-          <t>페이스리프트 스마트키(NYOMBEC7FOB2208, 아반떼 AA500과 같은 키) 칩 표기 상충 — 6A vs HITAG-AES 4A</t>
-        </is>
-      </c>
+          <t>uhs-hardware IB500YPN 6A, remotesandkeys 2024-2025 Elantra N IB500 6A</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6976,12 +6904,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -6991,9 +6919,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>ID6A[자료 상충], ID4A[자료 상충]</t>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7014,17 +6942,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n"/>
-      <c r="N101" s="4" t="n"/>
+      <c r="N101" s="2" t="n"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>transponderisland 2024-2026, yourcarkeyguys 2024-2026</t>
-        </is>
-      </c>
-      <c r="P101" s="4" t="inlineStr">
-        <is>
-          <t>페이스리프트 스마트키(NYOMBEC7FOB2208, 아반떼 AA500과 같은 키) 칩 표기 상충 — 6A vs HITAG-AES 4A</t>
-        </is>
-      </c>
+          <t>uhs-hardware IB500YPN 6A, remotesandkeys 2024-2025 Elantra N IB500 6A</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7042,12 +6966,12 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr"/>
-      <c r="E102" s="7" t="inlineStr"/>
-      <c r="F102" s="7" t="inlineStr"/>
+      <c r="D102" s="6" t="inlineStr"/>
+      <c r="E102" s="6" t="inlineStr"/>
+      <c r="F102" s="6" t="inlineStr"/>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>해당 없음[추정]</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7067,12 +6991,12 @@
       <c r="N102" s="8" t="n"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>다나와 베르나(LC), partsro 819961C400</t>
+          <t>partsro 819961C400 베르나 LC 클릭 TB</t>
         </is>
       </c>
       <c r="P102" s="8" t="inlineStr">
         <is>
-          <t>국내 LC 이모빌라이저 적용 원문 없음(해외 엑센트 LC는 ID46 키 81996-25010)</t>
+          <t>현대모비스 목록에 칩 없는 보조키(81996-1C400)만 있고 이모빌라이저키가 없어 미적용으로 추정</t>
         </is>
       </c>
     </row>
@@ -7092,12 +7016,12 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr"/>
-      <c r="E103" s="7" t="inlineStr"/>
-      <c r="F103" s="7" t="inlineStr"/>
+      <c r="D103" s="6" t="inlineStr"/>
+      <c r="E103" s="6" t="inlineStr"/>
+      <c r="F103" s="6" t="inlineStr"/>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>해당 없음[추정]</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -7117,12 +7041,12 @@
       <c r="N103" s="8" t="n"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>abkeys 81996-25010</t>
+          <t>partsro 819961C400 베르나 LC 클릭 TB</t>
         </is>
       </c>
       <c r="P103" s="8" t="inlineStr">
         <is>
-          <t>국내 LC 이모빌라이저 적용 원문 없음(해외 엑센트 LC는 ID46 키 81996-25010)</t>
+          <t>현대모비스 목록에 칩 없는 보조키(81996-1C400)만 있고 이모빌라이저키가 없어 미적용으로 추정</t>
         </is>
       </c>
     </row>
@@ -7142,12 +7066,12 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr"/>
-      <c r="E104" s="7" t="inlineStr"/>
-      <c r="F104" s="7" t="inlineStr"/>
+      <c r="D104" s="6" t="inlineStr"/>
+      <c r="E104" s="6" t="inlineStr"/>
+      <c r="F104" s="6" t="inlineStr"/>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>해당 없음[추정]</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -7167,12 +7091,12 @@
       <c r="N104" s="8" t="n"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>다나와 뉴 베르나(LC)</t>
+          <t>partsro 819961C400 베르나 LC 클릭 TB</t>
         </is>
       </c>
       <c r="P104" s="8" t="inlineStr">
         <is>
-          <t>국내 LC 이모빌라이저 적용 원문 없음(해외 엑센트 LC는 ID46 키 81996-25010)</t>
+          <t>현대모비스 목록에 칩 없는 보조키(81996-1C400)만 있고 이모빌라이저키가 없어 미적용으로 추정</t>
         </is>
       </c>
     </row>
@@ -7192,12 +7116,12 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr"/>
-      <c r="E105" s="7" t="inlineStr"/>
-      <c r="F105" s="7" t="inlineStr"/>
+      <c r="D105" s="6" t="inlineStr"/>
+      <c r="E105" s="6" t="inlineStr"/>
+      <c r="F105" s="6" t="inlineStr"/>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>해당 없음[추정]</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -7217,12 +7141,12 @@
       <c r="N105" s="8" t="n"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>다나와 뉴 베르나(LC)</t>
+          <t>partsro 819961C400 베르나 LC 클릭 TB</t>
         </is>
       </c>
       <c r="P105" s="8" t="inlineStr">
         <is>
-          <t>국내 LC 이모빌라이저 적용 원문 없음(해외 엑센트 LC는 ID46 키 81996-25010)</t>
+          <t>현대모비스 목록에 칩 없는 보조키(81996-1C400)만 있고 이모빌라이저키가 없어 미적용으로 추정</t>
         </is>
       </c>
     </row>
@@ -7242,12 +7166,12 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="D106" s="7" t="inlineStr"/>
-      <c r="E106" s="7" t="inlineStr"/>
-      <c r="F106" s="7" t="inlineStr"/>
+      <c r="D106" s="6" t="inlineStr"/>
+      <c r="E106" s="6" t="inlineStr"/>
+      <c r="F106" s="6" t="inlineStr"/>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>해당 없음[추정]</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -7267,12 +7191,12 @@
       <c r="N106" s="8" t="n"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>다나와 뉴 베르나(LC)</t>
+          <t>partsro 819961C400 베르나 LC 클릭 TB</t>
         </is>
       </c>
       <c r="P106" s="8" t="inlineStr">
         <is>
-          <t>국내 LC 이모빌라이저 적용 원문 없음(해외 엑센트 LC는 ID46 키 81996-25010)</t>
+          <t>현대모비스 목록에 칩 없는 보조키(81996-1C400)만 있고 이모빌라이저키가 없어 미적용으로 추정</t>
         </is>
       </c>
     </row>
@@ -7292,12 +7216,12 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr"/>
-      <c r="E107" s="7" t="inlineStr"/>
-      <c r="F107" s="7" t="inlineStr"/>
+      <c r="D107" s="6" t="inlineStr"/>
+      <c r="E107" s="6" t="inlineStr"/>
+      <c r="F107" s="6" t="inlineStr"/>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>확인 불가</t>
+          <t>해당 없음[추정]</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -7317,12 +7241,12 @@
       <c r="N107" s="8" t="n"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>다나와 뉴 베르나(LC)</t>
+          <t>partsro 819961C400 베르나 LC 클릭 TB</t>
         </is>
       </c>
       <c r="P107" s="8" t="inlineStr">
         <is>
-          <t>국내 LC 이모빌라이저 적용 원문 없음(해외 엑센트 LC는 ID46 키 81996-25010)</t>
+          <t>현대모비스 목록에 칩 없는 보조키(81996-1C400)만 있고 이모빌라이저키가 없어 미적용으로 추정</t>
         </is>
       </c>
     </row>
@@ -7342,12 +7266,24 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr"/>
-      <c r="E108" s="7" t="inlineStr"/>
-      <c r="F108" s="7" t="inlineStr"/>
-      <c r="G108" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -7355,22 +7291,22 @@
           <t>막대키,폴딩키</t>
         </is>
       </c>
-      <c r="I108" s="2" t="n"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>81996-1E010[이모빌라이저키], 81996-1E000[칩 없음]</t>
+        </is>
+      </c>
       <c r="J108" s="2" t="n"/>
       <c r="K108" s="2" t="n"/>
       <c r="L108" s="2" t="n"/>
       <c r="M108" s="2" t="n"/>
-      <c r="N108" s="8" t="n"/>
+      <c r="N108" s="2" t="n"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>hyundai.com heritage 2005 Verna MC, 나무위키 현대 베르나</t>
-        </is>
-      </c>
-      <c r="P108" s="8" t="inlineStr">
-        <is>
-          <t>국내 MC 이모빌라이저 적용·키 품번 원문 없음</t>
-        </is>
-      </c>
+          <t>hellowcar 베르나 819961E010/819961E000, amazon 81996-1E010 master immobilizer, superb-keys 1E010 ID46</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7388,12 +7324,24 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="D109" s="7" t="inlineStr"/>
-      <c r="E109" s="7" t="inlineStr"/>
-      <c r="F109" s="7" t="inlineStr"/>
-      <c r="G109" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -7401,22 +7349,22 @@
           <t>막대키,폴딩키</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>81996-1E010[이모빌라이저키], 81996-1E000[칩 없음]</t>
+        </is>
+      </c>
       <c r="J109" s="2" t="n"/>
       <c r="K109" s="2" t="n"/>
       <c r="L109" s="2" t="n"/>
       <c r="M109" s="2" t="n"/>
-      <c r="N109" s="8" t="n"/>
+      <c r="N109" s="2" t="n"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 엑센트 폴딩키, partsro</t>
-        </is>
-      </c>
-      <c r="P109" s="8" t="inlineStr">
-        <is>
-          <t>국내 MC 이모빌라이저 적용·키 품번 원문 없음</t>
-        </is>
-      </c>
+          <t>hellowcar 베르나 819961E010/819961E000, amazon 81996-1E010 master immobilizer, superb-keys 1E010 ID46</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7434,12 +7382,24 @@
           <t>2007</t>
         </is>
       </c>
-      <c r="D110" s="7" t="inlineStr"/>
-      <c r="E110" s="7" t="inlineStr"/>
-      <c r="F110" s="7" t="inlineStr"/>
-      <c r="G110" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -7447,22 +7407,22 @@
           <t>막대키,폴딩키</t>
         </is>
       </c>
-      <c r="I110" s="2" t="n"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>81996-1E010[이모빌라이저키], 81996-1E000[칩 없음]</t>
+        </is>
+      </c>
       <c r="J110" s="2" t="n"/>
       <c r="K110" s="2" t="n"/>
       <c r="L110" s="2" t="n"/>
       <c r="M110" s="2" t="n"/>
-      <c r="N110" s="8" t="n"/>
+      <c r="N110" s="2" t="n"/>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>carisyou 2009 베르나(MC), 다나와 베르나(MC)</t>
-        </is>
-      </c>
-      <c r="P110" s="8" t="inlineStr">
-        <is>
-          <t>국내 MC 이모빌라이저 적용·키 품번 원문 없음</t>
-        </is>
-      </c>
+          <t>hellowcar 베르나 819961E010/819961E000, amazon 81996-1E010 master immobilizer, superb-keys 1E010 ID46</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7480,12 +7440,24 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="D111" s="7" t="inlineStr"/>
-      <c r="E111" s="7" t="inlineStr"/>
-      <c r="F111" s="7" t="inlineStr"/>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -7493,22 +7465,22 @@
           <t>막대키,폴딩키</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>81996-1E010[이모빌라이저키], 81996-1E000[칩 없음]</t>
+        </is>
+      </c>
       <c r="J111" s="2" t="n"/>
       <c r="K111" s="2" t="n"/>
       <c r="L111" s="2" t="n"/>
       <c r="M111" s="2" t="n"/>
-      <c r="N111" s="8" t="n"/>
+      <c r="N111" s="2" t="n"/>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>다나와 베르나(MC), 나무위키 베르나</t>
-        </is>
-      </c>
-      <c r="P111" s="8" t="inlineStr">
-        <is>
-          <t>국내 MC 이모빌라이저 적용·키 품번 원문 없음</t>
-        </is>
-      </c>
+          <t>hellowcar 베르나 819961E010/819961E000, amazon 81996-1E010 master immobilizer, superb-keys 1E010 ID46</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7526,12 +7498,24 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="D112" s="7" t="inlineStr"/>
-      <c r="E112" s="7" t="inlineStr"/>
-      <c r="F112" s="7" t="inlineStr"/>
-      <c r="G112" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가[~2009.5], 해당 없음[베르나 트랜스폼, 2009.6~]</t>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>ID46[~2009.5, 이모빌라이저 사양], 해당 없음[베르나 트랜스폼, 2009.6~]</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -7539,22 +7523,22 @@
           <t>막대키,폴딩키</t>
         </is>
       </c>
-      <c r="I112" s="2" t="n"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>81996-1E010[이모빌라이저키], 81996-1E000[칩 없음]</t>
+        </is>
+      </c>
       <c r="J112" s="2" t="n"/>
       <c r="K112" s="2" t="n"/>
       <c r="L112" s="2" t="n"/>
       <c r="M112" s="2" t="n"/>
-      <c r="N112" s="8" t="n"/>
+      <c r="N112" s="2" t="n"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>나무위키 베르나/3세대(검색 요약), carisyou 2009 베르나 트랜스폼</t>
-        </is>
-      </c>
-      <c r="P112" s="8" t="inlineStr">
-        <is>
-          <t>2009.6 트랜스폼 이전 MC 이모빌라이저 적용 원문 없음</t>
-        </is>
-      </c>
+          <t>hellowcar 베르나 819961E010, 나무위키 베르나</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7572,9 +7556,9 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr"/>
-      <c r="E113" s="7" t="inlineStr"/>
-      <c r="F113" s="7" t="inlineStr"/>
+      <c r="D113" s="6" t="inlineStr"/>
+      <c r="E113" s="6" t="inlineStr"/>
+      <c r="F113" s="6" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -7585,7 +7569,11 @@
           <t>막대키,폴딩키</t>
         </is>
       </c>
-      <c r="I113" s="2" t="n"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>81996-1E000[칩 없음]</t>
+        </is>
+      </c>
       <c r="J113" s="2" t="n"/>
       <c r="K113" s="2" t="n"/>
       <c r="L113" s="2" t="n"/>
@@ -7593,7 +7581,7 @@
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>나무위키 베르나, 다나와 베르나 트랜스폼(MC)</t>
+          <t>hellowcar 베르나 819961E010, 나무위키 베르나</t>
         </is>
       </c>
       <c r="P113" s="2" t="n"/>
@@ -8988,12 +8976,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="D135" s="5" t="inlineStr">
+      <c r="D135" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -9046,12 +9034,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="D136" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -9104,12 +9092,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D137" s="5" t="inlineStr">
+      <c r="D137" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E137" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -9162,12 +9150,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="D138" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="E138" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -9220,12 +9208,12 @@
           <t>2020(단종)</t>
         </is>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D139" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="E139" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -9278,14 +9266,14 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -9293,9 +9281,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G140" s="4" t="inlineStr">
-        <is>
-          <t>ID6E-MA[자료 상충], ID8A[자료 상충]</t>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>ID6E-MA(TMS37126)[95440-3Z000 키]</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -9312,21 +9300,17 @@
       <c r="K140" s="2" t="n"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>95440-3Z000[~2012.4.2], 95440-3Z100</t>
+          <t>95440-3Z000[2011.12.15~2012.4.2], 95440-3Z100</t>
         </is>
       </c>
       <c r="M140" s="2" t="n"/>
-      <c r="N140" s="4" t="n"/>
+      <c r="N140" s="2" t="n"/>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>carkeyno1 95440-3Z000, abkeys 3Z000 TMS37126·3Z100, mk3 3Z001 8A</t>
-        </is>
-      </c>
-      <c r="P140" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 상충 — 95440-3Z000은 TMS37126(TI DST80) 표기, 3Z001은 8A 표기</t>
-        </is>
-      </c>
+          <t>abkeys 3Z000 TMS37126, auto-keys.eu 3Z000 TIRIS 4D+, 검색요약 3Z001 DST-AES, carkeyno1 3Z000 11.12.15~12.04.02·3Z002 13.02.01~</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -9344,12 +9328,12 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E141" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -9359,9 +9343,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G141" s="4" t="inlineStr">
-        <is>
-          <t>ID6E-MA[자료 상충], ID8A[자료 상충]</t>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>ID6E-MA(TMS37126)[95440-3Z000 키, ~2012.4.2], ID8A[95440-3Z001 키]</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -9382,17 +9366,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n"/>
-      <c r="N141" s="4" t="n"/>
+      <c r="N141" s="2" t="n"/>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>abkeys 95440-3Z001, mk3 i40 2014 3Z001</t>
-        </is>
-      </c>
-      <c r="P141" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 상충 — 95440-3Z000은 TMS37126(TI DST80) 표기, 3Z001은 8A 표기</t>
-        </is>
-      </c>
+          <t>abkeys 3Z000 TMS37126, auto-keys.eu 3Z000 TIRIS 4D+, 검색요약 3Z001 DST-AES, carkeyno1 3Z000 11.12.15~12.04.02·3Z002 13.02.01~</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -9410,24 +9390,24 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="G142" s="4" t="inlineStr">
-        <is>
-          <t>ID6E-MA[자료 상충], ID8A[자료 상충]</t>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -9444,21 +9424,17 @@
       <c r="K142" s="2" t="n"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>95440-3Z001, 95440-3Z002[2013.2~]</t>
+          <t>95440-3Z001, 95440-3Z002[2013.2.1~]</t>
         </is>
       </c>
       <c r="M142" s="2" t="n"/>
-      <c r="N142" s="4" t="n"/>
+      <c r="N142" s="2" t="n"/>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>carkeyno1 95440-3Z002</t>
-        </is>
-      </c>
-      <c r="P142" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 상충 — TIRIS 4D(DST80) 표기 vs 8A 표기</t>
-        </is>
-      </c>
+          <t>abkeys 3Z000 TMS37126, auto-keys.eu 3Z000 TIRIS 4D+, 검색요약 3Z001 DST-AES, carkeyno1 3Z000 11.12.15~12.04.02·3Z002 13.02.01~</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -9476,24 +9452,24 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="G143" s="4" t="inlineStr">
-        <is>
-          <t>ID6E-MA[자료 상충], ID8A[자료 상충]</t>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -9510,21 +9486,17 @@
       <c r="K143" s="2" t="n"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>95440-3Z001, 95440-3Z002[2013.2~]</t>
+          <t>95440-3Z001, 95440-3Z002[2013.2.1~]</t>
         </is>
       </c>
       <c r="M143" s="2" t="n"/>
-      <c r="N143" s="4" t="n"/>
+      <c r="N143" s="2" t="n"/>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu, mk3</t>
-        </is>
-      </c>
-      <c r="P143" s="4" t="inlineStr">
-        <is>
-          <t>스마트키 칩 자료 상충 — TIRIS 4D(DST80) 표기 vs 8A 표기</t>
-        </is>
-      </c>
+          <t>abkeys 3Z000 TMS37126, auto-keys.eu 3Z000 TIRIS 4D+, 검색요약 3Z001 DST-AES, carkeyno1 3Z000 11.12.15~12.04.02·3Z002 13.02.01~</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -9542,12 +9514,12 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="D144" s="5" t="inlineStr">
+      <c r="D144" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E144" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -9604,12 +9576,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D145" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E145" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -9666,12 +9638,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D146" s="5" t="inlineStr">
+      <c r="D146" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -9728,12 +9700,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D147" s="5" t="inlineStr">
+      <c r="D147" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -9790,12 +9762,12 @@
           <t>2019(단종)</t>
         </is>
       </c>
-      <c r="D148" s="5" t="inlineStr">
+      <c r="D148" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E148" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -10286,12 +10258,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D156" s="5" t="inlineStr">
+      <c r="D156" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E156" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -10344,12 +10316,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D157" s="5" t="inlineStr">
+      <c r="D157" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E157" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -10406,12 +10378,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D158" s="5" t="inlineStr">
+      <c r="D158" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E158" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -10468,12 +10440,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="D159" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E159" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -10530,12 +10502,12 @@
           <t>2022(단종)</t>
         </is>
       </c>
-      <c r="D160" s="5" t="inlineStr">
+      <c r="D160" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="E160" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -11212,12 +11184,12 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="D171" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="E171" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -11278,12 +11250,12 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="D172" s="5" t="inlineStr">
+      <c r="D172" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="E172" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -11344,12 +11316,12 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="D173" s="5" t="inlineStr">
+      <c r="D173" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="E173" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -11410,12 +11382,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="D174" s="5" t="inlineStr">
+      <c r="D174" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E174" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12058,12 +12030,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="D184" s="5" t="inlineStr">
+      <c r="D184" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="E184" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12120,12 +12092,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D185" s="5" t="inlineStr">
+      <c r="D185" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12182,12 +12154,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="D186" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E186" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12244,12 +12216,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="D187" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12306,12 +12278,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="D188" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12368,12 +12340,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="D189" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12430,12 +12402,12 @@
           <t>2022(단종)</t>
         </is>
       </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="D190" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12492,12 +12464,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D191" s="5" t="inlineStr">
+      <c r="D191" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E191" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12554,12 +12526,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D192" s="5" t="inlineStr">
+      <c r="D192" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E192" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12616,12 +12588,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D193" s="5" t="inlineStr">
+      <c r="D193" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E193" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12678,12 +12650,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D194" s="5" t="inlineStr">
+      <c r="D194" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="E194" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12736,12 +12708,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D195" s="5" t="inlineStr">
+      <c r="D195" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="E195" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12794,12 +12766,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D196" s="5" t="inlineStr">
+      <c r="D196" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="E196" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12852,12 +12824,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D197" s="5" t="inlineStr">
+      <c r="D197" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="E197" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12910,12 +12882,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D198" s="5" t="inlineStr">
+      <c r="D198" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E198" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -12968,12 +12940,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D199" s="5" t="inlineStr">
+      <c r="D199" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="E199" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -13026,12 +12998,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D200" s="5" t="inlineStr">
+      <c r="D200" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="E200" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -13084,12 +13056,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D201" s="5" t="inlineStr">
+      <c r="D201" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="E201" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -13099,9 +13071,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G201" s="4" t="inlineStr">
-        <is>
-          <t>ID6A[자료 상충], ID4A[자료 상충]</t>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -13109,7 +13081,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I201" s="2" t="n"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>81996-KL010</t>
+        </is>
+      </c>
       <c r="J201" s="2" t="n"/>
       <c r="K201" s="2" t="n"/>
       <c r="L201" s="2" t="inlineStr">
@@ -13118,17 +13094,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n"/>
-      <c r="N201" s="4" t="n"/>
+      <c r="N201" s="2" t="n"/>
       <c r="O201" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu KL000 ATMEL AES 6A, abkeys KL300 ID6A, gskeyae KL000</t>
-        </is>
-      </c>
-      <c r="P201" s="4" t="inlineStr">
-        <is>
-          <t>스마트키(95440-KL000) 칩 표기 상충 — ATMEL AES 6A(auto-keys·abkeys) vs ID4A(일부 판매처)</t>
-        </is>
-      </c>
+          <t>auto-keys.eu KL000·KL200 ATMEL AES 6A, abkeys KL300 ID6A, partsro 81996KL010 아이오닉6</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -13146,12 +13118,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D202" s="5" t="inlineStr">
+      <c r="D202" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="E202" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -13161,9 +13133,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G202" s="4" t="inlineStr">
-        <is>
-          <t>ID6A[자료 상충], ID4A[자료 상충]</t>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -13171,7 +13143,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I202" s="2" t="n"/>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>81996-KL010</t>
+        </is>
+      </c>
       <c r="J202" s="2" t="n"/>
       <c r="K202" s="2" t="n"/>
       <c r="L202" s="2" t="inlineStr">
@@ -13180,17 +13156,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n"/>
-      <c r="N202" s="4" t="n"/>
+      <c r="N202" s="2" t="n"/>
       <c r="O202" s="2" t="inlineStr">
         <is>
-          <t>abkeys 2023-2025 KL300, transponderisland KL000</t>
-        </is>
-      </c>
-      <c r="P202" s="4" t="inlineStr">
-        <is>
-          <t>스마트키(95440-KL000) 칩 표기 상충 — ATMEL AES 6A(auto-keys·abkeys) vs ID4A(일부 판매처)</t>
-        </is>
-      </c>
+          <t>auto-keys.eu KL000·KL200 ATMEL AES 6A, abkeys KL300 ID6A, partsro 81996KL010 아이오닉6</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -13208,12 +13180,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D203" s="5" t="inlineStr">
+      <c r="D203" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E203" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -13223,9 +13195,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G203" s="4" t="inlineStr">
-        <is>
-          <t>ID6A[자료 상충], ID4A[자료 상충]</t>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -13233,7 +13205,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I203" s="2" t="n"/>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>81996-KL010</t>
+        </is>
+      </c>
       <c r="J203" s="2" t="n"/>
       <c r="K203" s="2" t="n"/>
       <c r="L203" s="2" t="inlineStr">
@@ -13242,17 +13218,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n"/>
-      <c r="N203" s="4" t="n"/>
+      <c r="N203" s="2" t="n"/>
       <c r="O203" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2024 Ioniq 6 KL000</t>
-        </is>
-      </c>
-      <c r="P203" s="4" t="inlineStr">
-        <is>
-          <t>스마트키(95440-KL000) 칩 표기 상충 — ATMEL AES 6A(auto-keys·abkeys) vs ID4A(일부 판매처)</t>
-        </is>
-      </c>
+          <t>auto-keys.eu KL000·KL200 ATMEL AES 6A, abkeys KL300 ID6A, partsro 81996KL010 아이오닉6</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -13270,12 +13242,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D204" s="5" t="inlineStr">
+      <c r="D204" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="E204" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -13285,7 +13257,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G204" s="4" t="inlineStr">
+      <c r="G204" s="8" t="inlineStr">
         <is>
           <t>ID6A[추정]</t>
         </is>
@@ -13304,13 +13276,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n"/>
-      <c r="N204" s="4" t="n"/>
+      <c r="N204" s="8" t="n"/>
       <c r="O204" s="2" t="inlineStr">
         <is>
-          <t>mk3 Ioniq 6 2025 KL500</t>
-        </is>
-      </c>
-      <c r="P204" s="4" t="inlineStr">
+          <t>hellowcar 아이오닉6 스마트키, mk3 Ioniq 6 2025 KL500</t>
+        </is>
+      </c>
+      <c r="P204" s="8" t="inlineStr">
         <is>
           <t>더 뉴 아이오닉6 스마트키(95440-KL500) 칩 원문 없음 — KL000 계열 기준 추정</t>
         </is>
@@ -13332,12 +13304,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D205" s="5" t="inlineStr">
+      <c r="D205" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="E205" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -13347,7 +13319,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G205" s="4" t="inlineStr">
+      <c r="G205" s="8" t="inlineStr">
         <is>
           <t>ID6A[추정]</t>
         </is>
@@ -13366,13 +13338,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n"/>
-      <c r="N205" s="4" t="n"/>
+      <c r="N205" s="8" t="n"/>
       <c r="O205" s="2" t="inlineStr">
         <is>
-          <t>mk3 KL500</t>
-        </is>
-      </c>
-      <c r="P205" s="4" t="inlineStr">
+          <t>hellowcar 아이오닉6 스마트키, mk3 Ioniq 6 2025 KL500</t>
+        </is>
+      </c>
+      <c r="P205" s="8" t="inlineStr">
         <is>
           <t>더 뉴 아이오닉6 스마트키(95440-KL500) 칩 원문 없음 — KL000 계열 기준 추정</t>
         </is>
@@ -13394,12 +13366,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D206" s="5" t="inlineStr">
+      <c r="D206" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="E206" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -13452,12 +13424,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D207" s="5" t="inlineStr">
+      <c r="D207" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="E207" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -13510,9 +13482,9 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="D208" s="7" t="inlineStr"/>
-      <c r="E208" s="7" t="inlineStr"/>
-      <c r="F208" s="7" t="inlineStr"/>
+      <c r="D208" s="6" t="inlineStr"/>
+      <c r="E208" s="6" t="inlineStr"/>
+      <c r="F208" s="6" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -13552,9 +13524,9 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="D209" s="7" t="inlineStr"/>
-      <c r="E209" s="7" t="inlineStr"/>
-      <c r="F209" s="7" t="inlineStr"/>
+      <c r="D209" s="6" t="inlineStr"/>
+      <c r="E209" s="6" t="inlineStr"/>
+      <c r="F209" s="6" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -13594,9 +13566,9 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="D210" s="7" t="inlineStr"/>
-      <c r="E210" s="7" t="inlineStr"/>
-      <c r="F210" s="7" t="inlineStr"/>
+      <c r="D210" s="6" t="inlineStr"/>
+      <c r="E210" s="6" t="inlineStr"/>
+      <c r="F210" s="6" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -13636,9 +13608,9 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="D211" s="7" t="inlineStr"/>
-      <c r="E211" s="7" t="inlineStr"/>
-      <c r="F211" s="7" t="inlineStr"/>
+      <c r="D211" s="6" t="inlineStr"/>
+      <c r="E211" s="6" t="inlineStr"/>
+      <c r="F211" s="6" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -13695,7 +13667,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>해당 없음[~2004.7], ID46(PCF7936)[2005년형, 2004.8~]</t>
+          <t>해당 없음[~2004.7], ID60[2005년형, 2004.8~]</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -13703,10 +13675,14 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I212" s="2" t="n"/>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>81996-38010[2005년형~]</t>
+        </is>
+      </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>HYN6</t>
+          <t>HYN7</t>
         </is>
       </c>
       <c r="K212" s="2" t="n"/>
@@ -13715,7 +13691,7 @@
       <c r="N212" s="2" t="n"/>
       <c r="O212" s="2" t="inlineStr">
         <is>
-          <t>나무위키 싼타페/1세대, abkeys Santa Fe ID46 PCF7936</t>
+          <t>partsro·hyundaipartsdeal 81996-38010, abkeys 81996-38010 4D60</t>
         </is>
       </c>
       <c r="P212" s="2" t="n"/>
@@ -13753,7 +13729,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)</t>
+          <t>ID60</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -13761,10 +13737,14 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I213" s="2" t="n"/>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>81996-38010</t>
+        </is>
+      </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>HYN6</t>
+          <t>HYN7</t>
         </is>
       </c>
       <c r="K213" s="2" t="n"/>
@@ -13773,7 +13753,7 @@
       <c r="N213" s="2" t="n"/>
       <c r="O213" s="2" t="inlineStr">
         <is>
-          <t>나무위키, ebay Santa Fe 2001-2005 ID46</t>
+          <t>partsro·hyundaipartsdeal 81996-38010, abkeys 81996-38010 4D60</t>
         </is>
       </c>
       <c r="P213" s="2" t="n"/>
@@ -14784,12 +14764,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D229" s="5" t="inlineStr">
+      <c r="D229" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="E229" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -14846,12 +14826,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D230" s="5" t="inlineStr">
+      <c r="D230" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="E230" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -14908,12 +14888,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D231" s="5" t="inlineStr">
+      <c r="D231" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="E231" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -14970,12 +14950,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D232" s="5" t="inlineStr">
+      <c r="D232" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="E232" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15032,12 +15012,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D233" s="5" t="inlineStr">
+      <c r="D233" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="E233" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15094,12 +15074,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D234" s="5" t="inlineStr">
+      <c r="D234" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="E234" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15156,12 +15136,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D235" s="5" t="inlineStr">
+      <c r="D235" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="E235" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15218,12 +15198,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D236" s="5" t="inlineStr">
+      <c r="D236" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="E236" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15280,12 +15260,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D237" s="5" t="inlineStr">
+      <c r="D237" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="E237" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15342,12 +15322,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D238" s="5" t="inlineStr">
+      <c r="D238" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="E238" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15404,12 +15384,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D239" s="5" t="inlineStr">
+      <c r="D239" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E239" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15466,12 +15446,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D240" s="5" t="inlineStr">
+      <c r="D240" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="E240" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15528,12 +15508,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D241" s="5" t="inlineStr">
+      <c r="D241" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="E241" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15590,12 +15570,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D242" s="5" t="inlineStr">
+      <c r="D242" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E242" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15652,12 +15632,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D243" s="5" t="inlineStr">
+      <c r="D243" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15714,12 +15694,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D244" s="5" t="inlineStr">
+      <c r="D244" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15776,12 +15756,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D245" s="5" t="inlineStr">
+      <c r="D245" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="E245" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15838,12 +15818,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D246" s="5" t="inlineStr">
+      <c r="D246" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="E246" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15896,12 +15876,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D247" s="5" t="inlineStr">
+      <c r="D247" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="E247" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -15969,9 +15949,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G248" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[추정]</t>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -15981,7 +15961,7 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>81996-25010[해외 공용 품번]</t>
+          <t>81996-2E010[이모빌라이저키]</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
@@ -15993,20 +15973,16 @@
       <c r="L248" s="2" t="n"/>
       <c r="M248" s="2" t="inlineStr">
         <is>
-          <t>95430-2E200, 95430-2E210</t>
-        </is>
-      </c>
-      <c r="N248" s="4" t="n"/>
+          <t>95430-2E000, 95430-2E110, 95430-2E115, 95430-2E200, 95430-2E210</t>
+        </is>
+      </c>
+      <c r="N248" s="2" t="n"/>
       <c r="O248" s="2" t="inlineStr">
         <is>
-          <t>다나와 투싼(JM), abkeys 81996-25010</t>
-        </is>
-      </c>
-      <c r="P248" s="4" t="inlineStr">
-        <is>
-          <t>국내 JM 이모빌라이저 적용 원문 없음 — 해외 투싼 2005-2009 키(81996-25010, ID46) 기준</t>
-        </is>
-      </c>
+          <t>hellowcar 투싼구형 819962E010, motorialkorea 819962E010 2004-2009, hellowcar 투싼구형 리모콘, abkeys 81996-25010</t>
+        </is>
+      </c>
+      <c r="P248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -16039,9 +16015,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G249" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[추정]</t>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -16051,7 +16027,7 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>81996-25010[해외 공용 품번]</t>
+          <t>81996-2E010[이모빌라이저키]</t>
         </is>
       </c>
       <c r="J249" s="2" t="inlineStr">
@@ -16063,20 +16039,16 @@
       <c r="L249" s="2" t="n"/>
       <c r="M249" s="2" t="inlineStr">
         <is>
-          <t>95430-2E200, 95430-2E210</t>
-        </is>
-      </c>
-      <c r="N249" s="4" t="n"/>
+          <t>95430-2E000, 95430-2E110, 95430-2E115, 95430-2E200, 95430-2E210</t>
+        </is>
+      </c>
+      <c r="N249" s="2" t="n"/>
       <c r="O249" s="2" t="inlineStr">
         <is>
-          <t>abkeys 81996-25010, 원본 리모컨 품번</t>
-        </is>
-      </c>
-      <c r="P249" s="4" t="inlineStr">
-        <is>
-          <t>국내 JM 이모빌라이저 적용 원문 없음 — 해외 투싼 2005-2009 키(81996-25010, ID46) 기준</t>
-        </is>
-      </c>
+          <t>hellowcar 투싼구형 819962E010, motorialkorea 819962E010 2004-2009, hellowcar 투싼구형 리모콘, abkeys 81996-25010</t>
+        </is>
+      </c>
+      <c r="P249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -16109,9 +16081,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G250" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[추정]</t>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -16121,7 +16093,7 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>81996-25010[해외 공용 품번]</t>
+          <t>81996-2E010[이모빌라이저키]</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr">
@@ -16133,20 +16105,16 @@
       <c r="L250" s="2" t="n"/>
       <c r="M250" s="2" t="inlineStr">
         <is>
-          <t>95430-2E200, 95430-2E210</t>
-        </is>
-      </c>
-      <c r="N250" s="4" t="n"/>
+          <t>95430-2E000, 95430-2E110, 95430-2E115, 95430-2E200, 95430-2E210</t>
+        </is>
+      </c>
+      <c r="N250" s="2" t="n"/>
       <c r="O250" s="2" t="inlineStr">
         <is>
-          <t>abkeys</t>
-        </is>
-      </c>
-      <c r="P250" s="4" t="inlineStr">
-        <is>
-          <t>국내 JM 이모빌라이저 적용 원문 없음 — 해외 투싼 2005-2009 키(81996-25010, ID46) 기준</t>
-        </is>
-      </c>
+          <t>hellowcar 투싼구형 819962E010, motorialkorea 819962E010 2004-2009, hellowcar 투싼구형 리모콘, abkeys 81996-25010</t>
+        </is>
+      </c>
+      <c r="P250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -16179,9 +16147,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G251" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[추정]</t>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -16191,7 +16159,7 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>81996-25010[해외 공용 품번]</t>
+          <t>81996-2E010[이모빌라이저키]</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
@@ -16203,20 +16171,16 @@
       <c r="L251" s="2" t="n"/>
       <c r="M251" s="2" t="inlineStr">
         <is>
-          <t>95430-2E200, 95430-2E210</t>
-        </is>
-      </c>
-      <c r="N251" s="4" t="n"/>
+          <t>95430-2E000, 95430-2E110, 95430-2E115, 95430-2E200, 95430-2E210</t>
+        </is>
+      </c>
+      <c r="N251" s="2" t="n"/>
       <c r="O251" s="2" t="inlineStr">
         <is>
-          <t>abkeys</t>
-        </is>
-      </c>
-      <c r="P251" s="4" t="inlineStr">
-        <is>
-          <t>국내 JM 이모빌라이저 적용 원문 없음 — 해외 투싼 2005-2009 키(81996-25010, ID46) 기준</t>
-        </is>
-      </c>
+          <t>hellowcar 투싼구형 819962E010, motorialkorea 819962E010 2004-2009, hellowcar 투싼구형 리모콘, abkeys 81996-25010</t>
+        </is>
+      </c>
+      <c r="P251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -16249,9 +16213,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G252" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[추정]</t>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -16261,7 +16225,7 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>81996-25010[해외 공용 품번]</t>
+          <t>81996-2E010[이모빌라이저키]</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr">
@@ -16273,20 +16237,16 @@
       <c r="L252" s="2" t="n"/>
       <c r="M252" s="2" t="inlineStr">
         <is>
-          <t>95430-2E200, 95430-2E210</t>
-        </is>
-      </c>
-      <c r="N252" s="4" t="n"/>
+          <t>95430-2E000, 95430-2E110, 95430-2E115, 95430-2E200, 95430-2E210</t>
+        </is>
+      </c>
+      <c r="N252" s="2" t="n"/>
       <c r="O252" s="2" t="inlineStr">
         <is>
-          <t>abkeys</t>
-        </is>
-      </c>
-      <c r="P252" s="4" t="inlineStr">
-        <is>
-          <t>국내 JM 이모빌라이저 적용 원문 없음 — 해외 투싼 2005-2009 키(81996-25010, ID46) 기준</t>
-        </is>
-      </c>
+          <t>hellowcar 투싼구형 819962E010, motorialkorea 819962E010 2004-2009, hellowcar 투싼구형 리모콘, abkeys 81996-25010</t>
+        </is>
+      </c>
+      <c r="P252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -16319,9 +16279,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G253" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[추정]</t>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -16331,7 +16291,7 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>81996-25010[해외 공용 품번]</t>
+          <t>81996-2E010[이모빌라이저키]</t>
         </is>
       </c>
       <c r="J253" s="2" t="inlineStr">
@@ -16343,20 +16303,16 @@
       <c r="L253" s="2" t="n"/>
       <c r="M253" s="2" t="inlineStr">
         <is>
-          <t>95430-2E200, 95430-2E210</t>
-        </is>
-      </c>
-      <c r="N253" s="4" t="n"/>
+          <t>95430-2E000, 95430-2E110, 95430-2E115, 95430-2E200, 95430-2E210</t>
+        </is>
+      </c>
+      <c r="N253" s="2" t="n"/>
       <c r="O253" s="2" t="inlineStr">
         <is>
-          <t>abkeys</t>
-        </is>
-      </c>
-      <c r="P253" s="4" t="inlineStr">
-        <is>
-          <t>국내 JM 이모빌라이저 적용 원문 없음 — 해외 투싼 2005-2009 키(81996-25010, ID46) 기준</t>
-        </is>
-      </c>
+          <t>hellowcar 투싼구형 819962E010, motorialkorea 819962E010 2004-2009, hellowcar 투싼구형 리모콘, abkeys 81996-25010</t>
+        </is>
+      </c>
+      <c r="P253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -16792,12 +16748,12 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="D261" s="5" t="inlineStr">
+      <c r="D261" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="E261" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -16854,12 +16810,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="D262" s="5" t="inlineStr">
+      <c r="D262" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="E262" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -16916,12 +16872,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D263" s="5" t="inlineStr">
+      <c r="D263" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="E263" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -16978,12 +16934,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D264" s="5" t="inlineStr">
+      <c r="D264" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="E264" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -17040,12 +16996,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="D265" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="E265" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -17102,12 +17058,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D266" s="5" t="inlineStr">
+      <c r="D266" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="E266" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -17164,12 +17120,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D267" s="5" t="inlineStr">
+      <c r="D267" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="E267" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -17226,12 +17182,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D268" s="5" t="inlineStr">
+      <c r="D268" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="E268" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -17288,12 +17244,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D269" s="5" t="inlineStr">
+      <c r="D269" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -17350,12 +17306,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D270" s="5" t="inlineStr">
+      <c r="D270" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E270" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -17367,7 +17323,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>ID47(NCF29A1X)</t>
+          <t>ID47(NCF29A1X)[~2023.10], ID4A(NCF29A1M)[더 뉴 투싼, 2023.11~]</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -17384,14 +17340,14 @@
       <c r="K270" s="2" t="n"/>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>95440-N9000, 95440-N9002, 95440-N9010, 95440-N9012, 95440-N9070, 95440-N9072, 95440-N9080[7버튼], 95440-N9082</t>
+          <t>95440-N9070[~2023.10], 95440-N9080[~2023.10], 95440-N9500[더 뉴 투싼], 95440-N9570[더 뉴 투싼]</t>
         </is>
       </c>
       <c r="M270" s="2" t="n"/>
       <c r="N270" s="2" t="n"/>
       <c r="O270" s="2" t="inlineStr">
         <is>
-          <t>transponderisland 2021-2024 N9070</t>
+          <t>abkeys N9530/N9570 2024-2025, abkeys N9550·N9520 2025-2026 ID4A</t>
         </is>
       </c>
       <c r="P270" s="2" t="n"/>
@@ -17412,12 +17368,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D271" s="5" t="inlineStr">
+      <c r="D271" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="E271" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -17429,7 +17385,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>ID47(NCF29A1X)</t>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -17437,23 +17393,19 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I271" s="2" t="inlineStr">
-        <is>
-          <t>81996-N9000</t>
-        </is>
-      </c>
+      <c r="I271" s="2" t="n"/>
       <c r="J271" s="2" t="n"/>
       <c r="K271" s="2" t="n"/>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>95440-N9000, 95440-N9002, 95440-N9010, 95440-N9012, 95440-N9070, 95440-N9072, 95440-N9080[7버튼], 95440-N9082</t>
+          <t>95440-N9500[5버튼], 95440-N9520[3버튼], 95440-N9530[4버튼], 95440-N9550[4버튼], 95440-N9570[5버튼]</t>
         </is>
       </c>
       <c r="M271" s="2" t="n"/>
       <c r="N271" s="2" t="n"/>
       <c r="O271" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2024 Tucson N9070</t>
+          <t>abkeys N9550 2025-2026 ID4A, abkeys N9570 2024-2025, royalkeysupply 2026 Tucson N9500</t>
         </is>
       </c>
       <c r="P271" s="2" t="n"/>
@@ -17474,12 +17426,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D272" s="5" t="inlineStr">
+      <c r="D272" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="E272" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -17491,7 +17443,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>ID47(NCF29A1X)</t>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -17499,23 +17451,19 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I272" s="2" t="inlineStr">
-        <is>
-          <t>81996-N9000</t>
-        </is>
-      </c>
+      <c r="I272" s="2" t="n"/>
       <c r="J272" s="2" t="n"/>
       <c r="K272" s="2" t="n"/>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>95440-N9000, 95440-N9002, 95440-N9010, 95440-N9012, 95440-N9070, 95440-N9072, 95440-N9080[7버튼], 95440-N9082</t>
+          <t>95440-N9500[5버튼], 95440-N9520[3버튼], 95440-N9530[4버튼], 95440-N9550[4버튼], 95440-N9570[5버튼]</t>
         </is>
       </c>
       <c r="M272" s="2" t="n"/>
       <c r="N272" s="2" t="n"/>
       <c r="O272" s="2" t="inlineStr">
         <is>
-          <t>mk3 N9070</t>
+          <t>abkeys N9550 2025-2026 ID4A, abkeys N9570 2024-2025, royalkeysupply 2026 Tucson N9500</t>
         </is>
       </c>
       <c r="P272" s="2" t="n"/>
@@ -17536,12 +17484,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D273" s="5" t="inlineStr">
+      <c r="D273" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="E273" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -17551,9 +17499,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G273" s="4" t="inlineStr">
-        <is>
-          <t>ID47(NCF29A1X)[추정]</t>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -17561,30 +17509,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I273" s="2" t="inlineStr">
-        <is>
-          <t>81996-N9000</t>
-        </is>
-      </c>
+      <c r="I273" s="2" t="n"/>
       <c r="J273" s="2" t="n"/>
       <c r="K273" s="2" t="n"/>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>95440-N9070</t>
+          <t>95440-N9500[5버튼], 95440-N9520[3버튼], 95440-N9530[4버튼], 95440-N9550[4버튼], 95440-N9570[5버튼]</t>
         </is>
       </c>
       <c r="M273" s="2" t="n"/>
-      <c r="N273" s="4" t="n"/>
+      <c r="N273" s="2" t="n"/>
       <c r="O273" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 투싼NX4</t>
-        </is>
-      </c>
-      <c r="P273" s="4" t="inlineStr">
-        <is>
-          <t>2026년형 신규 품번·칩 원문 없음 — N9070 계열 기준 추정</t>
-        </is>
-      </c>
+          <t>abkeys N9550 2025-2026 ID4A, abkeys N9570 2024-2025, royalkeysupply 2026 Tucson N9500</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -18696,12 +18636,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D291" s="5" t="inlineStr">
+      <c r="D291" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="E291" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -18758,12 +18698,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D292" s="5" t="inlineStr">
+      <c r="D292" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="E292" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -18820,12 +18760,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D293" s="5" t="inlineStr">
+      <c r="D293" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -18882,12 +18822,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D294" s="5" t="inlineStr">
+      <c r="D294" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="E294" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -18944,12 +18884,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D295" s="5" t="inlineStr">
+      <c r="D295" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="E295" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19006,12 +18946,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D296" s="5" t="inlineStr">
+      <c r="D296" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="E296" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19068,12 +19008,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D297" s="5" t="inlineStr">
+      <c r="D297" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="E297" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19130,12 +19070,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D298" s="5" t="inlineStr">
+      <c r="D298" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E298" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19145,9 +19085,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G298" s="4" t="inlineStr">
-        <is>
-          <t>ID47[추정]</t>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>ID47(NCF29A1X)</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -19155,22 +19095,26 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I298" s="2" t="n"/>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>81996-J9020</t>
+        </is>
+      </c>
       <c r="J298" s="2" t="n"/>
       <c r="K298" s="2" t="n"/>
-      <c r="L298" s="2" t="n"/>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>95440-I3450[4버튼]</t>
+        </is>
+      </c>
       <c r="M298" s="2" t="n"/>
-      <c r="N298" s="4" t="n"/>
+      <c r="N298" s="2" t="n"/>
       <c r="O298" s="2" t="inlineStr">
         <is>
-          <t>abkeys 코나 2021+ J9400/I3450</t>
-        </is>
-      </c>
-      <c r="P298" s="4" t="inlineStr">
-        <is>
-          <t>코나 N 전용 스마트키 품번·칩 원문 없음 — 더 뉴 코나(ID47) 기준 추정</t>
-        </is>
-      </c>
+          <t>remotesandkeys 2023 Kona N 95440-I3450, royalkeysupply I3450, abkeys I3450 NCF29A1X</t>
+        </is>
+      </c>
+      <c r="P298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -19188,12 +19132,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D299" s="5" t="inlineStr">
+      <c r="D299" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="E299" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19203,9 +19147,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G299" s="4" t="inlineStr">
-        <is>
-          <t>ID47[추정]</t>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>ID47(NCF29A1X)</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -19213,22 +19157,26 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I299" s="2" t="n"/>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>81996-J9020</t>
+        </is>
+      </c>
       <c r="J299" s="2" t="n"/>
       <c r="K299" s="2" t="n"/>
-      <c r="L299" s="2" t="n"/>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>95440-I3450[4버튼]</t>
+        </is>
+      </c>
       <c r="M299" s="2" t="n"/>
-      <c r="N299" s="4" t="n"/>
+      <c r="N299" s="2" t="n"/>
       <c r="O299" s="2" t="inlineStr">
         <is>
-          <t>abkeys</t>
-        </is>
-      </c>
-      <c r="P299" s="4" t="inlineStr">
-        <is>
-          <t>코나 N 전용 스마트키 품번·칩 원문 없음 — 더 뉴 코나(ID47) 기준 추정</t>
-        </is>
-      </c>
+          <t>remotesandkeys 2023 Kona N 95440-I3450, royalkeysupply I3450, abkeys I3450 NCF29A1X</t>
+        </is>
+      </c>
+      <c r="P299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -19246,12 +19194,12 @@
           <t>2023(단종)</t>
         </is>
       </c>
-      <c r="D300" s="5" t="inlineStr">
+      <c r="D300" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="E300" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19261,9 +19209,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G300" s="4" t="inlineStr">
-        <is>
-          <t>ID47[추정]</t>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>ID47(NCF29A1X)</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -19271,22 +19219,26 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I300" s="2" t="n"/>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>81996-J9020</t>
+        </is>
+      </c>
       <c r="J300" s="2" t="n"/>
       <c r="K300" s="2" t="n"/>
-      <c r="L300" s="2" t="n"/>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>95440-I3450[4버튼]</t>
+        </is>
+      </c>
       <c r="M300" s="2" t="n"/>
-      <c r="N300" s="4" t="n"/>
+      <c r="N300" s="2" t="n"/>
       <c r="O300" s="2" t="inlineStr">
         <is>
-          <t>abkeys</t>
-        </is>
-      </c>
-      <c r="P300" s="4" t="inlineStr">
-        <is>
-          <t>코나 N 전용 스마트키 품번·칩 원문 없음 — 더 뉴 코나(ID47) 기준 추정</t>
-        </is>
-      </c>
+          <t>remotesandkeys 2023 Kona N 95440-I3450, royalkeysupply I3450, abkeys I3450 NCF29A1X</t>
+        </is>
+      </c>
+      <c r="P300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -19304,12 +19256,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D301" s="5" t="inlineStr">
+      <c r="D301" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="E301" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19362,12 +19314,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D302" s="5" t="inlineStr">
+      <c r="D302" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="E302" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19420,12 +19372,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D303" s="5" t="inlineStr">
+      <c r="D303" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="E303" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19478,12 +19430,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D304" s="5" t="inlineStr">
+      <c r="D304" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="E304" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19536,12 +19488,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D305" s="5" t="inlineStr">
+      <c r="D305" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="E305" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19594,12 +19546,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D306" s="5" t="inlineStr">
+      <c r="D306" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="E306" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19652,12 +19604,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D307" s="5" t="inlineStr">
+      <c r="D307" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="E307" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19710,12 +19662,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D308" s="5" t="inlineStr">
+      <c r="D308" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="E308" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19768,12 +19720,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D309" s="5" t="inlineStr">
+      <c r="D309" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="E309" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19830,12 +19782,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D310" s="5" t="inlineStr">
+      <c r="D310" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="E310" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19892,12 +19844,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D311" s="5" t="inlineStr">
+      <c r="D311" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="E311" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -19954,12 +19906,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D312" s="5" t="inlineStr">
+      <c r="D312" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="E312" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20016,12 +19968,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D313" s="5" t="inlineStr">
+      <c r="D313" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="E313" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20078,12 +20030,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D314" s="5" t="inlineStr">
+      <c r="D314" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="E314" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20140,12 +20092,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D315" s="5" t="inlineStr">
+      <c r="D315" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="E315" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20202,12 +20154,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D316" s="5" t="inlineStr">
+      <c r="D316" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="E316" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20264,12 +20216,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D317" s="5" t="inlineStr">
+      <c r="D317" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="E317" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20326,12 +20278,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D318" s="5" t="inlineStr">
+      <c r="D318" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="E318" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20388,12 +20340,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D319" s="5" t="inlineStr">
+      <c r="D319" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="E319" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20450,12 +20402,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D320" s="5" t="inlineStr">
+      <c r="D320" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="E320" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20512,12 +20464,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D321" s="5" t="inlineStr">
+      <c r="D321" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="E321" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20574,12 +20526,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D322" s="5" t="inlineStr">
+      <c r="D322" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="E322" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20636,12 +20588,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D323" s="5" t="inlineStr">
+      <c r="D323" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20698,12 +20650,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D324" s="5" t="inlineStr">
+      <c r="D324" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20760,12 +20712,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D325" s="5" t="inlineStr">
+      <c r="D325" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="E325" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20822,12 +20774,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D326" s="5" t="inlineStr">
+      <c r="D326" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="E326" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20888,12 +20840,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D327" s="5" t="inlineStr">
+      <c r="D327" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="E327" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -20954,12 +20906,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D328" s="5" t="inlineStr">
+      <c r="D328" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="E328" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -21020,12 +20972,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D329" s="5" t="inlineStr">
+      <c r="D329" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="E329" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -21086,12 +21038,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D330" s="5" t="inlineStr">
+      <c r="D330" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="E330" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -21152,12 +21104,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D331" s="5" t="inlineStr">
+      <c r="D331" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="E331" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -21218,12 +21170,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D332" s="5" t="inlineStr">
+      <c r="D332" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="E332" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -21284,12 +21236,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D333" s="5" t="inlineStr">
+      <c r="D333" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="E333" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -21350,12 +21302,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D334" s="5" t="inlineStr">
+      <c r="D334" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="E334" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -21412,12 +21364,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D335" s="5" t="inlineStr">
+      <c r="D335" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="E335" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -21474,9 +21426,9 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="D336" s="7" t="inlineStr"/>
-      <c r="E336" s="7" t="inlineStr"/>
-      <c r="F336" s="7" t="inlineStr"/>
+      <c r="D336" s="6" t="inlineStr"/>
+      <c r="E336" s="6" t="inlineStr"/>
+      <c r="F336" s="6" t="inlineStr"/>
       <c r="G336" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -21516,9 +21468,9 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="D337" s="7" t="inlineStr"/>
-      <c r="E337" s="7" t="inlineStr"/>
-      <c r="F337" s="7" t="inlineStr"/>
+      <c r="D337" s="6" t="inlineStr"/>
+      <c r="E337" s="6" t="inlineStr"/>
+      <c r="F337" s="6" t="inlineStr"/>
       <c r="G337" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -21558,9 +21510,9 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="D338" s="7" t="inlineStr"/>
-      <c r="E338" s="7" t="inlineStr"/>
-      <c r="F338" s="7" t="inlineStr"/>
+      <c r="D338" s="6" t="inlineStr"/>
+      <c r="E338" s="6" t="inlineStr"/>
+      <c r="F338" s="6" t="inlineStr"/>
       <c r="G338" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -21600,9 +21552,9 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="D339" s="7" t="inlineStr"/>
-      <c r="E339" s="7" t="inlineStr"/>
-      <c r="F339" s="7" t="inlineStr"/>
+      <c r="D339" s="6" t="inlineStr"/>
+      <c r="E339" s="6" t="inlineStr"/>
+      <c r="F339" s="6" t="inlineStr"/>
       <c r="G339" s="2" t="inlineStr">
         <is>
           <t>해당 없음</t>
@@ -21657,9 +21609,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G340" s="4" t="inlineStr">
-        <is>
-          <t>ID4C[일부 자료]</t>
+      <c r="G340" s="8" t="inlineStr">
+        <is>
+          <t>ID60[자료 상충], ID4C[자료 상충]</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -21667,20 +21619,28 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I340" s="2" t="n"/>
-      <c r="J340" s="2" t="n"/>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>81996-4A250</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>HYN6</t>
+        </is>
+      </c>
       <c r="K340" s="2" t="n"/>
       <c r="L340" s="2" t="n"/>
       <c r="M340" s="2" t="n"/>
-      <c r="N340" s="4" t="n"/>
+      <c r="N340" s="8" t="n"/>
       <c r="O340" s="2" t="inlineStr">
         <is>
-          <t>모토야, transpondery Hyundai catalog(H-1 Starex 2004-2006 4C)</t>
-        </is>
-      </c>
-      <c r="P340" s="4" t="inlineStr">
-        <is>
-          <t>뉴 스타렉스(2004.1) 이모빌라이저 기본 적용은 확인, 칩은 해외 H-1 스타렉스 자료 기준</t>
+          <t>ebay 819964A250 Starex 2000-2007, abkeys 81996-4A250 4D60, transpondery Hyundai</t>
+        </is>
+      </c>
+      <c r="P340" s="8" t="inlineStr">
+        <is>
+          <t>순정 이모빌라이저키 81996-4A250(2000.4~2007.12)은 4D60, 해외 카탈로그(transpondery)는 2004-2006 Texas 4C 표기</t>
         </is>
       </c>
     </row>
@@ -21715,9 +21675,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G341" s="4" t="inlineStr">
-        <is>
-          <t>ID4C[일부 자료]</t>
+      <c r="G341" s="8" t="inlineStr">
+        <is>
+          <t>ID60[자료 상충], ID4C[자료 상충]</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -21725,20 +21685,28 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I341" s="2" t="n"/>
-      <c r="J341" s="2" t="n"/>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>81996-4A250</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr">
+        <is>
+          <t>HYN6</t>
+        </is>
+      </c>
       <c r="K341" s="2" t="n"/>
       <c r="L341" s="2" t="n"/>
       <c r="M341" s="2" t="n"/>
-      <c r="N341" s="4" t="n"/>
+      <c r="N341" s="8" t="n"/>
       <c r="O341" s="2" t="inlineStr">
         <is>
-          <t>transpondery Hyundai catalog</t>
-        </is>
-      </c>
-      <c r="P341" s="4" t="inlineStr">
-        <is>
-          <t>뉴 스타렉스(2004.1) 이모빌라이저 기본 적용은 확인, 칩은 해외 H-1 스타렉스 자료 기준</t>
+          <t>ebay 819964A250 Starex 2000-2007, abkeys 81996-4A250 4D60, transpondery Hyundai</t>
+        </is>
+      </c>
+      <c r="P341" s="8" t="inlineStr">
+        <is>
+          <t>순정 이모빌라이저키 81996-4A250(2000.4~2007.12)은 4D60, 해외 카탈로그(transpondery)는 2004-2006 Texas 4C 표기</t>
         </is>
       </c>
     </row>
@@ -21773,9 +21741,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G342" s="4" t="inlineStr">
-        <is>
-          <t>ID4C[~2005, 일부 자료], ID60[2006~, 일부 자료]</t>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>ID60</t>
         </is>
       </c>
       <c r="H342" s="2" t="inlineStr">
@@ -21785,7 +21753,7 @@
       </c>
       <c r="I342" s="2" t="inlineStr">
         <is>
-          <t>81996-4A250[해외 공용 품번]</t>
+          <t>81996-4A250</t>
         </is>
       </c>
       <c r="J342" s="2" t="inlineStr">
@@ -21796,17 +21764,13 @@
       <c r="K342" s="2" t="n"/>
       <c r="L342" s="2" t="n"/>
       <c r="M342" s="2" t="n"/>
-      <c r="N342" s="4" t="n"/>
+      <c r="N342" s="2" t="n"/>
       <c r="O342" s="2" t="inlineStr">
         <is>
-          <t>abkeys H1 81996-4A250 4D60, transpondery</t>
-        </is>
-      </c>
-      <c r="P342" s="4" t="inlineStr">
-        <is>
-          <t>칩은 해외 H-1 스타렉스 자료 기준(4C → 4D60 전환)</t>
-        </is>
-      </c>
+          <t>abkeys 81996-4A250 4D60</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -21839,9 +21803,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G343" s="4" t="inlineStr">
-        <is>
-          <t>ID60[일부 자료]</t>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>ID60</t>
         </is>
       </c>
       <c r="H343" s="2" t="inlineStr">
@@ -21851,7 +21815,7 @@
       </c>
       <c r="I343" s="2" t="inlineStr">
         <is>
-          <t>81996-4A250[해외 공용 품번]</t>
+          <t>81996-4A250</t>
         </is>
       </c>
       <c r="J343" s="2" t="inlineStr">
@@ -21862,17 +21826,13 @@
       <c r="K343" s="2" t="n"/>
       <c r="L343" s="2" t="n"/>
       <c r="M343" s="2" t="n"/>
-      <c r="N343" s="4" t="n"/>
+      <c r="N343" s="2" t="n"/>
       <c r="O343" s="2" t="inlineStr">
         <is>
-          <t>abkeys 81996-4A250</t>
-        </is>
-      </c>
-      <c r="P343" s="4" t="inlineStr">
-        <is>
-          <t>칩은 해외 H-1 스타렉스 자료 기준</t>
-        </is>
-      </c>
+          <t>abkeys 81996-4A250 4D60</t>
+        </is>
+      </c>
+      <c r="P343" s="2" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -22424,10 +22384,14 @@
           <t>95430-4H400[이모빌라이저 미적용], 95430-4H500[이모빌라이저 사양], 95430-4H401</t>
         </is>
       </c>
-      <c r="N352" s="2" t="n"/>
+      <c r="N352" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000</t>
+        </is>
+      </c>
       <c r="O352" s="2" t="inlineStr">
         <is>
-          <t>partsro 819962H010</t>
+          <t>partsro 95420D4000 올뉴K7·포터2·그랜드 스타렉스, amazon 95420-D4000 Accent 18-21</t>
         </is>
       </c>
       <c r="P352" s="2" t="n"/>
@@ -22486,10 +22450,14 @@
           <t>95430-4H400[이모빌라이저 미적용], 95430-4H500[이모빌라이저 사양], 95430-4H401</t>
         </is>
       </c>
-      <c r="N353" s="2" t="n"/>
+      <c r="N353" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000</t>
+        </is>
+      </c>
       <c r="O353" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 95420D4000 올뉴K7·포터2·그랜드 스타렉스, amazon 95420-D4000 Accent 18-21</t>
         </is>
       </c>
       <c r="P353" s="2" t="n"/>
@@ -22548,10 +22516,14 @@
           <t>95430-4H400[이모빌라이저 미적용], 95430-4H500[이모빌라이저 사양], 95430-4H401</t>
         </is>
       </c>
-      <c r="N354" s="2" t="n"/>
+      <c r="N354" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000</t>
+        </is>
+      </c>
       <c r="O354" s="2" t="inlineStr">
         <is>
-          <t>hellowcar, 원본 모비스 기록</t>
+          <t>partsro 95420D4000 올뉴K7·포터2·그랜드 스타렉스, amazon 95420-D4000 Accent 18-21</t>
         </is>
       </c>
       <c r="P354" s="2" t="n"/>
@@ -22587,9 +22559,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G355" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H355" s="2" t="inlineStr">
@@ -22606,17 +22578,17 @@
           <t>95430-4H401</t>
         </is>
       </c>
-      <c r="N355" s="4" t="n"/>
+      <c r="N355" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000</t>
+        </is>
+      </c>
       <c r="O355" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 95430-4H400/4H500 ~2018.4.2</t>
-        </is>
-      </c>
-      <c r="P355" s="4" t="inlineStr">
-        <is>
-          <t>2018.4.2 이후 폴딩키 품번·칩 원문 없음 — 이전 ID46 기준 추정</t>
-        </is>
-      </c>
+          <t>partsro 95420D4000 올뉴K7·포터2·그랜드 스타렉스, amazon 95420-D4000 Accent 18-21</t>
+        </is>
+      </c>
+      <c r="P355" s="2" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -22649,9 +22621,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G356" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
@@ -22668,17 +22640,17 @@
           <t>95430-4H401</t>
         </is>
       </c>
-      <c r="N356" s="4" t="n"/>
+      <c r="N356" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000</t>
+        </is>
+      </c>
       <c r="O356" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
-        </is>
-      </c>
-      <c r="P356" s="4" t="inlineStr">
-        <is>
-          <t>2018.4.2 이후 폴딩키 품번·칩 원문 없음 — 이전 ID46 기준 추정</t>
-        </is>
-      </c>
+          <t>partsro 95420D4000 올뉴K7·포터2·그랜드 스타렉스, amazon 95420-D4000 Accent 18-21</t>
+        </is>
+      </c>
+      <c r="P356" s="2" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -22711,9 +22683,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G357" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
@@ -22730,17 +22702,17 @@
           <t>95430-4H401</t>
         </is>
       </c>
-      <c r="N357" s="4" t="n"/>
+      <c r="N357" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000</t>
+        </is>
+      </c>
       <c r="O357" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
-        </is>
-      </c>
-      <c r="P357" s="4" t="inlineStr">
-        <is>
-          <t>2018.4.2 이후 폴딩키 품번·칩 원문 없음 — 이전 ID46 기준 추정</t>
-        </is>
-      </c>
+          <t>partsro 95420D4000 올뉴K7·포터2·그랜드 스타렉스, amazon 95420-D4000 Accent 18-21</t>
+        </is>
+      </c>
+      <c r="P357" s="2" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -22773,9 +22745,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G358" s="4" t="inlineStr">
-        <is>
-          <t>ID46[추정]</t>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
@@ -22792,17 +22764,17 @@
           <t>95430-4H401</t>
         </is>
       </c>
-      <c r="N358" s="4" t="n"/>
+      <c r="N358" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000</t>
+        </is>
+      </c>
       <c r="O358" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
-        </is>
-      </c>
-      <c r="P358" s="4" t="inlineStr">
-        <is>
-          <t>2018.4.2 이후 폴딩키 품번·칩 원문 없음 — 이전 ID46 기준 추정</t>
-        </is>
-      </c>
+          <t>partsro 95420D4000 올뉴K7·포터2·그랜드 스타렉스, amazon 95420-D4000 Accent 18-21</t>
+        </is>
+      </c>
+      <c r="P358" s="2" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -22820,12 +22792,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D359" s="5" t="inlineStr">
+      <c r="D359" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="E359" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -22886,12 +22858,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D360" s="5" t="inlineStr">
+      <c r="D360" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="E360" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -22952,12 +22924,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D361" s="5" t="inlineStr">
+      <c r="D361" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="E361" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -23018,12 +22990,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D362" s="5" t="inlineStr">
+      <c r="D362" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="E362" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -23084,12 +23056,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D363" s="5" t="inlineStr">
+      <c r="D363" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="E363" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -23150,12 +23122,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D364" s="5" t="inlineStr">
+      <c r="D364" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="E364" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -23254,10 +23226,14 @@
           <t>81996-4F100[키리모컨], 81996-4F120[키리모컨]</t>
         </is>
       </c>
-      <c r="N365" s="2" t="n"/>
+      <c r="N365" s="2" t="inlineStr">
+        <is>
+          <t>95440-4F100</t>
+        </is>
+      </c>
       <c r="O365" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 포터2 819964F010/4F020/4F025/4F760/4F000, carkeyno1 81996-4F020 이모빌라이저키블레이드(46), hellowcar 키리모콘 819964F100/4F101/4F120/4F121</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P365" s="2" t="n"/>
@@ -23316,10 +23292,14 @@
           <t>81996-4F100[키리모컨], 81996-4F120[키리모컨]</t>
         </is>
       </c>
-      <c r="N366" s="2" t="n"/>
+      <c r="N366" s="2" t="inlineStr">
+        <is>
+          <t>95440-4F100</t>
+        </is>
+      </c>
       <c r="O366" s="2" t="inlineStr">
         <is>
-          <t>hellowcar, carkeyno1</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P366" s="2" t="n"/>
@@ -23378,10 +23358,14 @@
           <t>81996-4F100[키리모컨], 81996-4F120[키리모컨]</t>
         </is>
       </c>
-      <c r="N367" s="2" t="n"/>
+      <c r="N367" s="2" t="inlineStr">
+        <is>
+          <t>95440-4F100</t>
+        </is>
+      </c>
       <c r="O367" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P367" s="2" t="n"/>
@@ -23440,10 +23424,14 @@
           <t>81996-4F100[키리모컨], 81996-4F120[키리모컨]</t>
         </is>
       </c>
-      <c r="N368" s="2" t="n"/>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>95440-4F100</t>
+        </is>
+      </c>
       <c r="O368" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P368" s="2" t="n"/>
@@ -23502,10 +23490,14 @@
           <t>81996-4F100[~2008.9.1, 키리모컨], 81996-4F120[~2008.9.1, 키리모컨], 81996-4F101[2008.9.2~, 키리모컨], 81996-4F121[2008.9.2~, 키리모컨]</t>
         </is>
       </c>
-      <c r="N369" s="2" t="n"/>
+      <c r="N369" s="2" t="inlineStr">
+        <is>
+          <t>95440-4F100</t>
+        </is>
+      </c>
       <c r="O369" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P369" s="2" t="n"/>
@@ -23564,10 +23556,14 @@
           <t>81996-4F101[키리모컨], 81996-4F121[키리모컨]</t>
         </is>
       </c>
-      <c r="N370" s="2" t="n"/>
+      <c r="N370" s="2" t="inlineStr">
+        <is>
+          <t>95440-4F100</t>
+        </is>
+      </c>
       <c r="O370" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P370" s="2" t="n"/>
@@ -23626,10 +23622,14 @@
           <t>81996-4F101[키리모컨], 81996-4F121[키리모컨]</t>
         </is>
       </c>
-      <c r="N371" s="2" t="n"/>
+      <c r="N371" s="2" t="inlineStr">
+        <is>
+          <t>95440-4F100</t>
+        </is>
+      </c>
       <c r="O371" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P371" s="2" t="n"/>
@@ -23688,10 +23688,14 @@
           <t>81996-4F101[키리모컨], 81996-4F121[키리모컨]</t>
         </is>
       </c>
-      <c r="N372" s="2" t="n"/>
+      <c r="N372" s="2" t="inlineStr">
+        <is>
+          <t>95440-4F100</t>
+        </is>
+      </c>
       <c r="O372" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P372" s="2" t="n"/>
@@ -23750,10 +23754,14 @@
           <t>81996-4F101[키리모컨], 81996-4F121[키리모컨]</t>
         </is>
       </c>
-      <c r="N373" s="2" t="n"/>
+      <c r="N373" s="2" t="inlineStr">
+        <is>
+          <t>95440-4F100</t>
+        </is>
+      </c>
       <c r="O373" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P373" s="2" t="n"/>
@@ -23812,10 +23820,14 @@
           <t>81996-4F101[키리모컨], 81996-4F121[키리모컨]</t>
         </is>
       </c>
-      <c r="N374" s="2" t="n"/>
+      <c r="N374" s="2" t="inlineStr">
+        <is>
+          <t>95440-4F100</t>
+        </is>
+      </c>
       <c r="O374" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P374" s="2" t="n"/>
@@ -23874,10 +23886,14 @@
           <t>81996-4F101[키리모컨], 81996-4F121[키리모컨]</t>
         </is>
       </c>
-      <c r="N375" s="2" t="n"/>
+      <c r="N375" s="2" t="inlineStr">
+        <is>
+          <t>95440-4F100</t>
+        </is>
+      </c>
       <c r="O375" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P375" s="2" t="n"/>
@@ -23936,10 +23952,14 @@
           <t>81996-4F101[키리모컨], 81996-4F121[키리모컨]</t>
         </is>
       </c>
-      <c r="N376" s="2" t="n"/>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>95440-4F100</t>
+        </is>
+      </c>
       <c r="O376" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P376" s="2" t="n"/>
@@ -23998,10 +24018,14 @@
           <t>95430-4F500, 95430-4F510, 95430-4F515, 95430-4F000, 95430-4F100, 95430-4F001, 95430-4F101, 95430-4F600</t>
         </is>
       </c>
-      <c r="N377" s="2" t="n"/>
+      <c r="N377" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000, 95420-4F500</t>
+        </is>
+      </c>
       <c r="O377" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 포터2 폴딩키</t>
+          <t>partsro 95420D4000, partsro 954204F500, cvinfo 2024 포터II LPG 출시</t>
         </is>
       </c>
       <c r="P377" s="2" t="n"/>
@@ -24060,10 +24084,14 @@
           <t>95430-4F500, 95430-4F510, 95430-4F515, 95430-4F000, 95430-4F100, 95430-4F001, 95430-4F101, 95430-4F600</t>
         </is>
       </c>
-      <c r="N378" s="2" t="n"/>
+      <c r="N378" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000, 95420-4F500</t>
+        </is>
+      </c>
       <c r="O378" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 95420D4000, partsro 954204F500, cvinfo 2024 포터II LPG 출시</t>
         </is>
       </c>
       <c r="P378" s="2" t="n"/>
@@ -24122,10 +24150,14 @@
           <t>95430-4F500, 95430-4F510, 95430-4F515, 95430-4F000, 95430-4F100, 95430-4F001, 95430-4F101, 95430-4F600</t>
         </is>
       </c>
-      <c r="N379" s="2" t="n"/>
+      <c r="N379" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000, 95420-4F500</t>
+        </is>
+      </c>
       <c r="O379" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 95420D4000, partsro 954204F500, cvinfo 2024 포터II LPG 출시</t>
         </is>
       </c>
       <c r="P379" s="2" t="n"/>
@@ -24184,10 +24216,14 @@
           <t>95430-4F500, 95430-4F510, 95430-4F515, 95430-4F000, 95430-4F100, 95430-4F001, 95430-4F101, 95430-4F600</t>
         </is>
       </c>
-      <c r="N380" s="2" t="n"/>
+      <c r="N380" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000, 95420-4F500</t>
+        </is>
+      </c>
       <c r="O380" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>partsro 95420D4000, partsro 954204F500, cvinfo 2024 포터II LPG 출시</t>
         </is>
       </c>
       <c r="P380" s="2" t="n"/>
@@ -24223,14 +24259,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G381" s="8" t="inlineStr">
-        <is>
-          <t>ID46[폴딩키], 확인 불가[스마트키]</t>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>막대키,폴딩키,스마트키</t>
+          <t>막대키,폴딩키</t>
         </is>
       </c>
       <c r="I381" s="2" t="inlineStr">
@@ -24240,27 +24276,23 @@
       </c>
       <c r="J381" s="2" t="n"/>
       <c r="K381" s="2" t="n"/>
-      <c r="L381" s="2" t="inlineStr">
-        <is>
-          <t>95440-4FGA0</t>
-        </is>
-      </c>
+      <c r="L381" s="2" t="n"/>
       <c r="M381" s="2" t="inlineStr">
         <is>
           <t>95430-4F500</t>
         </is>
       </c>
-      <c r="N381" s="8" t="n"/>
+      <c r="N381" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000, 95420-4F500</t>
+        </is>
+      </c>
       <c r="O381" s="2" t="inlineStr">
         <is>
-          <t>원본 모비스 기록</t>
-        </is>
-      </c>
-      <c r="P381" s="8" t="inlineStr">
-        <is>
-          <t>스마트키(95440-4FGA0) 칩 원문 없음</t>
-        </is>
-      </c>
+          <t>partsro 95420D4000, partsro 954204F500, cvinfo 2024 포터II LPG 출시</t>
+        </is>
+      </c>
+      <c r="P381" s="2" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -24293,14 +24325,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G382" s="8" t="inlineStr">
-        <is>
-          <t>ID46[폴딩키], 확인 불가[스마트키]</t>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>막대키,폴딩키,스마트키</t>
+          <t>막대키,폴딩키</t>
         </is>
       </c>
       <c r="I382" s="2" t="inlineStr">
@@ -24310,27 +24342,23 @@
       </c>
       <c r="J382" s="2" t="n"/>
       <c r="K382" s="2" t="n"/>
-      <c r="L382" s="2" t="inlineStr">
-        <is>
-          <t>95440-4FGA0</t>
-        </is>
-      </c>
+      <c r="L382" s="2" t="n"/>
       <c r="M382" s="2" t="inlineStr">
         <is>
           <t>95430-4F500</t>
         </is>
       </c>
-      <c r="N382" s="8" t="n"/>
+      <c r="N382" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000, 95420-4F500</t>
+        </is>
+      </c>
       <c r="O382" s="2" t="inlineStr">
         <is>
-          <t>원본</t>
-        </is>
-      </c>
-      <c r="P382" s="8" t="inlineStr">
-        <is>
-          <t>스마트키(95440-4FGA0) 칩 원문 없음</t>
-        </is>
-      </c>
+          <t>partsro 95420D4000, partsro 954204F500, cvinfo 2024 포터II LPG 출시</t>
+        </is>
+      </c>
+      <c r="P382" s="2" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -24363,14 +24391,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G383" s="8" t="inlineStr">
-        <is>
-          <t>ID46[폴딩키], 확인 불가[스마트키]</t>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>막대키,폴딩키,스마트키</t>
+          <t>막대키,폴딩키</t>
         </is>
       </c>
       <c r="I383" s="2" t="inlineStr">
@@ -24380,27 +24408,23 @@
       </c>
       <c r="J383" s="2" t="n"/>
       <c r="K383" s="2" t="n"/>
-      <c r="L383" s="2" t="inlineStr">
-        <is>
-          <t>95440-4FGA0</t>
-        </is>
-      </c>
+      <c r="L383" s="2" t="n"/>
       <c r="M383" s="2" t="inlineStr">
         <is>
           <t>95430-4F500</t>
         </is>
       </c>
-      <c r="N383" s="8" t="n"/>
+      <c r="N383" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000, 95420-4F500</t>
+        </is>
+      </c>
       <c r="O383" s="2" t="inlineStr">
         <is>
-          <t>원본</t>
-        </is>
-      </c>
-      <c r="P383" s="8" t="inlineStr">
-        <is>
-          <t>스마트키(95440-4FGA0) 칩 원문 없음</t>
-        </is>
-      </c>
+          <t>partsro 95420D4000, partsro 954204F500, cvinfo 2024 포터II LPG 출시</t>
+        </is>
+      </c>
+      <c r="P383" s="2" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -24433,14 +24457,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G384" s="8" t="inlineStr">
-        <is>
-          <t>ID46[폴딩키], 확인 불가[스마트키]</t>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr">
         <is>
-          <t>막대키,폴딩키,스마트키</t>
+          <t>막대키,폴딩키</t>
         </is>
       </c>
       <c r="I384" s="2" t="inlineStr">
@@ -24450,27 +24474,23 @@
       </c>
       <c r="J384" s="2" t="n"/>
       <c r="K384" s="2" t="n"/>
-      <c r="L384" s="2" t="inlineStr">
-        <is>
-          <t>95440-4FGA0</t>
-        </is>
-      </c>
+      <c r="L384" s="2" t="n"/>
       <c r="M384" s="2" t="inlineStr">
         <is>
           <t>95430-4F500</t>
         </is>
       </c>
-      <c r="N384" s="8" t="n"/>
+      <c r="N384" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000, 95420-4F500</t>
+        </is>
+      </c>
       <c r="O384" s="2" t="inlineStr">
         <is>
-          <t>원본</t>
-        </is>
-      </c>
-      <c r="P384" s="8" t="inlineStr">
-        <is>
-          <t>스마트키(95440-4FGA0) 칩 원문 없음</t>
-        </is>
-      </c>
+          <t>partsro 95420D4000, partsro 954204F500, cvinfo 2024 포터II LPG 출시</t>
+        </is>
+      </c>
+      <c r="P384" s="2" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -24488,14 +24508,14 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D385" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E385" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="D385" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E385" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F385" s="3" t="inlineStr">
@@ -24505,7 +24525,7 @@
       </c>
       <c r="G385" s="8" t="inlineStr">
         <is>
-          <t>ID46[폴딩키], 확인 불가[스마트키]</t>
+          <t>ID46[폴딩키], ID6A[스마트키, 추정]</t>
         </is>
       </c>
       <c r="H385" s="2" t="inlineStr">
@@ -24515,14 +24535,14 @@
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
-          <t>81996-4F700, 81996-4F025, 81996-4F760</t>
+          <t>81996-4F700, 81996-4F025, 81996-4F760, 81996-CN000[스마트키용]</t>
         </is>
       </c>
       <c r="J385" s="2" t="n"/>
       <c r="K385" s="2" t="n"/>
       <c r="L385" s="2" t="inlineStr">
         <is>
-          <t>95440-4FGA0</t>
+          <t>95440-4FGA0[LPG]</t>
         </is>
       </c>
       <c r="M385" s="2" t="inlineStr">
@@ -24530,15 +24550,19 @@
           <t>95430-4F500</t>
         </is>
       </c>
-      <c r="N385" s="8" t="n"/>
+      <c r="N385" s="8" t="inlineStr">
+        <is>
+          <t>95420-D4000, 95420-4F500</t>
+        </is>
+      </c>
       <c r="O385" s="2" t="inlineStr">
         <is>
-          <t>원본</t>
+          <t>cvinfo 2024 포터II, hyundaimotorgroup 2026 포터II, ebay 954404FGA0/81996CN000, 기아 DB 봉고3 2024</t>
         </is>
       </c>
       <c r="P385" s="8" t="inlineStr">
         <is>
-          <t>스마트키(95440-4FGA0) 칩 원문 없음</t>
+          <t>LPG 스마트키(95440-4FGA0) 칩 원문 없음 — 비상키 81996-CN000을 같이 쓰는 포터2 일렉트릭 95440-CN100(AES 6A) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -24558,14 +24582,14 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D386" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E386" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="D386" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E386" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr">
@@ -24575,7 +24599,7 @@
       </c>
       <c r="G386" s="8" t="inlineStr">
         <is>
-          <t>ID46[폴딩키], 확인 불가[스마트키]</t>
+          <t>ID46[폴딩키], ID6A[스마트키, 추정]</t>
         </is>
       </c>
       <c r="H386" s="2" t="inlineStr">
@@ -24585,14 +24609,14 @@
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>81996-4F700, 81996-4F025, 81996-4F760</t>
+          <t>81996-4F700, 81996-4F025, 81996-4F760, 81996-CN000[스마트키용]</t>
         </is>
       </c>
       <c r="J386" s="2" t="n"/>
       <c r="K386" s="2" t="n"/>
       <c r="L386" s="2" t="inlineStr">
         <is>
-          <t>95440-4FGA0</t>
+          <t>95440-4FGA0[LPG]</t>
         </is>
       </c>
       <c r="M386" s="2" t="inlineStr">
@@ -24600,15 +24624,19 @@
           <t>95430-4F500</t>
         </is>
       </c>
-      <c r="N386" s="8" t="n"/>
+      <c r="N386" s="8" t="inlineStr">
+        <is>
+          <t>95420-D4000, 95420-4F500</t>
+        </is>
+      </c>
       <c r="O386" s="2" t="inlineStr">
         <is>
-          <t>원본</t>
+          <t>cvinfo 2024 포터II, hyundaimotorgroup 2026 포터II, ebay 954404FGA0/81996CN000, 기아 DB 봉고3 2024</t>
         </is>
       </c>
       <c r="P386" s="8" t="inlineStr">
         <is>
-          <t>스마트키(95440-4FGA0) 칩 원문 없음</t>
+          <t>LPG 스마트키(95440-4FGA0) 칩 원문 없음 — 비상키 81996-CN000을 같이 쓰는 포터2 일렉트릭 95440-CN100(AES 6A) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -24628,14 +24656,14 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D387" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E387" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="D387" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E387" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F387" s="3" t="inlineStr">
@@ -24645,7 +24673,7 @@
       </c>
       <c r="G387" s="8" t="inlineStr">
         <is>
-          <t>ID46[폴딩키], 확인 불가[스마트키]</t>
+          <t>ID46[폴딩키], ID6A[스마트키, 추정]</t>
         </is>
       </c>
       <c r="H387" s="2" t="inlineStr">
@@ -24655,14 +24683,14 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>81996-4F700, 81996-4F025, 81996-4F760</t>
+          <t>81996-4F700, 81996-4F025, 81996-4F760, 81996-CN000[스마트키용]</t>
         </is>
       </c>
       <c r="J387" s="2" t="n"/>
       <c r="K387" s="2" t="n"/>
       <c r="L387" s="2" t="inlineStr">
         <is>
-          <t>95440-4FGA0</t>
+          <t>95440-4FGA0[LPG]</t>
         </is>
       </c>
       <c r="M387" s="2" t="inlineStr">
@@ -24670,15 +24698,19 @@
           <t>95430-4F500</t>
         </is>
       </c>
-      <c r="N387" s="8" t="n"/>
+      <c r="N387" s="8" t="inlineStr">
+        <is>
+          <t>95420-D4000, 95420-4F500</t>
+        </is>
+      </c>
       <c r="O387" s="2" t="inlineStr">
         <is>
-          <t>원본</t>
+          <t>cvinfo 2024 포터II, hyundaimotorgroup 2026 포터II, ebay 954404FGA0/81996CN000, 기아 DB 봉고3 2024</t>
         </is>
       </c>
       <c r="P387" s="8" t="inlineStr">
         <is>
-          <t>스마트키(95440-4FGA0) 칩 원문 없음</t>
+          <t>LPG 스마트키(95440-4FGA0) 칩 원문 없음 — 비상키 81996-CN000을 같이 쓰는 포터2 일렉트릭 95440-CN100(AES 6A) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -24698,12 +24730,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D388" s="5" t="inlineStr">
+      <c r="D388" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="E388" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -24713,7 +24745,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G388" s="4" t="inlineStr">
+      <c r="G388" s="8" t="inlineStr">
         <is>
           <t>ID6A[추정]</t>
         </is>
@@ -24736,13 +24768,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n"/>
-      <c r="N388" s="4" t="n"/>
+      <c r="N388" s="8" t="n"/>
       <c r="O388" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 포터2 전기차 95440CN000/81996CN000/95440CN100, hyunkimall</t>
-        </is>
-      </c>
-      <c r="P388" s="4" t="inlineStr">
+          <t>hellowcar 포터2 전기차, vvdi 95440-CN100 AES 6A</t>
+        </is>
+      </c>
+      <c r="P388" s="8" t="inlineStr">
         <is>
           <t>95440-CN000 칩 원문 없음 — 후속 CN100(AES 6A) 기준 추정</t>
         </is>
@@ -24764,12 +24796,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D389" s="5" t="inlineStr">
+      <c r="D389" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="E389" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -24779,7 +24811,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G389" s="4" t="inlineStr">
+      <c r="G389" s="8" t="inlineStr">
         <is>
           <t>ID6A[추정]</t>
         </is>
@@ -24802,13 +24834,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n"/>
-      <c r="N389" s="4" t="n"/>
+      <c r="N389" s="8" t="n"/>
       <c r="O389" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
-        </is>
-      </c>
-      <c r="P389" s="4" t="inlineStr">
+          <t>hellowcar 포터2 전기차, vvdi 95440-CN100 AES 6A</t>
+        </is>
+      </c>
+      <c r="P389" s="8" t="inlineStr">
         <is>
           <t>95440-CN000 칩 원문 없음 — 후속 CN100(AES 6A) 기준 추정</t>
         </is>
@@ -24830,12 +24862,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D390" s="5" t="inlineStr">
+      <c r="D390" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="E390" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -24845,7 +24877,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G390" s="4" t="inlineStr">
+      <c r="G390" s="8" t="inlineStr">
         <is>
           <t>ID6A[추정]</t>
         </is>
@@ -24868,13 +24900,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n"/>
-      <c r="N390" s="4" t="n"/>
+      <c r="N390" s="8" t="n"/>
       <c r="O390" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
-        </is>
-      </c>
-      <c r="P390" s="4" t="inlineStr">
+          <t>hellowcar 포터2 전기차, vvdi 95440-CN100 AES 6A</t>
+        </is>
+      </c>
+      <c r="P390" s="8" t="inlineStr">
         <is>
           <t>95440-CN000 칩 원문 없음 — 후속 CN100(AES 6A) 기준 추정</t>
         </is>
@@ -24896,12 +24928,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D391" s="5" t="inlineStr">
+      <c r="D391" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="E391" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -24911,7 +24943,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G391" s="4" t="inlineStr">
+      <c r="G391" s="8" t="inlineStr">
         <is>
           <t>ID6A[추정]</t>
         </is>
@@ -24934,13 +24966,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n"/>
-      <c r="N391" s="4" t="n"/>
+      <c r="N391" s="8" t="n"/>
       <c r="O391" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
-        </is>
-      </c>
-      <c r="P391" s="4" t="inlineStr">
+          <t>hellowcar 포터2 전기차, vvdi 95440-CN100 AES 6A</t>
+        </is>
+      </c>
+      <c r="P391" s="8" t="inlineStr">
         <is>
           <t>95440-CN000 칩 원문 없음 — 후속 CN100(AES 6A) 기준 추정</t>
         </is>
@@ -24962,12 +24994,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D392" s="5" t="inlineStr">
+      <c r="D392" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="E392" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25024,12 +25056,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D393" s="5" t="inlineStr">
+      <c r="D393" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="E393" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25086,12 +25118,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D394" s="5" t="inlineStr">
+      <c r="D394" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="E394" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25148,12 +25180,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D395" s="5" t="inlineStr">
+      <c r="D395" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="E395" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25210,12 +25242,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="D396" s="5" t="inlineStr">
+      <c r="D396" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="E396" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25272,12 +25304,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D397" s="5" t="inlineStr">
+      <c r="D397" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="E397" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25334,12 +25366,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D398" s="5" t="inlineStr">
+      <c r="D398" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="E398" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25396,12 +25428,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D399" s="5" t="inlineStr">
+      <c r="D399" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="E399" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25458,12 +25490,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D400" s="5" t="inlineStr">
+      <c r="D400" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="E400" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25520,12 +25552,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D401" s="5" t="inlineStr">
+      <c r="D401" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="E401" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25578,12 +25610,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D402" s="5" t="inlineStr">
+      <c r="D402" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="E402" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25636,12 +25668,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D403" s="5" t="inlineStr">
+      <c r="D403" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="E403" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25694,12 +25726,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D404" s="5" t="inlineStr">
+      <c r="D404" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="E404" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25752,12 +25784,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D405" s="5" t="inlineStr">
+      <c r="D405" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="E405" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25810,12 +25842,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D406" s="5" t="inlineStr">
+      <c r="D406" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="E406" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25868,12 +25900,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D407" s="5" t="inlineStr">
+      <c r="D407" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="E407" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25926,12 +25958,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D408" s="5" t="inlineStr">
+      <c r="D408" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="E408" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -25984,12 +26016,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D409" s="5" t="inlineStr">
+      <c r="D409" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="E409" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26042,12 +26074,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D410" s="5" t="inlineStr">
+      <c r="D410" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="E410" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26100,12 +26132,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D411" s="5" t="inlineStr">
+      <c r="D411" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="E411" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26115,7 +26147,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G411" s="4" t="inlineStr">
+      <c r="G411" s="8" t="inlineStr">
         <is>
           <t>ID4A[추정]</t>
         </is>
@@ -26130,15 +26162,15 @@
       <c r="K411" s="2" t="n"/>
       <c r="L411" s="2" t="n"/>
       <c r="M411" s="2" t="n"/>
-      <c r="N411" s="4" t="n"/>
+      <c r="N411" s="8" t="n"/>
       <c r="O411" s="2" t="inlineStr">
         <is>
-          <t>abkeys T1BB0</t>
-        </is>
-      </c>
-      <c r="P411" s="4" t="inlineStr">
-        <is>
-          <t>부분변경 전용 스마트키 품번·칩 원문 없음 — G80 부분변경(ID4A) 기준 추정</t>
+          <t>eacar 2024 G80 일렉트리파이드 부분변경, partsro 95440T1210 전기차 공용</t>
+        </is>
+      </c>
+      <c r="P411" s="8" t="inlineStr">
+        <is>
+          <t>부분변경 스마트키 품번·칩 원문 없음(모비스 목록의 전기차 공용 95440-T1210은 부분변경 이전 키) — G80 부분변경(ID4A) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -26158,12 +26190,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D412" s="5" t="inlineStr">
+      <c r="D412" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="E412" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26173,7 +26205,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G412" s="4" t="inlineStr">
+      <c r="G412" s="8" t="inlineStr">
         <is>
           <t>ID4A[추정]</t>
         </is>
@@ -26188,15 +26220,15 @@
       <c r="K412" s="2" t="n"/>
       <c r="L412" s="2" t="n"/>
       <c r="M412" s="2" t="n"/>
-      <c r="N412" s="4" t="n"/>
+      <c r="N412" s="8" t="n"/>
       <c r="O412" s="2" t="inlineStr">
         <is>
-          <t>abkeys</t>
-        </is>
-      </c>
-      <c r="P412" s="4" t="inlineStr">
-        <is>
-          <t>부분변경 전용 스마트키 품번·칩 원문 없음 — G80 부분변경(ID4A) 기준 추정</t>
+          <t>eacar 2024 G80 일렉트리파이드 부분변경, partsro 95440T1210 전기차 공용</t>
+        </is>
+      </c>
+      <c r="P412" s="8" t="inlineStr">
+        <is>
+          <t>부분변경 스마트키 품번·칩 원문 없음(모비스 목록의 전기차 공용 95440-T1210은 부분변경 이전 키) — G80 부분변경(ID4A) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -26216,12 +26248,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D413" s="5" t="inlineStr">
+      <c r="D413" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="E413" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26231,7 +26263,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G413" s="4" t="inlineStr">
+      <c r="G413" s="8" t="inlineStr">
         <is>
           <t>ID4A[추정]</t>
         </is>
@@ -26246,15 +26278,15 @@
       <c r="K413" s="2" t="n"/>
       <c r="L413" s="2" t="n"/>
       <c r="M413" s="2" t="n"/>
-      <c r="N413" s="4" t="n"/>
+      <c r="N413" s="8" t="n"/>
       <c r="O413" s="2" t="inlineStr">
         <is>
-          <t>abkeys</t>
-        </is>
-      </c>
-      <c r="P413" s="4" t="inlineStr">
-        <is>
-          <t>부분변경 전용 스마트키 품번·칩 원문 없음 — G80 부분변경(ID4A) 기준 추정</t>
+          <t>eacar 2024 G80 일렉트리파이드 부분변경, partsro 95440T1210 전기차 공용</t>
+        </is>
+      </c>
+      <c r="P413" s="8" t="inlineStr">
+        <is>
+          <t>부분변경 스마트키 품번·칩 원문 없음(모비스 목록의 전기차 공용 95440-T1210은 부분변경 이전 키) — G80 부분변경(ID4A) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -26274,12 +26306,12 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="D414" s="5" t="inlineStr">
+      <c r="D414" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="E414" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26332,12 +26364,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="D415" s="5" t="inlineStr">
+      <c r="D415" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="E415" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26390,12 +26422,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D416" s="5" t="inlineStr">
+      <c r="D416" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E416" s="6" t="inlineStr">
+      <c r="E416" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26448,12 +26480,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D417" s="5" t="inlineStr">
+      <c r="D417" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E417" s="6" t="inlineStr">
+      <c r="E417" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26506,12 +26538,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D418" s="5" t="inlineStr">
+      <c r="D418" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E418" s="6" t="inlineStr">
+      <c r="E418" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26564,12 +26596,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D419" s="5" t="inlineStr">
+      <c r="D419" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E419" s="6" t="inlineStr">
+      <c r="E419" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26622,12 +26654,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D420" s="5" t="inlineStr">
+      <c r="D420" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E420" s="6" t="inlineStr">
+      <c r="E420" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26680,12 +26712,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D421" s="5" t="inlineStr">
+      <c r="D421" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E421" s="6" t="inlineStr">
+      <c r="E421" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26738,12 +26770,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D422" s="5" t="inlineStr">
+      <c r="D422" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E422" s="6" t="inlineStr">
+      <c r="E422" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26796,12 +26828,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D423" s="5" t="inlineStr">
+      <c r="D423" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E423" s="6" t="inlineStr">
+      <c r="E423" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26854,12 +26886,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D424" s="5" t="inlineStr">
+      <c r="D424" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E424" s="6" t="inlineStr">
+      <c r="E424" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26912,12 +26944,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D425" s="5" t="inlineStr">
+      <c r="D425" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E425" s="6" t="inlineStr">
+      <c r="E425" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -26970,12 +27002,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D426" s="5" t="inlineStr">
+      <c r="D426" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E426" s="6" t="inlineStr">
+      <c r="E426" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27028,12 +27060,12 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D427" s="5" t="inlineStr">
+      <c r="D427" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E427" s="6" t="inlineStr">
+      <c r="E427" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27090,12 +27122,12 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D428" s="5" t="inlineStr">
+      <c r="D428" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E428" s="6" t="inlineStr">
+      <c r="E428" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27152,12 +27184,12 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D429" s="5" t="inlineStr">
+      <c r="D429" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E429" s="6" t="inlineStr">
+      <c r="E429" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27214,12 +27246,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D430" s="5" t="inlineStr">
+      <c r="D430" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E430" s="6" t="inlineStr">
+      <c r="E430" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27276,12 +27308,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D431" s="5" t="inlineStr">
+      <c r="D431" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E431" s="6" t="inlineStr">
+      <c r="E431" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27338,12 +27370,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D432" s="5" t="inlineStr">
+      <c r="D432" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E432" s="6" t="inlineStr">
+      <c r="E432" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27400,12 +27432,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D433" s="5" t="inlineStr">
+      <c r="D433" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E433" s="6" t="inlineStr">
+      <c r="E433" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27462,12 +27494,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D434" s="5" t="inlineStr">
+      <c r="D434" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E434" s="6" t="inlineStr">
+      <c r="E434" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27520,12 +27552,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D435" s="5" t="inlineStr">
+      <c r="D435" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E435" s="6" t="inlineStr">
+      <c r="E435" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27578,12 +27610,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D436" s="5" t="inlineStr">
+      <c r="D436" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E436" s="6" t="inlineStr">
+      <c r="E436" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27636,12 +27668,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D437" s="5" t="inlineStr">
+      <c r="D437" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E437" s="6" t="inlineStr">
+      <c r="E437" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27698,12 +27730,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D438" s="5" t="inlineStr">
+      <c r="D438" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E438" s="6" t="inlineStr">
+      <c r="E438" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27760,12 +27792,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D439" s="5" t="inlineStr">
+      <c r="D439" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E439" s="6" t="inlineStr">
+      <c r="E439" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27822,12 +27854,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D440" s="5" t="inlineStr">
+      <c r="D440" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E440" s="6" t="inlineStr">
+      <c r="E440" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27884,12 +27916,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D441" s="5" t="inlineStr">
+      <c r="D441" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E441" s="6" t="inlineStr">
+      <c r="E441" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27906,26 +27938,30 @@
       </c>
       <c r="H441" s="2" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>스마트키,카드키</t>
         </is>
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>81996-T6000</t>
+          <t>81996-T6500, 81995-T6000</t>
         </is>
       </c>
       <c r="J441" s="2" t="n"/>
-      <c r="K441" s="2" t="n"/>
+      <c r="K441" s="2" t="inlineStr">
+        <is>
+          <t>95440-T6CA0, 95440-T6CB0</t>
+        </is>
+      </c>
       <c r="L441" s="2" t="inlineStr">
         <is>
-          <t>95440-T6AA0[7버튼], 95440-T6BA0[5버튼], 95440-T6DA0[5버튼], 95440-T6DB0[5버튼]</t>
+          <t>95440-T6AA0[7버튼], 95440-T6AB0, 95440-T6AC0[블랙 패키지], 95440-T6BA0[5버튼], 95440-T6BB0, 95440-T6DA0[5버튼], 95440-T6DB0[5버튼]</t>
         </is>
       </c>
       <c r="M441" s="2" t="n"/>
       <c r="N441" s="2" t="n"/>
       <c r="O441" s="2" t="inlineStr">
         <is>
-          <t>bestkeysupply T6AA0 ID4A, keyinnovations T6BA0 ID4A, uhs-hardware T6DB0</t>
+          <t>hellowcar 제네시스GV80페이스리프트</t>
         </is>
       </c>
       <c r="P441" s="2" t="n"/>
@@ -27946,12 +27982,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D442" s="5" t="inlineStr">
+      <c r="D442" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E442" s="6" t="inlineStr">
+      <c r="E442" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -27968,26 +28004,30 @@
       </c>
       <c r="H442" s="2" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>스마트키,카드키</t>
         </is>
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>81996-T6000</t>
+          <t>81996-T6500, 81995-T6000</t>
         </is>
       </c>
       <c r="J442" s="2" t="n"/>
-      <c r="K442" s="2" t="n"/>
+      <c r="K442" s="2" t="inlineStr">
+        <is>
+          <t>95440-T6CA0, 95440-T6CB0</t>
+        </is>
+      </c>
       <c r="L442" s="2" t="inlineStr">
         <is>
-          <t>95440-T6AA0[7버튼], 95440-T6BA0[5버튼], 95440-T6DA0[5버튼], 95440-T6DB0[5버튼]</t>
+          <t>95440-T6AA0[7버튼], 95440-T6AB0, 95440-T6AC0[블랙 패키지], 95440-T6BA0[5버튼], 95440-T6BB0, 95440-T6DA0[5버튼], 95440-T6DB0[5버튼]</t>
         </is>
       </c>
       <c r="M442" s="2" t="n"/>
       <c r="N442" s="2" t="n"/>
       <c r="O442" s="2" t="inlineStr">
         <is>
-          <t>transponderisland 2024-2025 T6DB0</t>
+          <t>hellowcar 제네시스GV80페이스리프트</t>
         </is>
       </c>
       <c r="P442" s="2" t="n"/>
@@ -28008,12 +28048,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D443" s="5" t="inlineStr">
+      <c r="D443" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E443" s="6" t="inlineStr">
+      <c r="E443" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28030,26 +28070,30 @@
       </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>스마트키,카드키</t>
         </is>
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>81996-T6000</t>
+          <t>81996-T6500, 81995-T6000</t>
         </is>
       </c>
       <c r="J443" s="2" t="n"/>
-      <c r="K443" s="2" t="n"/>
+      <c r="K443" s="2" t="inlineStr">
+        <is>
+          <t>95440-T6CA0, 95440-T6CB0</t>
+        </is>
+      </c>
       <c r="L443" s="2" t="inlineStr">
         <is>
-          <t>95440-T6AA0[7버튼], 95440-T6BA0[5버튼], 95440-T6DA0[5버튼], 95440-T6DB0[5버튼]</t>
+          <t>95440-T6AA0[7버튼], 95440-T6AB0, 95440-T6AC0[블랙 패키지], 95440-T6BA0[5버튼], 95440-T6BB0, 95440-T6DA0[5버튼], 95440-T6DB0[5버튼]</t>
         </is>
       </c>
       <c r="M443" s="2" t="n"/>
       <c r="N443" s="2" t="n"/>
       <c r="O443" s="2" t="inlineStr">
         <is>
-          <t>yourcarkeyguys 2024-2026 T6AA0, sffobsinc T6DA0</t>
+          <t>hellowcar 제네시스GV80페이스리프트</t>
         </is>
       </c>
       <c r="P443" s="2" t="n"/>
@@ -28070,12 +28114,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D444" s="5" t="inlineStr">
+      <c r="D444" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E444" s="6" t="inlineStr">
+      <c r="E444" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28085,32 +28129,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G444" s="4" t="inlineStr">
-        <is>
-          <t>ID4A[추정]</t>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I444" s="2" t="n"/>
+          <t>스마트키,카드키</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>81996-T6500, 81995-T6000</t>
+        </is>
+      </c>
       <c r="J444" s="2" t="n"/>
-      <c r="K444" s="2" t="n"/>
-      <c r="L444" s="2" t="n"/>
+      <c r="K444" s="2" t="inlineStr">
+        <is>
+          <t>95440-T6CA0, 95440-T6CB0</t>
+        </is>
+      </c>
+      <c r="L444" s="2" t="inlineStr">
+        <is>
+          <t>95440-T6AA0[7버튼], 95440-T6AB0, 95440-T6BA0, 95440-T6BB0[5버튼]</t>
+        </is>
+      </c>
       <c r="M444" s="2" t="n"/>
-      <c r="N444" s="4" t="n"/>
+      <c r="N444" s="2" t="n"/>
       <c r="O444" s="2" t="inlineStr">
         <is>
-          <t>bestkeysupply T6AA0 2024-2026</t>
-        </is>
-      </c>
-      <c r="P444" s="4" t="inlineStr">
-        <is>
-          <t>쿠페 전용 스마트키 품번·칩 원문 없음 — GV80 부분변경(ID4A) 기준 추정</t>
-        </is>
-      </c>
+          <t>검색요약 T6AA0 GV80 Coupe 4A, hellowcar 제네시스GV80페이스리프트, uhs-hardware T6AB0</t>
+        </is>
+      </c>
+      <c r="P444" s="2" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -28128,12 +28180,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D445" s="5" t="inlineStr">
+      <c r="D445" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E445" s="6" t="inlineStr">
+      <c r="E445" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28143,32 +28195,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G445" s="4" t="inlineStr">
-        <is>
-          <t>ID4A[추정]</t>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I445" s="2" t="n"/>
+          <t>스마트키,카드키</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>81996-T6500, 81995-T6000</t>
+        </is>
+      </c>
       <c r="J445" s="2" t="n"/>
-      <c r="K445" s="2" t="n"/>
-      <c r="L445" s="2" t="n"/>
+      <c r="K445" s="2" t="inlineStr">
+        <is>
+          <t>95440-T6CA0, 95440-T6CB0</t>
+        </is>
+      </c>
+      <c r="L445" s="2" t="inlineStr">
+        <is>
+          <t>95440-T6AA0[7버튼], 95440-T6AB0, 95440-T6BA0, 95440-T6BB0[5버튼]</t>
+        </is>
+      </c>
       <c r="M445" s="2" t="n"/>
-      <c r="N445" s="4" t="n"/>
+      <c r="N445" s="2" t="n"/>
       <c r="O445" s="2" t="inlineStr">
         <is>
-          <t>bestkeysupply</t>
-        </is>
-      </c>
-      <c r="P445" s="4" t="inlineStr">
-        <is>
-          <t>쿠페 전용 스마트키 품번·칩 원문 없음 — GV80 부분변경(ID4A) 기준 추정</t>
-        </is>
-      </c>
+          <t>검색요약 T6AA0 GV80 Coupe 4A, hellowcar 제네시스GV80페이스리프트, uhs-hardware T6AB0</t>
+        </is>
+      </c>
+      <c r="P445" s="2" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -28186,12 +28246,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D446" s="5" t="inlineStr">
+      <c r="D446" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E446" s="6" t="inlineStr">
+      <c r="E446" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28201,32 +28261,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G446" s="4" t="inlineStr">
-        <is>
-          <t>ID4A[추정]</t>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I446" s="2" t="n"/>
+          <t>스마트키,카드키</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="inlineStr">
+        <is>
+          <t>81996-T6500, 81995-T6000</t>
+        </is>
+      </c>
       <c r="J446" s="2" t="n"/>
-      <c r="K446" s="2" t="n"/>
-      <c r="L446" s="2" t="n"/>
+      <c r="K446" s="2" t="inlineStr">
+        <is>
+          <t>95440-T6CA0, 95440-T6CB0</t>
+        </is>
+      </c>
+      <c r="L446" s="2" t="inlineStr">
+        <is>
+          <t>95440-T6AA0[7버튼], 95440-T6AB0, 95440-T6BA0, 95440-T6BB0[5버튼]</t>
+        </is>
+      </c>
       <c r="M446" s="2" t="n"/>
-      <c r="N446" s="4" t="n"/>
+      <c r="N446" s="2" t="n"/>
       <c r="O446" s="2" t="inlineStr">
         <is>
-          <t>bestkeysupply</t>
-        </is>
-      </c>
-      <c r="P446" s="4" t="inlineStr">
-        <is>
-          <t>쿠페 전용 스마트키 품번·칩 원문 없음 — GV80 부분변경(ID4A) 기준 추정</t>
-        </is>
-      </c>
+          <t>검색요약 T6AA0 GV80 Coupe 4A, hellowcar 제네시스GV80페이스리프트, uhs-hardware T6AB0</t>
+        </is>
+      </c>
+      <c r="P446" s="2" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -28244,12 +28312,12 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D447" s="5" t="inlineStr">
+      <c r="D447" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E447" s="6" t="inlineStr">
+      <c r="E447" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28302,12 +28370,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D448" s="5" t="inlineStr">
+      <c r="D448" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E448" s="6" t="inlineStr">
+      <c r="E448" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28360,12 +28428,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D449" s="5" t="inlineStr">
+      <c r="D449" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E449" s="6" t="inlineStr">
+      <c r="E449" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28418,12 +28486,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D450" s="5" t="inlineStr">
+      <c r="D450" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E450" s="6" t="inlineStr">
+      <c r="E450" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28476,12 +28544,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D451" s="5" t="inlineStr">
+      <c r="D451" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E451" s="6" t="inlineStr">
+      <c r="E451" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28534,12 +28602,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D452" s="5" t="inlineStr">
+      <c r="D452" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E452" s="6" t="inlineStr">
+      <c r="E452" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28559,19 +28627,23 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I452" s="2" t="n"/>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>81996-T6500, 81995-T6000</t>
+        </is>
+      </c>
       <c r="J452" s="2" t="n"/>
       <c r="K452" s="2" t="n"/>
       <c r="L452" s="2" t="inlineStr">
         <is>
-          <t>95440-ARAA0[5버튼], 95440-ARAB0[5버튼], 95440-ARDA0[7버튼]</t>
+          <t>95440-ARAA0[5버튼], 95440-ARAB0[5버튼], 95440-ARBA0, 95440-ARBB0, 95440-ARDA0[7버튼], 95440-ARDB0</t>
         </is>
       </c>
       <c r="M452" s="2" t="n"/>
       <c r="N452" s="2" t="n"/>
       <c r="O452" s="2" t="inlineStr">
         <is>
-          <t>bestkeysupply ARAA0 4A, royalkeysupply ARDA0, sffobsinc ARAB0</t>
+          <t>hellowcar 제네시스GV70 페이스리프트</t>
         </is>
       </c>
       <c r="P452" s="2" t="n"/>
@@ -28592,12 +28664,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D453" s="5" t="inlineStr">
+      <c r="D453" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E453" s="6" t="inlineStr">
+      <c r="E453" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28617,19 +28689,23 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I453" s="2" t="n"/>
+      <c r="I453" s="2" t="inlineStr">
+        <is>
+          <t>81996-T6500, 81995-T6000</t>
+        </is>
+      </c>
       <c r="J453" s="2" t="n"/>
       <c r="K453" s="2" t="n"/>
       <c r="L453" s="2" t="inlineStr">
         <is>
-          <t>95440-ARAA0[5버튼], 95440-ARAB0[5버튼], 95440-ARDA0[7버튼]</t>
+          <t>95440-ARAA0[5버튼], 95440-ARAB0[5버튼], 95440-ARBA0, 95440-ARBB0, 95440-ARDA0[7버튼], 95440-ARDB0</t>
         </is>
       </c>
       <c r="M453" s="2" t="n"/>
       <c r="N453" s="2" t="n"/>
       <c r="O453" s="2" t="inlineStr">
         <is>
-          <t>bestkeysupply 2025-2026</t>
+          <t>hellowcar 제네시스GV70 페이스리프트</t>
         </is>
       </c>
       <c r="P453" s="2" t="n"/>
@@ -28650,12 +28726,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D454" s="5" t="inlineStr">
+      <c r="D454" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E454" s="6" t="inlineStr">
+      <c r="E454" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28665,9 +28741,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G454" s="4" t="inlineStr">
-        <is>
-          <t>ID47[추정]</t>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
@@ -28678,19 +28754,19 @@
       <c r="I454" s="2" t="n"/>
       <c r="J454" s="2" t="n"/>
       <c r="K454" s="2" t="n"/>
-      <c r="L454" s="2" t="n"/>
+      <c r="L454" s="2" t="inlineStr">
+        <is>
+          <t>95440-DS000, 95440-DS010[8버튼]</t>
+        </is>
+      </c>
       <c r="M454" s="2" t="n"/>
-      <c r="N454" s="4" t="n"/>
+      <c r="N454" s="2" t="n"/>
       <c r="O454" s="2" t="inlineStr">
         <is>
-          <t>transponderisland 2022-2025 AR001</t>
-        </is>
-      </c>
-      <c r="P454" s="4" t="inlineStr">
-        <is>
-          <t>EV 전용 스마트키 품번·칩 원문 없음 — GV70(ID47) 기준 추정</t>
-        </is>
-      </c>
+          <t>remotesandkeys 2023 GV70 Electrified DS010 ID47, transponderisland 2023-2025 DS010, noblekeysupply DS000</t>
+        </is>
+      </c>
+      <c r="P454" s="2" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -28708,12 +28784,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D455" s="5" t="inlineStr">
+      <c r="D455" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E455" s="6" t="inlineStr">
+      <c r="E455" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28723,9 +28799,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G455" s="4" t="inlineStr">
-        <is>
-          <t>ID47[추정]</t>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -28736,19 +28812,19 @@
       <c r="I455" s="2" t="n"/>
       <c r="J455" s="2" t="n"/>
       <c r="K455" s="2" t="n"/>
-      <c r="L455" s="2" t="n"/>
+      <c r="L455" s="2" t="inlineStr">
+        <is>
+          <t>95440-DS000, 95440-DS010[8버튼]</t>
+        </is>
+      </c>
       <c r="M455" s="2" t="n"/>
-      <c r="N455" s="4" t="n"/>
+      <c r="N455" s="2" t="n"/>
       <c r="O455" s="2" t="inlineStr">
         <is>
-          <t>transponderisland</t>
-        </is>
-      </c>
-      <c r="P455" s="4" t="inlineStr">
-        <is>
-          <t>EV 전용 스마트키 품번·칩 원문 없음 — GV70(ID47) 기준 추정</t>
-        </is>
-      </c>
+          <t>remotesandkeys 2023 GV70 Electrified DS010 ID47, transponderisland 2023-2025 DS010, noblekeysupply DS000</t>
+        </is>
+      </c>
+      <c r="P455" s="2" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -28766,12 +28842,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D456" s="5" t="inlineStr">
+      <c r="D456" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E456" s="6" t="inlineStr">
+      <c r="E456" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28781,9 +28857,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G456" s="4" t="inlineStr">
-        <is>
-          <t>ID47[추정]</t>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -28794,19 +28870,19 @@
       <c r="I456" s="2" t="n"/>
       <c r="J456" s="2" t="n"/>
       <c r="K456" s="2" t="n"/>
-      <c r="L456" s="2" t="n"/>
+      <c r="L456" s="2" t="inlineStr">
+        <is>
+          <t>95440-DS000, 95440-DS010[8버튼]</t>
+        </is>
+      </c>
       <c r="M456" s="2" t="n"/>
-      <c r="N456" s="4" t="n"/>
+      <c r="N456" s="2" t="n"/>
       <c r="O456" s="2" t="inlineStr">
         <is>
-          <t>transponderisland</t>
-        </is>
-      </c>
-      <c r="P456" s="4" t="inlineStr">
-        <is>
-          <t>EV 전용 스마트키 품번·칩 원문 없음 — GV70(ID47) 기준 추정</t>
-        </is>
-      </c>
+          <t>remotesandkeys 2023 GV70 Electrified DS010 ID47, transponderisland 2023-2025 DS010, noblekeysupply DS000</t>
+        </is>
+      </c>
+      <c r="P456" s="2" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -28824,12 +28900,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D457" s="5" t="inlineStr">
+      <c r="D457" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E457" s="6" t="inlineStr">
+      <c r="E457" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28839,30 +28915,38 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G457" s="4" t="inlineStr">
-        <is>
-          <t>ID4A[추정]</t>
+      <c r="G457" s="8" t="inlineStr">
+        <is>
+          <t>ID47[95440-DS010 키, ~2025.1], ID4A[부분변경, 추정]</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>스마트키,카드키</t>
         </is>
       </c>
       <c r="I457" s="2" t="n"/>
       <c r="J457" s="2" t="n"/>
-      <c r="K457" s="2" t="n"/>
-      <c r="L457" s="2" t="n"/>
+      <c r="K457" s="2" t="inlineStr">
+        <is>
+          <t>95440-DSBA0, 95440-DSBB0, 95440-DSDA0, 95440-DSDB0</t>
+        </is>
+      </c>
+      <c r="L457" s="2" t="inlineStr">
+        <is>
+          <t>95440-DS010[~2025.1]</t>
+        </is>
+      </c>
       <c r="M457" s="2" t="n"/>
-      <c r="N457" s="4" t="n"/>
+      <c r="N457" s="8" t="n"/>
       <c r="O457" s="2" t="inlineStr">
         <is>
-          <t>bestkeysupply 2025-2026 ARAA0</t>
-        </is>
-      </c>
-      <c r="P457" s="4" t="inlineStr">
-        <is>
-          <t>EV 부분변경 전용 스마트키 품번·칩 원문 없음 — GV70 부분변경(ID4A) 기준 추정</t>
+          <t>hyundaimotorgroup GV70 전동화 부분변경 출시, shop.genesis.com Electrified GV70 스마트 카드 키</t>
+        </is>
+      </c>
+      <c r="P457" s="8" t="inlineStr">
+        <is>
+          <t>부분변경(2025.1) 스마트키 품번·칩 원문 없음 — GV70 부분변경(ID4A) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -28882,12 +28966,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D458" s="5" t="inlineStr">
+      <c r="D458" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E458" s="6" t="inlineStr">
+      <c r="E458" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28897,30 +28981,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G458" s="4" t="inlineStr">
+      <c r="G458" s="8" t="inlineStr">
         <is>
           <t>ID4A[추정]</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>스마트키,카드키</t>
         </is>
       </c>
       <c r="I458" s="2" t="n"/>
       <c r="J458" s="2" t="n"/>
-      <c r="K458" s="2" t="n"/>
+      <c r="K458" s="2" t="inlineStr">
+        <is>
+          <t>95440-DSBA0, 95440-DSBB0, 95440-DSDA0, 95440-DSDB0</t>
+        </is>
+      </c>
       <c r="L458" s="2" t="n"/>
       <c r="M458" s="2" t="n"/>
-      <c r="N458" s="4" t="n"/>
+      <c r="N458" s="8" t="n"/>
       <c r="O458" s="2" t="inlineStr">
         <is>
-          <t>bestkeysupply</t>
-        </is>
-      </c>
-      <c r="P458" s="4" t="inlineStr">
-        <is>
-          <t>EV 부분변경 전용 스마트키 품번·칩 원문 없음 — GV70 부분변경(ID4A) 기준 추정</t>
+          <t>hyundaimotorgroup GV70 전동화 부분변경 출시, shop.genesis.com Electrified GV70 스마트 카드 키</t>
+        </is>
+      </c>
+      <c r="P458" s="8" t="inlineStr">
+        <is>
+          <t>부분변경 스마트키 품번·칩 원문 없음 — GV70 부분변경(ID4A) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -28940,12 +29028,12 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D459" s="5" t="inlineStr">
+      <c r="D459" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E459" s="6" t="inlineStr">
+      <c r="E459" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -28998,12 +29086,12 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D460" s="5" t="inlineStr">
+      <c r="D460" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E460" s="6" t="inlineStr">
+      <c r="E460" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -29056,12 +29144,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D461" s="5" t="inlineStr">
+      <c r="D461" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E461" s="6" t="inlineStr">
+      <c r="E461" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -29114,12 +29202,12 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D462" s="5" t="inlineStr">
+      <c r="D462" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E462" s="6" t="inlineStr">
+      <c r="E462" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -29172,12 +29260,12 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D463" s="5" t="inlineStr">
+      <c r="D463" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E463" s="6" t="inlineStr">
+      <c r="E463" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -29230,12 +29318,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D464" s="5" t="inlineStr">
+      <c r="D464" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E464" s="6" t="inlineStr">
+      <c r="E464" s="5" t="inlineStr">
         <is>
           <t>△</t>
         </is>
@@ -29245,7 +29333,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G464" s="4" t="inlineStr">
+      <c r="G464" s="8" t="inlineStr">
         <is>
           <t>ID4A[추정]</t>
         </is>
@@ -29264,13 +29352,13 @@
         </is>
       </c>
       <c r="M464" s="2" t="n"/>
-      <c r="N464" s="4" t="n"/>
+      <c r="N464" s="8" t="n"/>
       <c r="O464" s="2" t="inlineStr">
         <is>
           <t>royalkeysupply 2026 GV60 CU260</t>
         </is>
       </c>
-      <c r="P464" s="4" t="inlineStr">
+      <c r="P464" s="8" t="inlineStr">
         <is>
           <t>부분변경 스마트키(95440-CU260) 칩 원문 없음 — 같은 키 모델(FCC TQ8-FOB-4F75M44)을 쓰는 G70·GV80 부분변경 ID4A 기준 추정</t>
         </is>
@@ -29288,7 +29376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -29363,7 +29451,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>- '이모빌라이저 시스템' 칸은 현대 차종별 이모빌라이저 모듈 자료를 찾지 못해 비웠습니다.</t>
+          <t>- '이모빌라이저 시스템' 칸은 현대모비스 품번이 확인된 차종만 적었습니다(그랜드 스타렉스·포터2 이모빌라이저 모듈 95420-D4000·95420-4F500, 포터2 안테나 95440-4F100).</t>
         </is>
       </c>
     </row>
@@ -29401,276 +29489,318 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>- 빨간색: 확인 불가 — 국내 이모빌라이저 적용 여부나 칩을 자료로 확인하지 못함(베르나 LC·MC, 아반떼 J2, 포터2 스마트키).</t>
+          <t>- 빨간색: 확인 불가 — 아반떼 J2(2000) 1행.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>- 전환 연식은 칩코드 칸에 전·후를 함께 적었습니다(예: 쏘나타 DN8 2023 = ID47(NCF29A1X)[~2023.2], ID4A(NCF29A1M)[디 엣지, 2023.3~]).</t>
+          <t>- 주황색으로 남은 행(재조사 후 23행): 부분변경 신형 스마트키 칩 원문이 아직 없는 경우(아이오닉6 2025~, 일렉트리파이드 G80 2024~, 일렉트리파이드 GV70 2025~, GV60 2026, 포터2 LPG 스마트키, 포터2 일렉트릭 CN000), 스타렉스 2004-2005(순정 4D60 키 vs 해외 카탈로그 4C), 베르나 LC(이모빌라이저키 품번이 없어 미적용 추정).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
+          <t>- 전환 연식은 칩코드 칸에 전·후를 함께 적었습니다(예: 쏘나타 DN8 2023 = ID47(NCF29A1X)[~2023.2], ID4A(NCF29A1M)[디 엣지, 2023.3~]).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
           <t>- 칩코드 추가 뜻: ID4C = Texas 4C(고정 코드, 스타렉스 2004-2006 해외 자료), 해당 없음 = 그 연식 국내형에 이모빌라이저가 없음.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>※ 예전 현대 파일에서 바로잡은 주요 오류</t>
-        </is>
-      </c>
+      <c r="A21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>- 쏘나타 LF(2014-2019): ID47 → ID8A(DST-AES). 95440-C1001·C1500 모두 8A.</t>
+          <t>※ 예전 현대 파일에서 바로잡은 주요 오류</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>- 쏘나타 DN8 2019-2022: ID4A → ID47(NCF29A1X). ID4A는 디 엣지(2023.3~)부터.</t>
+          <t>- 쏘나타 LF(2014-2019): ID47 → ID8A(DST-AES). 95440-C1001·C1500 모두 8A.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>- 아반떼 AD(2015-2020): ID47 → ID8A. 아반떼 CN7(2020-2022): ID4A → ID6A(DST-AES). 더 뉴 아반떼(2023.3~)는 6A·4A 표기가 상충해 주황색.</t>
+          <t>- 쏘나타 DN8 2019-2022: ID4A → ID47(NCF29A1X). ID4A는 디 엣지(2023.3~)부터.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>- 그랜저 GN7: 스마트키 품번 95440-BY000 → 95440-N1xxx(N1000·N1050·N1110 등).</t>
+          <t>- 아반떼 AD(2015-2020): ID47 → ID8A. 아반떼 CN7·아반떼 N·아이오닉6: ID4A → ID6A. 더 뉴 아반떼(95440-AA500)·아이오닉6(KL000)은 FCC NYOMBEC7FOB2208(MBEC 계열 = CN7 AA000·캐스퍼와 같은 6A 계열)이고 auto-keys·keyshop-online·abkeys가 6A로 일치. 일부 판매처(remotesandkeys)의 '4A' 표기는 같은 키를 4A·6A로 섞어 적어 따르지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>- 제네시스 DH 2013-2014: 'BH 전자장비 유지, ID46(95440-3M220)' → DH는 출시(2013.11)부터 95440-B1200BLH ID47. 95440-3M220은 미국형 315MHz.</t>
+          <t>- 투싼 NX4 부분변경(더 뉴 투싼, 2023.11~): 스마트키가 95440-N95xx(ID4A)로 바뀜 — 처음 작성 때 ID47로 잘못 이어 적었던 것을 정정.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>- 제네시스 BH: 95440-3M220(미국형) → 국내 95440-3M010·3M020·3M030. 제네시스 쿠페: 95440-2M350·2M300·3V021(미국형) → 국내 95440-2M050·2M420.</t>
+          <t>- 그랜저 GN7: 스마트키 품번 95440-BY000 → 95440-N1xxx(N1000·N1050·N1110 등).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>- 싼타페 DM 2016-2018·맥스크루즈 2016-2019: 'ID46 또는 ID47' → ID46(95440-2W500·B8100 모두 PCF7952A). 싼타페 DM 95440-4Z200은 미국형.</t>
+          <t>- 제네시스 DH 2013-2014: 'BH 전자장비 유지, ID46(95440-3M220)' → DH는 출시(2013.11)부터 95440-B1200BLH ID47. 95440-3M220은 미국형 315MHz.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>- 싼타페 SM 2000-2002: 4D60 → 국내 이모빌라이저는 2005년형(2004.8.11)부터 적용, 그 이전은 해당 없음.</t>
+          <t>- 제네시스 BH: 95440-3M220(미국형) → 국내 95440-3M010·3M020·3M030. 제네시스 쿠페: 95440-2M350·2M300·3V021(미국형) → 국내 95440-2M050·2M420.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>- 투싼 TL: 'ID6E-MA 또는 ID47' → ID47(NCF2952X).</t>
+          <t>- 싼타페 DM 2016-2018·맥스크루즈 2016-2019: 'ID46 또는 ID47' → ID46(95440-2W500·B8100 모두 PCF7952A). 싼타페 DM 95440-4Z200은 미국형.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>- 스타리아: ID4A → ID47(NCF29A1X).</t>
+          <t>- 싼타페 SM 2000-2002: 4D60 → 국내 이모빌라이저는 2005년형(2004.8.11)부터 적용, 그 이전은 해당 없음.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>- 그랜드 스타렉스 2007-2011·포터2 2004-2015: '4D60 또는 미탑재' → 국내 이모빌라이저 사양 키는 ID46(그랜드 스타렉스 블랭킹키 81996-2H010 = 아반떼 HD 공용, 포터2 81996-4F020 = ID46 키블레이드).</t>
+          <t>- 투싼 TL: 'ID6E-MA 또는 ID47' → ID47(NCF2952X).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>- 베라크루즈 2013-2015: '수출형 ix55 확인 불가' → 국내 판매가 2015년까지 이어짐(95440-3J560 ID46).</t>
+          <t>- 스타리아: ID4A → ID47(NCF29A1X).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>- i40 2011-2014: 판매처마다 TMS37126(TI DST80) 표기와 8A 표기가 갈려 주황색(2015년 이후 3Z003·3Z500은 8A).</t>
+          <t>- 그랜드 스타렉스 2007-2011·포터2 2004-2015: '4D60 또는 미탑재' → 국내 이모빌라이저 사양 키는 ID46(그랜드 스타렉스 블랭킹키 81996-2H010 = 아반떼 HD 공용, 포터2 81996-4F020 = ID46 키블레이드).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr"/>
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>- 베라크루즈 2013-2015: '수출형 ix55 확인 불가' → 국내 판매가 2015년까지 이어짐(95440-3J560 ID46).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>※ 조사하며 확인된 주요 사항</t>
+          <t>- i40: 품번별로 칩이 다름 — 95440-3Z000(2011.12.15~2012.4.2)은 TMS37126(DST80, ID6E-MA), 3Z001·3Z002 이후는 DST-AES(8A).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>- 연식별 검색 기록은 research/hyundai/yearly.md, 예전 파일 내용은 research/hyundai/old_rows.tsv에 있습니다.</t>
+          <t>- 그랜저 TG 스마트키 95440-3L100은 TIRIS DST80(ID6E-MA), 이모빌라이저키 81996-3L010은 ID46.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>- 아반떼 XD는 2005년형(2004.7.1)부터, 싼타페 SM은 2005년형(2004.8.11)부터, 스타렉스는 뉴 스타렉스(2004.1.29)부터 이모빌라이저가 기본 적용됐습니다. 베르나 트랜스폼(2009.6)은 원가절감으로 이모빌라이저가 빠졌습니다.</t>
+          <t>- 쏘나타 EF·그랜저 XG·싼타페 SM(2005년형~): 현대모비스 순정 이모빌라이저키 81996-38010(4D60). 베르나 MC: 81996-1E010(ID46, 트랜스폼 2009.6부터 이모빌라이저 삭제). 투싼 JM: 81996-2E010(ID46). 스타렉스: 81996-4A250(4D60).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>- 아반떼 HD 리모컨은 2008년형까지 447MHz, 2009년형부터 433MHz입니다. 싼타페 CM 스마트키 95440-2B800과 베라크루즈 스마트키는 한국형 447MHz입니다.</t>
+          <t>- 포터2 스마트키는 2024 포터II LPG(2023.12~)부터(95440-4FGA0). 2020-2023 디젤에는 스마트키가 없어 예전 파일의 95440-4FGA0 기재는 오류.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
+          <t>- 코나 N 95440-I3450(ID47), 일렉트리파이드 GV70 95440-DS000·DS010(ID47), GV80 쿠페 95440-T6AA0(ID4A) 품번을 새로 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>※ 조사하며 확인된 주요 사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>- 연식별 검색 기록은 research/hyundai/yearly.md, 예전 파일 내용은 research/hyundai/old_rows.tsv에 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>- 아반떼 XD는 2005년형(2004.7.1)부터, 싼타페 SM은 2005년형(2004.8.11)부터, 스타렉스는 뉴 스타렉스(2004.1.29)부터 이모빌라이저가 기본 적용됐습니다. 베르나 트랜스폼(2009.6)은 원가절감으로 이모빌라이저가 빠졌습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>- 아반떼 HD 리모컨은 2008년형까지 447MHz, 2009년형부터 433MHz입니다. 싼타페 CM 스마트키 95440-2B800과 베라크루즈 스마트키는 한국형 447MHz입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
           <t>- 그랜드 스타렉스·포터2는 이모빌라이저 사양과 비사양이 공존합니다(키·폴딩키 품번이 따로 있음).</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>- 칩 세대 흐름: ID46(Hitag2, ~2015년경) → ID8A(DST-AES, LF·AD·i30 PD·i40 후기) / ID47(Hitag3, IG·TL·TM·코나·제네시스) → ID4A(Hitag AES, GN7·DN8 디 엣지·MX5·아이오닉5·제네시스 부분변경) / ID6A(아반떼 CN7·캐스퍼·포터2 일렉트릭).</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="10" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
-        </is>
-      </c>
+      <c r="A48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
+          <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="n"/>
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>※ 칩 ID 코드 뜻</t>
+          <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
+          <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
+          <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
+          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
+          <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
-        </is>
-      </c>
+      <c r="A56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
+          <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>

--- a/현대_트랜스폰더_칩코드_DB.xlsx
+++ b/현대_트랜스폰더_칩코드_DB.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -157,6 +157,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4692,7 +4698,7 @@
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="n"/>
-      <c r="N64" s="7" t="n"/>
+      <c r="N64" s="11" t="n"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
           <t>나무위키 아반떼/2세대</t>
@@ -6988,7 +6994,7 @@
       <c r="K102" s="2" t="n"/>
       <c r="L102" s="2" t="n"/>
       <c r="M102" s="2" t="n"/>
-      <c r="N102" s="8" t="n"/>
+      <c r="N102" s="12" t="n"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
           <t>partsro 819961C400 베르나 LC 클릭 TB</t>
@@ -7038,7 +7044,7 @@
       <c r="K103" s="2" t="n"/>
       <c r="L103" s="2" t="n"/>
       <c r="M103" s="2" t="n"/>
-      <c r="N103" s="8" t="n"/>
+      <c r="N103" s="12" t="n"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
           <t>partsro 819961C400 베르나 LC 클릭 TB</t>
@@ -7088,7 +7094,7 @@
       <c r="K104" s="2" t="n"/>
       <c r="L104" s="2" t="n"/>
       <c r="M104" s="2" t="n"/>
-      <c r="N104" s="8" t="n"/>
+      <c r="N104" s="12" t="n"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
           <t>partsro 819961C400 베르나 LC 클릭 TB</t>
@@ -7138,7 +7144,7 @@
       <c r="K105" s="2" t="n"/>
       <c r="L105" s="2" t="n"/>
       <c r="M105" s="2" t="n"/>
-      <c r="N105" s="8" t="n"/>
+      <c r="N105" s="12" t="n"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
           <t>partsro 819961C400 베르나 LC 클릭 TB</t>
@@ -7188,7 +7194,7 @@
       <c r="K106" s="2" t="n"/>
       <c r="L106" s="2" t="n"/>
       <c r="M106" s="2" t="n"/>
-      <c r="N106" s="8" t="n"/>
+      <c r="N106" s="12" t="n"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
           <t>partsro 819961C400 베르나 LC 클릭 TB</t>
@@ -7238,7 +7244,7 @@
       <c r="K107" s="2" t="n"/>
       <c r="L107" s="2" t="n"/>
       <c r="M107" s="2" t="n"/>
-      <c r="N107" s="8" t="n"/>
+      <c r="N107" s="12" t="n"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
           <t>partsro 819961C400 베르나 LC 클릭 TB</t>
@@ -13276,7 +13282,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n"/>
-      <c r="N204" s="8" t="n"/>
+      <c r="N204" s="12" t="n"/>
       <c r="O204" s="2" t="inlineStr">
         <is>
           <t>hellowcar 아이오닉6 스마트키, mk3 Ioniq 6 2025 KL500</t>
@@ -13338,7 +13344,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n"/>
-      <c r="N205" s="8" t="n"/>
+      <c r="N205" s="12" t="n"/>
       <c r="O205" s="2" t="inlineStr">
         <is>
           <t>hellowcar 아이오닉6 스마트키, mk3 Ioniq 6 2025 KL500</t>
@@ -21632,7 +21638,7 @@
       <c r="K340" s="2" t="n"/>
       <c r="L340" s="2" t="n"/>
       <c r="M340" s="2" t="n"/>
-      <c r="N340" s="8" t="n"/>
+      <c r="N340" s="12" t="n"/>
       <c r="O340" s="2" t="inlineStr">
         <is>
           <t>ebay 819964A250 Starex 2000-2007, abkeys 81996-4A250 4D60, transpondery Hyundai</t>
@@ -21698,7 +21704,7 @@
       <c r="K341" s="2" t="n"/>
       <c r="L341" s="2" t="n"/>
       <c r="M341" s="2" t="n"/>
-      <c r="N341" s="8" t="n"/>
+      <c r="N341" s="12" t="n"/>
       <c r="O341" s="2" t="inlineStr">
         <is>
           <t>ebay 819964A250 Starex 2000-2007, abkeys 81996-4A250 4D60, transpondery Hyundai</t>
@@ -24768,7 +24774,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n"/>
-      <c r="N388" s="8" t="n"/>
+      <c r="N388" s="12" t="n"/>
       <c r="O388" s="2" t="inlineStr">
         <is>
           <t>hellowcar 포터2 전기차, vvdi 95440-CN100 AES 6A</t>
@@ -24834,7 +24840,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n"/>
-      <c r="N389" s="8" t="n"/>
+      <c r="N389" s="12" t="n"/>
       <c r="O389" s="2" t="inlineStr">
         <is>
           <t>hellowcar 포터2 전기차, vvdi 95440-CN100 AES 6A</t>
@@ -24900,7 +24906,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n"/>
-      <c r="N390" s="8" t="n"/>
+      <c r="N390" s="12" t="n"/>
       <c r="O390" s="2" t="inlineStr">
         <is>
           <t>hellowcar 포터2 전기차, vvdi 95440-CN100 AES 6A</t>
@@ -24966,7 +24972,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n"/>
-      <c r="N391" s="8" t="n"/>
+      <c r="N391" s="12" t="n"/>
       <c r="O391" s="2" t="inlineStr">
         <is>
           <t>hellowcar 포터2 전기차, vvdi 95440-CN100 AES 6A</t>
@@ -26162,7 +26168,7 @@
       <c r="K411" s="2" t="n"/>
       <c r="L411" s="2" t="n"/>
       <c r="M411" s="2" t="n"/>
-      <c r="N411" s="8" t="n"/>
+      <c r="N411" s="12" t="n"/>
       <c r="O411" s="2" t="inlineStr">
         <is>
           <t>eacar 2024 G80 일렉트리파이드 부분변경, partsro 95440T1210 전기차 공용</t>
@@ -26220,7 +26226,7 @@
       <c r="K412" s="2" t="n"/>
       <c r="L412" s="2" t="n"/>
       <c r="M412" s="2" t="n"/>
-      <c r="N412" s="8" t="n"/>
+      <c r="N412" s="12" t="n"/>
       <c r="O412" s="2" t="inlineStr">
         <is>
           <t>eacar 2024 G80 일렉트리파이드 부분변경, partsro 95440T1210 전기차 공용</t>
@@ -26278,7 +26284,7 @@
       <c r="K413" s="2" t="n"/>
       <c r="L413" s="2" t="n"/>
       <c r="M413" s="2" t="n"/>
-      <c r="N413" s="8" t="n"/>
+      <c r="N413" s="12" t="n"/>
       <c r="O413" s="2" t="inlineStr">
         <is>
           <t>eacar 2024 G80 일렉트리파이드 부분변경, partsro 95440T1210 전기차 공용</t>
@@ -28938,7 +28944,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n"/>
-      <c r="N457" s="8" t="n"/>
+      <c r="N457" s="12" t="n"/>
       <c r="O457" s="2" t="inlineStr">
         <is>
           <t>hyundaimotorgroup GV70 전동화 부분변경 출시, shop.genesis.com Electrified GV70 스마트 카드 키</t>
@@ -29000,7 +29006,7 @@
       </c>
       <c r="L458" s="2" t="n"/>
       <c r="M458" s="2" t="n"/>
-      <c r="N458" s="8" t="n"/>
+      <c r="N458" s="12" t="n"/>
       <c r="O458" s="2" t="inlineStr">
         <is>
           <t>hyundaimotorgroup GV70 전동화 부분변경 출시, shop.genesis.com Electrified GV70 스마트 카드 키</t>
@@ -29352,7 +29358,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n"/>
-      <c r="N464" s="8" t="n"/>
+      <c r="N464" s="12" t="n"/>
       <c r="O464" s="2" t="inlineStr">
         <is>
           <t>royalkeysupply 2026 GV60 CU260</t>
@@ -29383,313 +29389,313 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr"/>
+      <c r="A2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>- 예전 현대 파일(컬럼 10개, 칩·세부ID·부품번호가 섞인 구조)을 버리고 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같은 컬럼으로 새로 작성했습니다. 칩코드 뒤에 '키종류'를 추가했습니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '현대 쏘나타', '제네시스 G80'처럼 브랜드와 모델명을 함께 검색 가능). 제네시스 브랜드 독립(2015.11) 이후 모델은 '제네시스', 그 이전 현대 제네시스(BH·DH)·제네시스 쿠페는 '현대'입니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다. 예전 파일에서 연식을 나누지 않고 한 줄로 적었던 모델(예: 2006-2010)은 조사 대상에서 뺐습니다(에쿠스·i20·갤로퍼·테라칸·트라제 XG·라비타·클릭·마이티 등).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>- 연식은 실제 국내 판매(출시일) 기준입니다. 풀체인지가 있는 해는 전·후 세대가 각각 한 행씩 있습니다. 후속 없이 단종된 모델의 마지막 연식은 '2019(단종)' 형식입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 카드키는 그랜저 HG·IG, 제네시스 DH의 카드형 스마트키입니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434/447MHz)만 적었습니다. 미국형 315MHz 키(예: 95440-3Q000·95440-3M220·95440-2M350·95440-2V100·95440-4Z200, FCC SY5HMFNA04)는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>- 스마트키에 딸린 비상키(블랭킹키)는 '키블레이드(부품번호)' 칸에 적었습니다. 키리모컨 일체형(81996-4H100 등)은 '폴딩키(부품번호)' 칸에 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템' 칸은 현대모비스 품번이 확인된 차종만 적었습니다(그랜드 스타렉스·포터2 이모빌라이저 모듈 95420-D4000·95420-4F500, 포터2 안테나 95440-4F100).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. hellowcar·partsro(현대모비스 공식 부품몰)는 적용 기간이 적힌 국내 순정 품번의 근거이고, 칩 종류는 대부분 해외 키 판매처(abkeys·mk3·remotesandkeys 등)의 같은 품번 설명을 근거로 했습니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr"/>
+      <c r="A14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값 — 실물 키·VIN으로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — 아반떼 J2(2000) 1행.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>- 주황색으로 남은 행(재조사 후 23행): 부분변경 신형 스마트키 칩 원문이 아직 없는 경우(아이오닉6 2025~, 일렉트리파이드 G80 2024~, 일렉트리파이드 GV70 2025~, GV60 2026, 포터2 LPG 스마트키, 포터2 일렉트릭 CN000), 스타렉스 2004-2005(순정 4D60 키 vs 해외 카탈로그 4C), 베르나 LC(이모빌라이저키 품번이 없어 미적용 추정).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>- 전환 연식은 칩코드 칸에 전·후를 함께 적었습니다(예: 쏘나타 DN8 2023 = ID47(NCF29A1X)[~2023.2], ID4A(NCF29A1M)[디 엣지, 2023.3~]).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>- 칩코드 추가 뜻: ID4C = Texas 4C(고정 코드, 스타렉스 2004-2006 해외 자료), 해당 없음 = 그 연식 국내형에 이모빌라이저가 없음.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr"/>
+      <c r="A21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>※ 예전 현대 파일에서 바로잡은 주요 오류</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>- 쏘나타 LF(2014-2019): ID47 → ID8A(DST-AES). 95440-C1001·C1500 모두 8A.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>- 쏘나타 DN8 2019-2022: ID4A → ID47(NCF29A1X). ID4A는 디 엣지(2023.3~)부터.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>- 아반떼 AD(2015-2020): ID47 → ID8A. 아반떼 CN7·아반떼 N·아이오닉6: ID4A → ID6A. 더 뉴 아반떼(95440-AA500)·아이오닉6(KL000)은 FCC NYOMBEC7FOB2208(MBEC 계열 = CN7 AA000·캐스퍼와 같은 6A 계열)이고 auto-keys·keyshop-online·abkeys가 6A로 일치. 일부 판매처(remotesandkeys)의 '4A' 표기는 같은 키를 4A·6A로 섞어 적어 따르지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>- 투싼 NX4 부분변경(더 뉴 투싼, 2023.11~): 스마트키가 95440-N95xx(ID4A)로 바뀜 — 처음 작성 때 ID47로 잘못 이어 적었던 것을 정정.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>- 그랜저 GN7: 스마트키 품번 95440-BY000 → 95440-N1xxx(N1000·N1050·N1110 등).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>- 제네시스 DH 2013-2014: 'BH 전자장비 유지, ID46(95440-3M220)' → DH는 출시(2013.11)부터 95440-B1200BLH ID47. 95440-3M220은 미국형 315MHz.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>- 제네시스 BH: 95440-3M220(미국형) → 국내 95440-3M010·3M020·3M030. 제네시스 쿠페: 95440-2M350·2M300·3V021(미국형) → 국내 95440-2M050·2M420.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>- 싼타페 DM 2016-2018·맥스크루즈 2016-2019: 'ID46 또는 ID47' → ID46(95440-2W500·B8100 모두 PCF7952A). 싼타페 DM 95440-4Z200은 미국형.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>- 싼타페 SM 2000-2002: 4D60 → 국내 이모빌라이저는 2005년형(2004.8.11)부터 적용, 그 이전은 해당 없음.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>- 투싼 TL: 'ID6E-MA 또는 ID47' → ID47(NCF2952X).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>- 스타리아: ID4A → ID47(NCF29A1X).</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>- 그랜드 스타렉스 2007-2011·포터2 2004-2015: '4D60 또는 미탑재' → 국내 이모빌라이저 사양 키는 ID46(그랜드 스타렉스 블랭킹키 81996-2H010 = 아반떼 HD 공용, 포터2 81996-4F020 = ID46 키블레이드).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>- 베라크루즈 2013-2015: '수출형 ix55 확인 불가' → 국내 판매가 2015년까지 이어짐(95440-3J560 ID46).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>- i40: 품번별로 칩이 다름 — 95440-3Z000(2011.12.15~2012.4.2)은 TMS37126(DST80, ID6E-MA), 3Z001·3Z002 이후는 DST-AES(8A).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>- 그랜저 TG 스마트키 95440-3L100은 TIRIS DST80(ID6E-MA), 이모빌라이저키 81996-3L010은 ID46.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>- 쏘나타 EF·그랜저 XG·싼타페 SM(2005년형~): 현대모비스 순정 이모빌라이저키 81996-38010(4D60). 베르나 MC: 81996-1E010(ID46, 트랜스폼 2009.6부터 이모빌라이저 삭제). 투싼 JM: 81996-2E010(ID46). 스타렉스: 81996-4A250(4D60).</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>- 포터2 스마트키는 2024 포터II LPG(2023.12~)부터(95440-4FGA0). 2020-2023 디젤에는 스마트키가 없어 예전 파일의 95440-4FGA0 기재는 오류.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>- 코나 N 95440-I3450(ID47), 일렉트리파이드 GV70 95440-DS000·DS010(ID47), GV80 쿠페 95440-T6AA0(ID4A) 품번을 새로 확인.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr"/>
+      <c r="A41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>- 연식별 검색 기록은 research/hyundai/yearly.md, 예전 파일 내용은 research/hyundai/old_rows.tsv에 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>- 아반떼 XD는 2005년형(2004.7.1)부터, 싼타페 SM은 2005년형(2004.8.11)부터, 스타렉스는 뉴 스타렉스(2004.1.29)부터 이모빌라이저가 기본 적용됐습니다. 베르나 트랜스폼(2009.6)은 원가절감으로 이모빌라이저가 빠졌습니다.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>- 아반떼 HD 리모컨은 2008년형까지 447MHz, 2009년형부터 433MHz입니다. 싼타페 CM 스마트키 95440-2B800과 베라크루즈 스마트키는 한국형 447MHz입니다.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>- 그랜드 스타렉스·포터2는 이모빌라이저 사양과 비사양이 공존합니다(키·폴딩키 품번이 따로 있음).</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>- 칩 세대 흐름: ID46(Hitag2, ~2015년경) → ID8A(DST-AES, LF·AD·i30 PD·i40 후기) / ID47(Hitag3, IG·TL·TM·코나·제네시스) → ID4A(Hitag AES, GN7·DN8 디 엣지·MX5·아이오닉5·제네시스 부분변경) / ID6A(아반떼 CN7·캐스퍼·포터2 일렉트릭).</t>
         </is>

--- a/현대_트랜스폰더_칩코드_DB.xlsx
+++ b/현대_트랜스폰더_칩코드_DB.xlsx
@@ -13273,19 +13273,23 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I204" s="2" t="n"/>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>81996-KL010</t>
+        </is>
+      </c>
       <c r="J204" s="2" t="n"/>
       <c r="K204" s="2" t="n"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>95440-KL500</t>
+          <t>95440-KL500, 95440-KL510, 95440-KL550, 95440-KL560</t>
         </is>
       </c>
       <c r="M204" s="2" t="n"/>
       <c r="N204" s="12" t="n"/>
       <c r="O204" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 아이오닉6 스마트키, mk3 Ioniq 6 2025 KL500</t>
+          <t>hellowcar 아이오닉6 CE1 페이스리프트</t>
         </is>
       </c>
       <c r="P204" s="8" t="inlineStr">
@@ -13335,19 +13339,23 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I205" s="2" t="n"/>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>81996-KL010</t>
+        </is>
+      </c>
       <c r="J205" s="2" t="n"/>
       <c r="K205" s="2" t="n"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>95440-KL500</t>
+          <t>95440-KL500, 95440-KL510, 95440-KL550, 95440-KL560</t>
         </is>
       </c>
       <c r="M205" s="2" t="n"/>
       <c r="N205" s="12" t="n"/>
       <c r="O205" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 아이오닉6 스마트키, mk3 Ioniq 6 2025 KL500</t>
+          <t>hellowcar 아이오닉6 CE1 페이스리프트</t>
         </is>
       </c>
       <c r="P205" s="8" t="inlineStr">
@@ -24751,9 +24759,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G388" s="8" t="inlineStr">
-        <is>
-          <t>ID6A[추정]</t>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr">
@@ -24774,17 +24782,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n"/>
-      <c r="N388" s="12" t="n"/>
+      <c r="N388" s="2" t="n"/>
       <c r="O388" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 포터2 전기차, vvdi 95440-CN100 AES 6A</t>
-        </is>
-      </c>
-      <c r="P388" s="8" t="inlineStr">
-        <is>
-          <t>95440-CN000 칩 원문 없음 — 후속 CN100(AES 6A) 기준 추정</t>
-        </is>
-      </c>
+          <t>mk3 Hyundai Porter2 EV 95440-CN000</t>
+        </is>
+      </c>
+      <c r="P388" s="2" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -24817,9 +24821,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G389" s="8" t="inlineStr">
-        <is>
-          <t>ID6A[추정]</t>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H389" s="2" t="inlineStr">
@@ -24840,17 +24844,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n"/>
-      <c r="N389" s="12" t="n"/>
+      <c r="N389" s="2" t="n"/>
       <c r="O389" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 포터2 전기차, vvdi 95440-CN100 AES 6A</t>
-        </is>
-      </c>
-      <c r="P389" s="8" t="inlineStr">
-        <is>
-          <t>95440-CN000 칩 원문 없음 — 후속 CN100(AES 6A) 기준 추정</t>
-        </is>
-      </c>
+          <t>mk3 Hyundai Porter2 EV 95440-CN000</t>
+        </is>
+      </c>
+      <c r="P389" s="2" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -24883,9 +24883,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G390" s="8" t="inlineStr">
-        <is>
-          <t>ID6A[추정]</t>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
@@ -24906,17 +24906,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n"/>
-      <c r="N390" s="12" t="n"/>
+      <c r="N390" s="2" t="n"/>
       <c r="O390" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 포터2 전기차, vvdi 95440-CN100 AES 6A</t>
-        </is>
-      </c>
-      <c r="P390" s="8" t="inlineStr">
-        <is>
-          <t>95440-CN000 칩 원문 없음 — 후속 CN100(AES 6A) 기준 추정</t>
-        </is>
-      </c>
+          <t>mk3 Hyundai Porter2 EV 95440-CN000</t>
+        </is>
+      </c>
+      <c r="P390" s="2" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -24949,9 +24945,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G391" s="8" t="inlineStr">
-        <is>
-          <t>ID6A[추정]</t>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
@@ -24972,17 +24968,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n"/>
-      <c r="N391" s="12" t="n"/>
+      <c r="N391" s="2" t="n"/>
       <c r="O391" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 포터2 전기차, vvdi 95440-CN100 AES 6A</t>
-        </is>
-      </c>
-      <c r="P391" s="8" t="inlineStr">
-        <is>
-          <t>95440-CN000 칩 원문 없음 — 후속 CN100(AES 6A) 기준 추정</t>
-        </is>
-      </c>
+          <t>mk3 Hyundai Porter2 EV 95440-CN000</t>
+        </is>
+      </c>
+      <c r="P391" s="2" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -28757,12 +28749,16 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I454" s="2" t="n"/>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>81996-AR000</t>
+        </is>
+      </c>
       <c r="J454" s="2" t="n"/>
       <c r="K454" s="2" t="n"/>
       <c r="L454" s="2" t="inlineStr">
         <is>
-          <t>95440-DS000, 95440-DS010[8버튼]</t>
+          <t>95440-DS000[6버튼], 95440-DS010[8버튼]</t>
         </is>
       </c>
       <c r="M454" s="2" t="n"/>
@@ -28815,12 +28811,16 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I455" s="2" t="n"/>
+      <c r="I455" s="2" t="inlineStr">
+        <is>
+          <t>81996-AR000</t>
+        </is>
+      </c>
       <c r="J455" s="2" t="n"/>
       <c r="K455" s="2" t="n"/>
       <c r="L455" s="2" t="inlineStr">
         <is>
-          <t>95440-DS000, 95440-DS010[8버튼]</t>
+          <t>95440-DS000[6버튼], 95440-DS010[8버튼]</t>
         </is>
       </c>
       <c r="M455" s="2" t="n"/>
@@ -28873,12 +28873,16 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I456" s="2" t="n"/>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>81996-AR000</t>
+        </is>
+      </c>
       <c r="J456" s="2" t="n"/>
       <c r="K456" s="2" t="n"/>
       <c r="L456" s="2" t="inlineStr">
         <is>
-          <t>95440-DS000, 95440-DS010[8버튼]</t>
+          <t>95440-DS000[6버튼], 95440-DS010[8버튼]</t>
         </is>
       </c>
       <c r="M456" s="2" t="n"/>

--- a/현대_트랜스폰더_칩코드_DB.xlsx
+++ b/현대_트랜스폰더_칩코드_DB.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P472"/>
+  <dimension ref="A1:P473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21938,24 +21938,12 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="D346" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E346" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F346" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G346" s="8" t="inlineStr">
-        <is>
-          <t>ID60[자료 상충], ID4C[자료 상충]</t>
+      <c r="D346" s="6" t="inlineStr"/>
+      <c r="E346" s="6" t="inlineStr"/>
+      <c r="F346" s="6" t="inlineStr"/>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
         </is>
       </c>
       <c r="H346" s="2" t="inlineStr">
@@ -21963,30 +21951,18 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I346" s="2" t="inlineStr">
-        <is>
-          <t>81996-4A250</t>
-        </is>
-      </c>
-      <c r="J346" s="2" t="inlineStr">
-        <is>
-          <t>HYN6</t>
-        </is>
-      </c>
+      <c r="I346" s="2" t="n"/>
+      <c r="J346" s="2" t="n"/>
       <c r="K346" s="2" t="n"/>
       <c r="L346" s="2" t="n"/>
       <c r="M346" s="2" t="n"/>
-      <c r="N346" s="13" t="n"/>
+      <c r="N346" s="2" t="n"/>
       <c r="O346" s="2" t="inlineStr">
         <is>
           <t>ebay 819964A250 Starex 2000-2007, abkeys 81996-4A250 4D60, transpondery Hyundai</t>
         </is>
       </c>
-      <c r="P346" s="8" t="inlineStr">
-        <is>
-          <t>순정 이모빌라이저키 81996-4A250(2000.4~2007.12)은 4D60, 해외 카탈로그(transpondery)는 2004-2006 Texas 4C 표기</t>
-        </is>
-      </c>
+      <c r="P346" s="2" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -22004,24 +21980,12 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="D347" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E347" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F347" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G347" s="8" t="inlineStr">
-        <is>
-          <t>ID60[자료 상충], ID4C[자료 상충]</t>
+      <c r="D347" s="12" t="n"/>
+      <c r="E347" s="12" t="n"/>
+      <c r="F347" s="12" t="n"/>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>해당 없음[~2005.6]</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr">
@@ -22029,11 +21993,7 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I347" s="2" t="inlineStr">
-        <is>
-          <t>81996-4A250</t>
-        </is>
-      </c>
+      <c r="I347" s="2" t="n"/>
       <c r="J347" s="2" t="inlineStr">
         <is>
           <t>HYN6</t>
@@ -22042,17 +22002,13 @@
       <c r="K347" s="2" t="n"/>
       <c r="L347" s="2" t="n"/>
       <c r="M347" s="2" t="n"/>
-      <c r="N347" s="13" t="n"/>
+      <c r="N347" s="2" t="n"/>
       <c r="O347" s="2" t="inlineStr">
         <is>
           <t>ebay 819964A250 Starex 2000-2007, abkeys 81996-4A250 4D60, transpondery Hyundai</t>
         </is>
       </c>
-      <c r="P347" s="8" t="inlineStr">
-        <is>
-          <t>순정 이모빌라이저키 81996-4A250(2000.4~2007.12)은 4D60, 해외 카탈로그(transpondery)는 2004-2006 Texas 4C 표기</t>
-        </is>
-      </c>
+      <c r="P347" s="2" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -22067,7 +22023,7 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
@@ -22087,7 +22043,7 @@
       </c>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>ID60</t>
+          <t>ID60[2006년형, 2005.7~, 11·12인승]</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
@@ -22097,7 +22053,7 @@
       </c>
       <c r="I348" s="2" t="inlineStr">
         <is>
-          <t>81996-4A250</t>
+          <t>81996-4A250[2006년형~]</t>
         </is>
       </c>
       <c r="J348" s="2" t="inlineStr">
@@ -22111,7 +22067,7 @@
       <c r="N348" s="2" t="n"/>
       <c r="O348" s="2" t="inlineStr">
         <is>
-          <t>abkeys 81996-4A250 4D60</t>
+          <t>ebay 819964A250 Starex 2000-2007, abkeys 81996-4A250 4D60, transpondery Hyundai</t>
         </is>
       </c>
       <c r="P348" s="2" t="n"/>
@@ -22129,7 +22085,7 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
@@ -22186,7 +22142,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>그랜드 스타렉스 (TQ)</t>
+          <t>스타렉스 (A1)</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
@@ -22211,31 +22167,31 @@
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)[이모빌라이저 사양]</t>
+          <t>ID60</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
         <is>
-          <t>막대키,폴딩키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I350" s="2" t="inlineStr">
         <is>
-          <t>81996-2H010</t>
-        </is>
-      </c>
-      <c r="J350" s="2" t="n"/>
+          <t>81996-4A250</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr">
+        <is>
+          <t>HYN6</t>
+        </is>
+      </c>
       <c r="K350" s="2" t="n"/>
       <c r="L350" s="2" t="n"/>
-      <c r="M350" s="2" t="inlineStr">
-        <is>
-          <t>81996-4H100[이모빌라이저 미적용, 키리모컨], 81996-4H200[이모빌라이저 사양, 키리모컨], 95430-4H400[이모빌라이저 미적용], 95430-4H500[이모빌라이저 사양]</t>
-        </is>
-      </c>
+      <c r="M350" s="2" t="n"/>
       <c r="N350" s="2" t="n"/>
       <c r="O350" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 그랜드스타렉스 키리모콘 819964H100/4H200/4H400/4H500, partsro 819962H010, key-programmer.org Starex 2007 ID46</t>
+          <t>abkeys 81996-4A250 4D60</t>
         </is>
       </c>
       <c r="P350" s="2" t="n"/>
@@ -22253,7 +22209,7 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
@@ -22297,7 +22253,7 @@
       <c r="N351" s="2" t="n"/>
       <c r="O351" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>hellowcar 그랜드스타렉스 키리모콘 819964H100/4H200/4H400/4H500, partsro 819962H010, key-programmer.org Starex 2007 ID46</t>
         </is>
       </c>
       <c r="P351" s="2" t="n"/>
@@ -22315,7 +22271,7 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
@@ -22353,7 +22309,7 @@
       <c r="L352" s="2" t="n"/>
       <c r="M352" s="2" t="inlineStr">
         <is>
-          <t>95430-4H400[이모빌라이저 미적용], 95430-4H500[이모빌라이저 사양], 95430-4H401</t>
+          <t>81996-4H100[이모빌라이저 미적용, 키리모컨], 81996-4H200[이모빌라이저 사양, 키리모컨], 95430-4H400[이모빌라이저 미적용], 95430-4H500[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="N352" s="2" t="n"/>
@@ -22377,7 +22333,7 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
@@ -22439,7 +22395,7 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
@@ -22501,7 +22457,7 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
@@ -22563,7 +22519,7 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
@@ -22625,7 +22581,7 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
@@ -22687,7 +22643,7 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
@@ -22728,14 +22684,10 @@
           <t>95430-4H400[이모빌라이저 미적용], 95430-4H500[이모빌라이저 사양], 95430-4H401</t>
         </is>
       </c>
-      <c r="N358" s="2" t="inlineStr">
-        <is>
-          <t>95420-D4000</t>
-        </is>
-      </c>
+      <c r="N358" s="2" t="n"/>
       <c r="O358" s="2" t="inlineStr">
         <is>
-          <t>partsro 95420D4000 올뉴K7·포터2·그랜드 스타렉스, amazon 95420-D4000 Accent 18-21</t>
+          <t>hellowcar</t>
         </is>
       </c>
       <c r="P358" s="2" t="n"/>
@@ -22753,7 +22705,7 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
@@ -22819,7 +22771,7 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
@@ -22885,7 +22837,7 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
@@ -22905,7 +22857,7 @@
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>ID46[이모빌라이저 사양]</t>
+          <t>ID46(PCF7936)[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr">
@@ -22913,13 +22865,17 @@
           <t>막대키,폴딩키</t>
         </is>
       </c>
-      <c r="I361" s="2" t="n"/>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>81996-2H010</t>
+        </is>
+      </c>
       <c r="J361" s="2" t="n"/>
       <c r="K361" s="2" t="n"/>
       <c r="L361" s="2" t="n"/>
       <c r="M361" s="2" t="inlineStr">
         <is>
-          <t>95430-4H401</t>
+          <t>95430-4H400[이모빌라이저 미적용], 95430-4H500[이모빌라이저 사양], 95430-4H401</t>
         </is>
       </c>
       <c r="N361" s="2" t="inlineStr">
@@ -22947,7 +22903,7 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
@@ -23009,7 +22965,7 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
@@ -23071,7 +23027,7 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
@@ -23128,7 +23084,7 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>스타리아 (US4)</t>
+          <t>그랜드 스타렉스 (TQ)</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
@@ -23136,14 +23092,14 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D365" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E365" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+      <c r="D365" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E365" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F365" s="3" t="inlineStr">
@@ -23153,35 +23109,31 @@
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>ID47(NCF29A1X)</t>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I365" s="2" t="inlineStr">
-        <is>
-          <t>81996-L1100, 81996-M5000</t>
-        </is>
-      </c>
+          <t>막대키,폴딩키</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="n"/>
       <c r="J365" s="2" t="n"/>
       <c r="K365" s="2" t="n"/>
-      <c r="L365" s="2" t="inlineStr">
-        <is>
-          <t>95440-CG020, 95440-CG030[7버튼], 95440-CG070[4버튼], 95440-CG080[6버튼], 95440-CG120[4버튼], 95440-CG140[2버튼]</t>
-        </is>
-      </c>
+      <c r="L365" s="2" t="n"/>
       <c r="M365" s="2" t="inlineStr">
         <is>
-          <t>95430-CG000, 95430-CG100</t>
-        </is>
-      </c>
-      <c r="N365" s="2" t="n"/>
+          <t>95430-4H401</t>
+        </is>
+      </c>
+      <c r="N365" s="2" t="inlineStr">
+        <is>
+          <t>95420-D4000</t>
+        </is>
+      </c>
       <c r="O365" s="2" t="inlineStr">
         <is>
-          <t>mk3 Staria CG070 ID47, abkeys CG080/CG120/CG140, gskeyae CG030</t>
+          <t>partsro 95420D4000 올뉴K7·포터2·그랜드 스타렉스, amazon 95420-D4000 Accent 18-21</t>
         </is>
       </c>
       <c r="P365" s="2" t="n"/>
@@ -23199,7 +23151,7 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
@@ -23247,7 +23199,7 @@
       <c r="N366" s="2" t="n"/>
       <c r="O366" s="2" t="inlineStr">
         <is>
-          <t>abkeys 2022-2024 CG080/CG120</t>
+          <t>mk3 Staria CG070 ID47, abkeys CG080/CG120/CG140, gskeyae CG030</t>
         </is>
       </c>
       <c r="P366" s="2" t="n"/>
@@ -23265,7 +23217,7 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -23295,14 +23247,14 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>81996-M5000, 81996-AA540</t>
+          <t>81996-L1100, 81996-M5000</t>
         </is>
       </c>
       <c r="J367" s="2" t="n"/>
       <c r="K367" s="2" t="n"/>
       <c r="L367" s="2" t="inlineStr">
         <is>
-          <t>95440-CG020[~2023.8], 95440-CG030[~2023.8], 95440-CG120[~2023.8], 95440-CG520[2023.9~], 95440-CG530[2023.9~], 95440-CG620[2023.9~]</t>
+          <t>95440-CG020, 95440-CG030[7버튼], 95440-CG070[4버튼], 95440-CG080[6버튼], 95440-CG120[4버튼], 95440-CG140[2버튼]</t>
         </is>
       </c>
       <c r="M367" s="2" t="inlineStr">
@@ -23313,7 +23265,7 @@
       <c r="N367" s="2" t="n"/>
       <c r="O367" s="2" t="inlineStr">
         <is>
-          <t>abkeys 2021-2023 CG140, 원본 모비스 기록</t>
+          <t>abkeys 2022-2024 CG080/CG120</t>
         </is>
       </c>
       <c r="P367" s="2" t="n"/>
@@ -23331,7 +23283,7 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
@@ -23361,14 +23313,14 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>81996-AA540</t>
+          <t>81996-M5000, 81996-AA540</t>
         </is>
       </c>
       <c r="J368" s="2" t="n"/>
       <c r="K368" s="2" t="n"/>
       <c r="L368" s="2" t="inlineStr">
         <is>
-          <t>95440-CG520, 95440-CG530[7버튼], 95440-CG620</t>
+          <t>95440-CG020[~2023.8], 95440-CG030[~2023.8], 95440-CG120[~2023.8], 95440-CG520[2023.9~], 95440-CG530[2023.9~], 95440-CG620[2023.9~]</t>
         </is>
       </c>
       <c r="M368" s="2" t="inlineStr">
@@ -23379,7 +23331,7 @@
       <c r="N368" s="2" t="n"/>
       <c r="O368" s="2" t="inlineStr">
         <is>
-          <t>abkeys CG530 2024-2025</t>
+          <t>abkeys 2021-2023 CG140, 원본 모비스 기록</t>
         </is>
       </c>
       <c r="P368" s="2" t="n"/>
@@ -23397,7 +23349,7 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
@@ -23463,7 +23415,7 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
@@ -23511,7 +23463,7 @@
       <c r="N370" s="2" t="n"/>
       <c r="O370" s="2" t="inlineStr">
         <is>
-          <t>abkeys</t>
+          <t>abkeys CG530 2024-2025</t>
         </is>
       </c>
       <c r="P370" s="2" t="n"/>
@@ -23524,22 +23476,22 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>포터2 (HR)</t>
+          <t>스타리아 (US4)</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="D371" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E371" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D371" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E371" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F371" s="3" t="inlineStr">
@@ -23549,35 +23501,35 @@
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>ID46[이모빌라이저 사양]</t>
+          <t>ID47(NCF29A1X)</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>81996-4F010, 81996-4F020, 81996-4F000[칩 없음]</t>
+          <t>81996-AA540</t>
         </is>
       </c>
       <c r="J371" s="2" t="n"/>
       <c r="K371" s="2" t="n"/>
-      <c r="L371" s="2" t="n"/>
+      <c r="L371" s="2" t="inlineStr">
+        <is>
+          <t>95440-CG520, 95440-CG530[7버튼], 95440-CG620</t>
+        </is>
+      </c>
       <c r="M371" s="2" t="inlineStr">
         <is>
-          <t>81996-4F100[키리모컨], 81996-4F120[키리모컨]</t>
-        </is>
-      </c>
-      <c r="N371" s="2" t="inlineStr">
-        <is>
-          <t>95440-4F100</t>
-        </is>
-      </c>
+          <t>95430-CG000, 95430-CG100</t>
+        </is>
+      </c>
+      <c r="N371" s="2" t="n"/>
       <c r="O371" s="2" t="inlineStr">
         <is>
-          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
+          <t>abkeys</t>
         </is>
       </c>
       <c r="P371" s="2" t="n"/>
@@ -23595,7 +23547,7 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
@@ -23661,7 +23613,7 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
@@ -23727,7 +23679,7 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
@@ -23793,7 +23745,7 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
@@ -23831,7 +23783,7 @@
       <c r="L375" s="2" t="n"/>
       <c r="M375" s="2" t="inlineStr">
         <is>
-          <t>81996-4F100[~2008.9.1, 키리모컨], 81996-4F120[~2008.9.1, 키리모컨], 81996-4F101[2008.9.2~, 키리모컨], 81996-4F121[2008.9.2~, 키리모컨]</t>
+          <t>81996-4F100[키리모컨], 81996-4F120[키리모컨]</t>
         </is>
       </c>
       <c r="N375" s="2" t="inlineStr">
@@ -23859,7 +23811,7 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
@@ -23897,7 +23849,7 @@
       <c r="L376" s="2" t="n"/>
       <c r="M376" s="2" t="inlineStr">
         <is>
-          <t>81996-4F101[키리모컨], 81996-4F121[키리모컨]</t>
+          <t>81996-4F100[~2008.9.1, 키리모컨], 81996-4F120[~2008.9.1, 키리모컨], 81996-4F101[2008.9.2~, 키리모컨], 81996-4F121[2008.9.2~, 키리모컨]</t>
         </is>
       </c>
       <c r="N376" s="2" t="inlineStr">
@@ -23925,7 +23877,7 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
@@ -23991,7 +23943,7 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
@@ -24057,7 +24009,7 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
@@ -24123,7 +24075,7 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
@@ -24189,7 +24141,7 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
@@ -24255,7 +24207,7 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
@@ -24321,7 +24273,7 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
@@ -24346,12 +24298,12 @@
       </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>막대키,폴딩키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>81996-4F700, 81996-4F025</t>
+          <t>81996-4F010, 81996-4F020, 81996-4F000[칩 없음]</t>
         </is>
       </c>
       <c r="J383" s="2" t="n"/>
@@ -24359,17 +24311,17 @@
       <c r="L383" s="2" t="n"/>
       <c r="M383" s="2" t="inlineStr">
         <is>
-          <t>95430-4F500, 95430-4F510, 95430-4F515, 95430-4F000, 95430-4F100, 95430-4F001, 95430-4F101, 95430-4F600</t>
+          <t>81996-4F101[키리모컨], 81996-4F121[키리모컨]</t>
         </is>
       </c>
       <c r="N383" s="2" t="inlineStr">
         <is>
-          <t>95420-D4000, 95420-4F500</t>
+          <t>95440-4F100</t>
         </is>
       </c>
       <c r="O383" s="2" t="inlineStr">
         <is>
-          <t>partsro 95420D4000, partsro 954204F500, cvinfo 2024 포터II LPG 출시</t>
+          <t>partsro 954404F100 포터2 이모빌라이저 모듈 안테나</t>
         </is>
       </c>
       <c r="P383" s="2" t="n"/>
@@ -24387,7 +24339,7 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
@@ -24453,7 +24405,7 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
@@ -24519,7 +24471,7 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
@@ -24585,7 +24537,7 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
@@ -24615,7 +24567,7 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>81996-4F700, 81996-4F025, 81996-4F760</t>
+          <t>81996-4F700, 81996-4F025</t>
         </is>
       </c>
       <c r="J387" s="2" t="n"/>
@@ -24623,7 +24575,7 @@
       <c r="L387" s="2" t="n"/>
       <c r="M387" s="2" t="inlineStr">
         <is>
-          <t>95430-4F500</t>
+          <t>95430-4F500, 95430-4F510, 95430-4F515, 95430-4F000, 95430-4F100, 95430-4F001, 95430-4F101, 95430-4F600</t>
         </is>
       </c>
       <c r="N387" s="2" t="inlineStr">
@@ -24651,7 +24603,7 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
@@ -24717,7 +24669,7 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
@@ -24783,7 +24735,7 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
@@ -24849,17 +24801,17 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D391" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E391" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D391" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E391" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F391" s="3" t="inlineStr">
@@ -24867,48 +24819,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G391" s="8" t="inlineStr">
-        <is>
-          <t>ID46[폴딩키], ID6A[스마트키, 추정]</t>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>ID46[이모빌라이저 사양]</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
         <is>
-          <t>막대키,폴딩키,스마트키</t>
+          <t>막대키,폴딩키</t>
         </is>
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>81996-4F700, 81996-4F025, 81996-4F760, 81996-CN000[스마트키용]</t>
+          <t>81996-4F700, 81996-4F025, 81996-4F760</t>
         </is>
       </c>
       <c r="J391" s="2" t="n"/>
       <c r="K391" s="2" t="n"/>
-      <c r="L391" s="2" t="inlineStr">
-        <is>
-          <t>95440-4FGA0[LPG]</t>
-        </is>
-      </c>
+      <c r="L391" s="2" t="n"/>
       <c r="M391" s="2" t="inlineStr">
         <is>
           <t>95430-4F500</t>
         </is>
       </c>
-      <c r="N391" s="8" t="inlineStr">
+      <c r="N391" s="2" t="inlineStr">
         <is>
           <t>95420-D4000, 95420-4F500</t>
         </is>
       </c>
       <c r="O391" s="2" t="inlineStr">
         <is>
-          <t>cvinfo 2024 포터II, hyundaimotorgroup 2026 포터II, ebay 954404FGA0/81996CN000, 기아 DB 봉고3 2024</t>
-        </is>
-      </c>
-      <c r="P391" s="8" t="inlineStr">
-        <is>
-          <t>LPG 스마트키(95440-4FGA0) 칩 원문 없음 — 비상키 81996-CN000을 같이 쓰는 포터2 일렉트릭 95440-CN100(AES 6A) 기준 추정</t>
-        </is>
-      </c>
+          <t>partsro 95420D4000, partsro 954204F500, cvinfo 2024 포터II LPG 출시</t>
+        </is>
+      </c>
+      <c r="P391" s="2" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -24923,7 +24867,7 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D392" s="5" t="inlineStr">
@@ -24997,7 +24941,7 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D393" s="5" t="inlineStr">
@@ -25066,17 +25010,17 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>포터2 일렉트릭</t>
+          <t>포터2 (HR)</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D394" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D394" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="E394" s="5" t="inlineStr">
@@ -25089,36 +25033,48 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G394" s="2" t="inlineStr">
-        <is>
-          <t>ID6A</t>
+      <c r="G394" s="8" t="inlineStr">
+        <is>
+          <t>ID46[폴딩키], ID6A[스마트키, 추정]</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키,폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>81996-CN000</t>
+          <t>81996-4F700, 81996-4F025, 81996-4F760, 81996-CN000[스마트키용]</t>
         </is>
       </c>
       <c r="J394" s="2" t="n"/>
       <c r="K394" s="2" t="n"/>
       <c r="L394" s="2" t="inlineStr">
         <is>
-          <t>95440-CN000</t>
-        </is>
-      </c>
-      <c r="M394" s="2" t="n"/>
-      <c r="N394" s="2" t="n"/>
+          <t>95440-4FGA0[LPG]</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="inlineStr">
+        <is>
+          <t>95430-4F500</t>
+        </is>
+      </c>
+      <c r="N394" s="8" t="inlineStr">
+        <is>
+          <t>95420-D4000, 95420-4F500</t>
+        </is>
+      </c>
       <c r="O394" s="2" t="inlineStr">
         <is>
-          <t>mk3 Hyundai Porter2 EV 95440-CN000</t>
-        </is>
-      </c>
-      <c r="P394" s="2" t="n"/>
+          <t>cvinfo 2024 포터II, hyundaimotorgroup 2026 포터II, ebay 954404FGA0/81996CN000, 기아 DB 봉고3 2024</t>
+        </is>
+      </c>
+      <c r="P394" s="8" t="inlineStr">
+        <is>
+          <t>LPG 스마트키(95440-4FGA0) 칩 원문 없음 — 비상키 81996-CN000을 같이 쓰는 포터2 일렉트릭 95440-CN100(AES 6A) 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -25133,7 +25089,7 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
@@ -25195,7 +25151,7 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D396" s="4" t="inlineStr">
@@ -25257,7 +25213,7 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -25319,7 +25275,7 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D398" s="4" t="inlineStr">
@@ -25356,14 +25312,14 @@
       <c r="K398" s="2" t="n"/>
       <c r="L398" s="2" t="inlineStr">
         <is>
-          <t>95440-CN000[~2023.1], 95440-CN100[2023.2.1~]</t>
+          <t>95440-CN000</t>
         </is>
       </c>
       <c r="M398" s="2" t="n"/>
       <c r="N398" s="2" t="n"/>
       <c r="O398" s="2" t="inlineStr">
         <is>
-          <t>hellowcar</t>
+          <t>mk3 Hyundai Porter2 EV 95440-CN000</t>
         </is>
       </c>
       <c r="P398" s="2" t="n"/>
@@ -25381,7 +25337,7 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
@@ -25418,7 +25374,7 @@
       <c r="K399" s="2" t="n"/>
       <c r="L399" s="2" t="inlineStr">
         <is>
-          <t>95440-CN100</t>
+          <t>95440-CN000[~2023.1], 95440-CN100[2023.2.1~]</t>
         </is>
       </c>
       <c r="M399" s="2" t="n"/>
@@ -25443,7 +25399,7 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D400" s="4" t="inlineStr">
@@ -25505,7 +25461,7 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
@@ -25557,17 +25513,17 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>제네시스</t>
+          <t>현대</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>제네시스 G80 (DH)</t>
+          <t>포터2 일렉트릭</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D402" s="4" t="inlineStr">
@@ -25587,7 +25543,7 @@
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>ID47(NCF29A1X)</t>
+          <t>ID6A</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
@@ -25597,21 +25553,21 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>81996-B1500</t>
+          <t>81996-CN000</t>
         </is>
       </c>
       <c r="J402" s="2" t="n"/>
       <c r="K402" s="2" t="n"/>
       <c r="L402" s="2" t="inlineStr">
         <is>
-          <t>95440-D2000BLH</t>
+          <t>95440-CN100</t>
         </is>
       </c>
       <c r="M402" s="2" t="n"/>
       <c r="N402" s="2" t="n"/>
       <c r="O402" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 제네시스G80DH 95440D2000BLH/81996B1500, uhs-hardware 2017-2020 D2000</t>
+          <t>hellowcar</t>
         </is>
       </c>
       <c r="P402" s="2" t="n"/>
@@ -25629,7 +25585,7 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
@@ -25673,7 +25629,7 @@
       <c r="N403" s="2" t="n"/>
       <c r="O403" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2017 G80 D2000</t>
+          <t>hellowcar 제네시스G80DH 95440D2000BLH/81996B1500, uhs-hardware 2017-2020 D2000</t>
         </is>
       </c>
       <c r="P403" s="2" t="n"/>
@@ -25691,7 +25647,7 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D404" s="4" t="inlineStr">
@@ -25735,7 +25691,7 @@
       <c r="N404" s="2" t="n"/>
       <c r="O404" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2018 G80</t>
+          <t>remotesandkeys 2017 G80 D2000</t>
         </is>
       </c>
       <c r="P404" s="2" t="n"/>
@@ -25753,7 +25709,7 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
@@ -25797,7 +25753,7 @@
       <c r="N405" s="2" t="n"/>
       <c r="O405" s="2" t="inlineStr">
         <is>
-          <t>royalkeysupply 2017-2020</t>
+          <t>remotesandkeys 2018 G80</t>
         </is>
       </c>
       <c r="P405" s="2" t="n"/>
@@ -25815,7 +25771,7 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D406" s="4" t="inlineStr">
@@ -25859,7 +25815,7 @@
       <c r="N406" s="2" t="n"/>
       <c r="O406" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2020 G80</t>
+          <t>royalkeysupply 2017-2020</t>
         </is>
       </c>
       <c r="P406" s="2" t="n"/>
@@ -25872,7 +25828,7 @@
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>제네시스 G80 (RG3)</t>
+          <t>제네시스 G80 (DH)</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
@@ -25897,7 +25853,7 @@
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>ID47</t>
+          <t>ID47(NCF29A1X)</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
@@ -25905,19 +25861,23 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I407" s="2" t="n"/>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>81996-B1500</t>
+        </is>
+      </c>
       <c r="J407" s="2" t="n"/>
       <c r="K407" s="2" t="n"/>
       <c r="L407" s="2" t="inlineStr">
         <is>
-          <t>95440-T1000[6버튼], 95440-T1010, 95440-T1200, 95440-T1210[8버튼]</t>
+          <t>95440-D2000BLH</t>
         </is>
       </c>
       <c r="M407" s="2" t="n"/>
       <c r="N407" s="2" t="n"/>
       <c r="O407" s="2" t="inlineStr">
         <is>
-          <t>partsro 95440T1210, mk3 Genesis 2021 T1000 ID47, keyecu T1200 ID47</t>
+          <t>remotesandkeys 2020 G80</t>
         </is>
       </c>
       <c r="P407" s="2" t="n"/>
@@ -25935,7 +25895,7 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D408" s="4" t="inlineStr">
@@ -25975,7 +25935,7 @@
       <c r="N408" s="2" t="n"/>
       <c r="O408" s="2" t="inlineStr">
         <is>
-          <t>abkeys 2021-2023 T1210, key4 T1000</t>
+          <t>partsro 95440T1210, mk3 Genesis 2021 T1000 ID47, keyecu T1200 ID47</t>
         </is>
       </c>
       <c r="P408" s="2" t="n"/>
@@ -25993,7 +25953,7 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D409" s="4" t="inlineStr">
@@ -26033,7 +25993,7 @@
       <c r="N409" s="2" t="n"/>
       <c r="O409" s="2" t="inlineStr">
         <is>
-          <t>abkeys 2022+ T1010</t>
+          <t>abkeys 2021-2023 T1210, key4 T1000</t>
         </is>
       </c>
       <c r="P409" s="2" t="n"/>
@@ -26051,7 +26011,7 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D410" s="4" t="inlineStr">
@@ -26091,7 +26051,7 @@
       <c r="N410" s="2" t="n"/>
       <c r="O410" s="2" t="inlineStr">
         <is>
-          <t>abkeys, remotesandkeys</t>
+          <t>abkeys 2022+ T1010</t>
         </is>
       </c>
       <c r="P410" s="2" t="n"/>
@@ -26109,7 +26069,7 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
@@ -26129,7 +26089,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M)</t>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -26142,14 +26102,14 @@
       <c r="K411" s="2" t="n"/>
       <c r="L411" s="2" t="inlineStr">
         <is>
-          <t>95440-T1AB0[7버튼], 95440-T1BB0[5버튼]</t>
+          <t>95440-T1000[6버튼], 95440-T1010, 95440-T1200, 95440-T1210[8버튼]</t>
         </is>
       </c>
       <c r="M411" s="2" t="n"/>
       <c r="N411" s="2" t="n"/>
       <c r="O411" s="2" t="inlineStr">
         <is>
-          <t>abkeys T1BB0 ID4A, yourcarkeyguys 2024-2026 T1AB0</t>
+          <t>abkeys, remotesandkeys</t>
         </is>
       </c>
       <c r="P411" s="2" t="n"/>
@@ -26167,7 +26127,7 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D412" s="4" t="inlineStr">
@@ -26207,7 +26167,7 @@
       <c r="N412" s="2" t="n"/>
       <c r="O412" s="2" t="inlineStr">
         <is>
-          <t>abkeys 2024-2025</t>
+          <t>abkeys T1BB0 ID4A, yourcarkeyguys 2024-2026 T1AB0</t>
         </is>
       </c>
       <c r="P412" s="2" t="n"/>
@@ -26225,7 +26185,7 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D413" s="4" t="inlineStr">
@@ -26265,7 +26225,7 @@
       <c r="N413" s="2" t="n"/>
       <c r="O413" s="2" t="inlineStr">
         <is>
-          <t>yourcarkeyguys 2024-2026</t>
+          <t>abkeys 2024-2025</t>
         </is>
       </c>
       <c r="P413" s="2" t="n"/>
@@ -26278,12 +26238,12 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>제네시스 일렉트리파이드 G80 (RG3 EV)</t>
+          <t>제네시스 G80 (RG3)</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D414" s="4" t="inlineStr">
@@ -26303,7 +26263,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>ID47</t>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26316,14 +26276,14 @@
       <c r="K414" s="2" t="n"/>
       <c r="L414" s="2" t="inlineStr">
         <is>
-          <t>95440-T1210[8버튼]</t>
+          <t>95440-T1AB0[7버튼], 95440-T1BB0[5버튼]</t>
         </is>
       </c>
       <c r="M414" s="2" t="n"/>
       <c r="N414" s="2" t="n"/>
       <c r="O414" s="2" t="inlineStr">
         <is>
-          <t>partsro 95440T1210(전기차 공용)</t>
+          <t>yourcarkeyguys 2024-2026</t>
         </is>
       </c>
       <c r="P414" s="2" t="n"/>
@@ -26341,7 +26301,7 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr">
@@ -26381,7 +26341,7 @@
       <c r="N415" s="2" t="n"/>
       <c r="O415" s="2" t="inlineStr">
         <is>
-          <t>abkeys 2021-2023 T1210</t>
+          <t>partsro 95440T1210(전기차 공용)</t>
         </is>
       </c>
       <c r="P415" s="2" t="n"/>
@@ -26399,7 +26359,7 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D416" s="4" t="inlineStr">
@@ -26439,7 +26399,7 @@
       <c r="N416" s="2" t="n"/>
       <c r="O416" s="2" t="inlineStr">
         <is>
-          <t>abkeys</t>
+          <t>abkeys 2021-2023 T1210</t>
         </is>
       </c>
       <c r="P416" s="2" t="n"/>
@@ -26457,7 +26417,7 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D417" s="4" t="inlineStr">
@@ -26475,9 +26435,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G417" s="8" t="inlineStr">
-        <is>
-          <t>ID4A[추정]</t>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26488,19 +26448,19 @@
       <c r="I417" s="2" t="n"/>
       <c r="J417" s="2" t="n"/>
       <c r="K417" s="2" t="n"/>
-      <c r="L417" s="2" t="n"/>
+      <c r="L417" s="2" t="inlineStr">
+        <is>
+          <t>95440-T1210[8버튼]</t>
+        </is>
+      </c>
       <c r="M417" s="2" t="n"/>
-      <c r="N417" s="13" t="n"/>
+      <c r="N417" s="2" t="n"/>
       <c r="O417" s="2" t="inlineStr">
         <is>
-          <t>eacar 2024 G80 일렉트리파이드 부분변경, partsro 95440T1210 전기차 공용</t>
-        </is>
-      </c>
-      <c r="P417" s="8" t="inlineStr">
-        <is>
-          <t>부분변경 스마트키 품번·칩 원문 없음(모비스 목록의 전기차 공용 95440-T1210은 부분변경 이전 키) — G80 부분변경(ID4A) 기준 추정</t>
-        </is>
-      </c>
+          <t>abkeys</t>
+        </is>
+      </c>
+      <c r="P417" s="2" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -26515,7 +26475,7 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D418" s="4" t="inlineStr">
@@ -26573,7 +26533,7 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
@@ -26626,12 +26586,12 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>제네시스 EQ900/G90 (HI)</t>
+          <t>제네시스 일렉트리파이드 G80 (RG3 EV)</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D420" s="4" t="inlineStr">
@@ -26649,9 +26609,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G420" s="2" t="inlineStr">
-        <is>
-          <t>ID47</t>
+      <c r="G420" s="8" t="inlineStr">
+        <is>
+          <t>ID4A[추정]</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26662,19 +26622,19 @@
       <c r="I420" s="2" t="n"/>
       <c r="J420" s="2" t="n"/>
       <c r="K420" s="2" t="n"/>
-      <c r="L420" s="2" t="inlineStr">
-        <is>
-          <t>95440-D2000NNB</t>
-        </is>
-      </c>
+      <c r="L420" s="2" t="n"/>
       <c r="M420" s="2" t="n"/>
-      <c r="N420" s="2" t="n"/>
+      <c r="N420" s="13" t="n"/>
       <c r="O420" s="2" t="inlineStr">
         <is>
-          <t>transponderisland 2017-2022 G90 D2000NNB, gskeyae D2000NNB</t>
-        </is>
-      </c>
-      <c r="P420" s="2" t="n"/>
+          <t>eacar 2024 G80 일렉트리파이드 부분변경, partsro 95440T1210 전기차 공용</t>
+        </is>
+      </c>
+      <c r="P420" s="8" t="inlineStr">
+        <is>
+          <t>부분변경 스마트키 품번·칩 원문 없음(모비스 목록의 전기차 공용 95440-T1210은 부분변경 이전 키) — G80 부분변경(ID4A) 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -26689,7 +26649,7 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
@@ -26729,7 +26689,7 @@
       <c r="N421" s="2" t="n"/>
       <c r="O421" s="2" t="inlineStr">
         <is>
-          <t>gskeyae 2017-2021</t>
+          <t>transponderisland 2017-2022 G90 D2000NNB, gskeyae D2000NNB</t>
         </is>
       </c>
       <c r="P421" s="2" t="n"/>
@@ -26747,7 +26707,7 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D422" s="4" t="inlineStr">
@@ -26787,7 +26747,7 @@
       <c r="N422" s="2" t="n"/>
       <c r="O422" s="2" t="inlineStr">
         <is>
-          <t>transponderisland</t>
+          <t>gskeyae 2017-2021</t>
         </is>
       </c>
       <c r="P422" s="2" t="n"/>
@@ -26805,7 +26765,7 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
@@ -26845,7 +26805,7 @@
       <c r="N423" s="2" t="n"/>
       <c r="O423" s="2" t="inlineStr">
         <is>
-          <t>yourcarkeyguys 2017-2022</t>
+          <t>transponderisland</t>
         </is>
       </c>
       <c r="P423" s="2" t="n"/>
@@ -26863,7 +26823,7 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D424" s="4" t="inlineStr">
@@ -26896,14 +26856,14 @@
       <c r="K424" s="2" t="n"/>
       <c r="L424" s="2" t="inlineStr">
         <is>
-          <t>95440-D2000NNB, 95440-G9000[4버튼]</t>
+          <t>95440-D2000NNB</t>
         </is>
       </c>
       <c r="M424" s="2" t="n"/>
       <c r="N424" s="2" t="n"/>
       <c r="O424" s="2" t="inlineStr">
         <is>
-          <t>gskeyae G9000 G70 G90</t>
+          <t>yourcarkeyguys 2017-2022</t>
         </is>
       </c>
       <c r="P424" s="2" t="n"/>
@@ -26921,7 +26881,7 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
@@ -26961,7 +26921,7 @@
       <c r="N425" s="2" t="n"/>
       <c r="O425" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2021 G90 D2000NNB</t>
+          <t>gskeyae G9000 G70 G90</t>
         </is>
       </c>
       <c r="P425" s="2" t="n"/>
@@ -26979,7 +26939,7 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D426" s="4" t="inlineStr">
@@ -27019,7 +26979,7 @@
       <c r="N426" s="2" t="n"/>
       <c r="O426" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2021 G90</t>
+          <t>remotesandkeys 2021 G90 D2000NNB</t>
         </is>
       </c>
       <c r="P426" s="2" t="n"/>
@@ -27037,7 +26997,7 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
@@ -27077,7 +27037,7 @@
       <c r="N427" s="2" t="n"/>
       <c r="O427" s="2" t="inlineStr">
         <is>
-          <t>transponderisland 2017-2022</t>
+          <t>remotesandkeys 2021 G90</t>
         </is>
       </c>
       <c r="P427" s="2" t="n"/>
@@ -27090,7 +27050,7 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>제네시스 G90 (RS4)</t>
+          <t>제네시스 EQ900/G90 (HI)</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
@@ -27128,14 +27088,14 @@
       <c r="K428" s="2" t="n"/>
       <c r="L428" s="2" t="inlineStr">
         <is>
-          <t>95440-T4100[7버튼], 95440-T4110[7버튼], 95440-T4120[7버튼]</t>
+          <t>95440-D2000NNB, 95440-G9000[4버튼]</t>
         </is>
       </c>
       <c r="M428" s="2" t="n"/>
       <c r="N428" s="2" t="n"/>
       <c r="O428" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware T4100/T4110/T4120PH3 ID47, auto-keys.eu RS4 T4100 HITAG3</t>
+          <t>transponderisland 2017-2022</t>
         </is>
       </c>
       <c r="P428" s="2" t="n"/>
@@ -27153,7 +27113,7 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
@@ -27193,7 +27153,7 @@
       <c r="N429" s="2" t="n"/>
       <c r="O429" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2023 G90 T4100/T4110</t>
+          <t>uhs-hardware T4100/T4110/T4120PH3 ID47, auto-keys.eu RS4 T4100 HITAG3</t>
         </is>
       </c>
       <c r="P429" s="2" t="n"/>
@@ -27211,7 +27171,7 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D430" s="4" t="inlineStr">
@@ -27251,7 +27211,7 @@
       <c r="N430" s="2" t="n"/>
       <c r="O430" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware 2022-2024</t>
+          <t>remotesandkeys 2023 G90 T4100/T4110</t>
         </is>
       </c>
       <c r="P430" s="2" t="n"/>
@@ -27269,7 +27229,7 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
@@ -27309,7 +27269,7 @@
       <c r="N431" s="2" t="n"/>
       <c r="O431" s="2" t="inlineStr">
         <is>
-          <t>paylesscarkeys 2023-2026 T4100, sffobsinc 2023-2026</t>
+          <t>uhs-hardware 2022-2024</t>
         </is>
       </c>
       <c r="P431" s="2" t="n"/>
@@ -27327,7 +27287,7 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D432" s="4" t="inlineStr">
@@ -27367,7 +27327,7 @@
       <c r="N432" s="2" t="n"/>
       <c r="O432" s="2" t="inlineStr">
         <is>
-          <t>sffobsinc 2023-2026 T4100</t>
+          <t>paylesscarkeys 2023-2026 T4100, sffobsinc 2023-2026</t>
         </is>
       </c>
       <c r="P432" s="2" t="n"/>
@@ -27380,12 +27340,12 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>제네시스 G70 (IK)</t>
+          <t>제네시스 G90 (RS4)</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
@@ -27414,22 +27374,18 @@
         </is>
       </c>
       <c r="I433" s="2" t="n"/>
-      <c r="J433" s="2" t="inlineStr">
-        <is>
-          <t>HY22</t>
-        </is>
-      </c>
+      <c r="J433" s="2" t="n"/>
       <c r="K433" s="2" t="n"/>
       <c r="L433" s="2" t="inlineStr">
         <is>
-          <t>95440-G9000[4버튼]</t>
+          <t>95440-T4100[7버튼], 95440-T4110[7버튼], 95440-T4120[7버튼]</t>
         </is>
       </c>
       <c r="M433" s="2" t="n"/>
       <c r="N433" s="2" t="n"/>
       <c r="O433" s="2" t="inlineStr">
         <is>
-          <t>mk3 G70 2018+ G9000, auto-keys.eu G9000 ID47</t>
+          <t>sffobsinc 2023-2026 T4100</t>
         </is>
       </c>
       <c r="P433" s="2" t="n"/>
@@ -27447,7 +27403,7 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D434" s="4" t="inlineStr">
@@ -27491,7 +27447,7 @@
       <c r="N434" s="2" t="n"/>
       <c r="O434" s="2" t="inlineStr">
         <is>
-          <t>keyless-city 2018-2021</t>
+          <t>mk3 G70 2018+ G9000, auto-keys.eu G9000 ID47</t>
         </is>
       </c>
       <c r="P434" s="2" t="n"/>
@@ -27509,7 +27465,7 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
@@ -27553,7 +27509,7 @@
       <c r="N435" s="2" t="n"/>
       <c r="O435" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2019 G70</t>
+          <t>keyless-city 2018-2021</t>
         </is>
       </c>
       <c r="P435" s="2" t="n"/>
@@ -27571,7 +27527,7 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D436" s="4" t="inlineStr">
@@ -27615,7 +27571,7 @@
       <c r="N436" s="2" t="n"/>
       <c r="O436" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2020 G70, 위키 Genesis G70</t>
+          <t>remotesandkeys 2019 G70</t>
         </is>
       </c>
       <c r="P436" s="2" t="n"/>
@@ -27633,7 +27589,7 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
@@ -27677,7 +27633,7 @@
       <c r="N437" s="2" t="n"/>
       <c r="O437" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2021 G70, paylesscarkeys 2022-2023 Hitag3</t>
+          <t>remotesandkeys 2020 G70, 위키 Genesis G70</t>
         </is>
       </c>
       <c r="P437" s="2" t="n"/>
@@ -27695,7 +27651,7 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D438" s="4" t="inlineStr">
@@ -27739,7 +27695,7 @@
       <c r="N438" s="2" t="n"/>
       <c r="O438" s="2" t="inlineStr">
         <is>
-          <t>paylesscarkeys 2022-2023 G70 Hitag3 ID47</t>
+          <t>remotesandkeys 2021 G70, paylesscarkeys 2022-2023 Hitag3</t>
         </is>
       </c>
       <c r="P438" s="2" t="n"/>
@@ -27757,7 +27713,7 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
@@ -27777,7 +27733,7 @@
       </c>
       <c r="G439" s="2" t="inlineStr">
         <is>
-          <t>ID47[이전 키]</t>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H439" s="2" t="inlineStr">
@@ -27792,12 +27748,16 @@
         </is>
       </c>
       <c r="K439" s="2" t="n"/>
-      <c r="L439" s="2" t="n"/>
+      <c r="L439" s="2" t="inlineStr">
+        <is>
+          <t>95440-G9000[4버튼]</t>
+        </is>
+      </c>
       <c r="M439" s="2" t="n"/>
       <c r="N439" s="2" t="n"/>
       <c r="O439" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware 2023-2025 G9720 ID4A, paylesscarkeys 2022-2023</t>
+          <t>paylesscarkeys 2022-2023 G70 Hitag3 ID47</t>
         </is>
       </c>
       <c r="P439" s="2" t="n"/>
@@ -27835,7 +27795,7 @@
       </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M)[95440-G9720 키]</t>
+          <t>ID47[이전 키]</t>
         </is>
       </c>
       <c r="H440" s="2" t="inlineStr">
@@ -27850,11 +27810,7 @@
         </is>
       </c>
       <c r="K440" s="2" t="n"/>
-      <c r="L440" s="2" t="inlineStr">
-        <is>
-          <t>95440-G9720[5버튼]</t>
-        </is>
-      </c>
+      <c r="L440" s="2" t="n"/>
       <c r="M440" s="2" t="n"/>
       <c r="N440" s="2" t="n"/>
       <c r="O440" s="2" t="inlineStr">
@@ -27877,7 +27833,7 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D441" s="4" t="inlineStr">
@@ -27897,7 +27853,7 @@
       </c>
       <c r="G441" s="2" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M)</t>
+          <t>ID4A(NCF29A1M)[95440-G9720 키]</t>
         </is>
       </c>
       <c r="H441" s="2" t="inlineStr">
@@ -27906,18 +27862,22 @@
         </is>
       </c>
       <c r="I441" s="2" t="n"/>
-      <c r="J441" s="2" t="n"/>
+      <c r="J441" s="2" t="inlineStr">
+        <is>
+          <t>HY22</t>
+        </is>
+      </c>
       <c r="K441" s="2" t="n"/>
       <c r="L441" s="2" t="inlineStr">
         <is>
-          <t>95440-G9720[5버튼], 95440-G9820[5버튼]</t>
+          <t>95440-G9720[5버튼]</t>
         </is>
       </c>
       <c r="M441" s="2" t="n"/>
       <c r="N441" s="2" t="n"/>
       <c r="O441" s="2" t="inlineStr">
         <is>
-          <t>bestkeysupply G9820 ID4A, mk3 2024 G9820</t>
+          <t>uhs-hardware 2023-2025 G9720 ID4A, paylesscarkeys 2022-2023</t>
         </is>
       </c>
       <c r="P441" s="2" t="n"/>
@@ -27935,7 +27895,7 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D442" s="4" t="inlineStr">
@@ -27975,7 +27935,7 @@
       <c r="N442" s="2" t="n"/>
       <c r="O442" s="2" t="inlineStr">
         <is>
-          <t>bestkeysupply 2024-2025 G9720</t>
+          <t>bestkeysupply G9820 ID4A, mk3 2024 G9820</t>
         </is>
       </c>
       <c r="P442" s="2" t="n"/>
@@ -27993,7 +27953,7 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D443" s="4" t="inlineStr">
@@ -28033,7 +27993,7 @@
       <c r="N443" s="2" t="n"/>
       <c r="O443" s="2" t="inlineStr">
         <is>
-          <t>transponderisland 2023-2026 G9820</t>
+          <t>bestkeysupply 2024-2025 G9720</t>
         </is>
       </c>
       <c r="P443" s="2" t="n"/>
@@ -28046,12 +28006,12 @@
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>제네시스 GV80 (JX1)</t>
+          <t>제네시스 G70 (IK)</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D444" s="4" t="inlineStr">
@@ -28071,7 +28031,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>ID47</t>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -28079,23 +28039,19 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I444" s="2" t="inlineStr">
-        <is>
-          <t>81996-T6000</t>
-        </is>
-      </c>
+      <c r="I444" s="2" t="n"/>
       <c r="J444" s="2" t="n"/>
       <c r="K444" s="2" t="n"/>
       <c r="L444" s="2" t="inlineStr">
         <is>
-          <t>95440-T6010, 95440-T6011, 95440-T6014, 95440-T6100, 95440-T6104</t>
+          <t>95440-G9720[5버튼], 95440-G9820[5버튼]</t>
         </is>
       </c>
       <c r="M444" s="2" t="n"/>
       <c r="N444" s="2" t="n"/>
       <c r="O444" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 제네시스GV80 95440T6104/T6014/T6010/T6100/81996T6000/T6011, keyecu T6010 ID47, abkeys T6011</t>
+          <t>transponderisland 2023-2026 G9820</t>
         </is>
       </c>
       <c r="P444" s="2" t="n"/>
@@ -28113,7 +28069,7 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D445" s="4" t="inlineStr">
@@ -28157,7 +28113,7 @@
       <c r="N445" s="2" t="n"/>
       <c r="O445" s="2" t="inlineStr">
         <is>
-          <t>abkeys 2021+ T6011, locksmithkeyless 2021-2024 T6100</t>
+          <t>hellowcar 제네시스GV80 95440T6104/T6014/T6010/T6100/81996T6000/T6011, keyecu T6010 ID47, abkeys T6011</t>
         </is>
       </c>
       <c r="P445" s="2" t="n"/>
@@ -28175,7 +28131,7 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D446" s="4" t="inlineStr">
@@ -28219,7 +28175,7 @@
       <c r="N446" s="2" t="n"/>
       <c r="O446" s="2" t="inlineStr">
         <is>
-          <t>royalkeysupply 2022-2024 T6014</t>
+          <t>abkeys 2021+ T6011, locksmithkeyless 2021-2024 T6100</t>
         </is>
       </c>
       <c r="P446" s="2" t="n"/>
@@ -28237,7 +28193,7 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D447" s="4" t="inlineStr">
@@ -28281,7 +28237,7 @@
       <c r="N447" s="2" t="n"/>
       <c r="O447" s="2" t="inlineStr">
         <is>
-          <t>carandtruckremotes 2024 GV80 T6104</t>
+          <t>royalkeysupply 2022-2024 T6014</t>
         </is>
       </c>
       <c r="P447" s="2" t="n"/>
@@ -28299,7 +28255,7 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D448" s="4" t="inlineStr">
@@ -28319,35 +28275,31 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>ID4A(NCF29A1M)</t>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>스마트키,카드키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>81996-T6500, 81995-T6000</t>
+          <t>81996-T6000</t>
         </is>
       </c>
       <c r="J448" s="2" t="n"/>
-      <c r="K448" s="2" t="inlineStr">
-        <is>
-          <t>95440-T6CA0, 95440-T6CB0</t>
-        </is>
-      </c>
+      <c r="K448" s="2" t="n"/>
       <c r="L448" s="2" t="inlineStr">
         <is>
-          <t>95440-T6AA0[7버튼], 95440-T6AB0, 95440-T6AC0[블랙 패키지], 95440-T6BA0[5버튼], 95440-T6BB0, 95440-T6DA0[5버튼], 95440-T6DB0[5버튼]</t>
+          <t>95440-T6010, 95440-T6011, 95440-T6014, 95440-T6100, 95440-T6104</t>
         </is>
       </c>
       <c r="M448" s="2" t="n"/>
       <c r="N448" s="2" t="n"/>
       <c r="O448" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 제네시스GV80페이스리프트</t>
+          <t>carandtruckremotes 2024 GV80 T6104</t>
         </is>
       </c>
       <c r="P448" s="2" t="n"/>
@@ -28365,7 +28317,7 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D449" s="4" t="inlineStr">
@@ -28431,7 +28383,7 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D450" s="4" t="inlineStr">
@@ -28492,12 +28444,12 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>제네시스 GV80 쿠페 (JX1)</t>
+          <t>제네시스 GV80 (JX1)</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D451" s="4" t="inlineStr">
@@ -28538,14 +28490,14 @@
       </c>
       <c r="L451" s="2" t="inlineStr">
         <is>
-          <t>95440-T6AA0[7버튼], 95440-T6AB0, 95440-T6BA0, 95440-T6BB0[5버튼]</t>
+          <t>95440-T6AA0[7버튼], 95440-T6AB0, 95440-T6AC0[블랙 패키지], 95440-T6BA0[5버튼], 95440-T6BB0, 95440-T6DA0[5버튼], 95440-T6DB0[5버튼]</t>
         </is>
       </c>
       <c r="M451" s="2" t="n"/>
       <c r="N451" s="2" t="n"/>
       <c r="O451" s="2" t="inlineStr">
         <is>
-          <t>검색요약 T6AA0 GV80 Coupe 4A, hellowcar 제네시스GV80페이스리프트, uhs-hardware T6AB0</t>
+          <t>hellowcar 제네시스GV80페이스리프트</t>
         </is>
       </c>
       <c r="P451" s="2" t="n"/>
@@ -28563,7 +28515,7 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D452" s="4" t="inlineStr">
@@ -28629,7 +28581,7 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D453" s="4" t="inlineStr">
@@ -28690,12 +28642,12 @@
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>제네시스 GV70 (JK1)</t>
+          <t>제네시스 GV80 쿠페 (JX1)</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D454" s="4" t="inlineStr">
@@ -28715,27 +28667,35 @@
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>ID47(NCF29A1X)</t>
+          <t>ID4A(NCF29A1M)</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I454" s="2" t="n"/>
+          <t>스마트키,카드키</t>
+        </is>
+      </c>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>81996-T6500, 81995-T6000</t>
+        </is>
+      </c>
       <c r="J454" s="2" t="n"/>
-      <c r="K454" s="2" t="n"/>
+      <c r="K454" s="2" t="inlineStr">
+        <is>
+          <t>95440-T6CA0, 95440-T6CB0</t>
+        </is>
+      </c>
       <c r="L454" s="2" t="inlineStr">
         <is>
-          <t>95440-AR000[6버튼], 95440-AR001[6버튼], 95440-AR011[8버튼]</t>
+          <t>95440-T6AA0[7버튼], 95440-T6AB0, 95440-T6BA0, 95440-T6BB0[5버튼]</t>
         </is>
       </c>
       <c r="M454" s="2" t="n"/>
       <c r="N454" s="2" t="n"/>
       <c r="O454" s="2" t="inlineStr">
         <is>
-          <t>mk3 GV70 AR000, transponderisland AR001, yourcarkeyguys AR011</t>
+          <t>검색요약 T6AA0 GV80 Coupe 4A, hellowcar 제네시스GV80페이스리프트, uhs-hardware T6AB0</t>
         </is>
       </c>
       <c r="P454" s="2" t="n"/>
@@ -28753,7 +28713,7 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D455" s="4" t="inlineStr">
@@ -28793,7 +28753,7 @@
       <c r="N455" s="2" t="n"/>
       <c r="O455" s="2" t="inlineStr">
         <is>
-          <t>key4 GV70 AR000</t>
+          <t>mk3 GV70 AR000, transponderisland AR001, yourcarkeyguys AR011</t>
         </is>
       </c>
       <c r="P455" s="2" t="n"/>
@@ -28811,7 +28771,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D456" s="4" t="inlineStr">
@@ -28851,7 +28811,7 @@
       <c r="N456" s="2" t="n"/>
       <c r="O456" s="2" t="inlineStr">
         <is>
-          <t>keyless-city 2022-2024 AR001, vvdi 2022 GV70</t>
+          <t>key4 GV70 AR000</t>
         </is>
       </c>
       <c r="P456" s="2" t="n"/>
@@ -28869,7 +28829,7 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D457" s="4" t="inlineStr">
@@ -28909,7 +28869,7 @@
       <c r="N457" s="2" t="n"/>
       <c r="O457" s="2" t="inlineStr">
         <is>
-          <t>mykeysupply 2022-2024</t>
+          <t>keyless-city 2022-2024 AR001, vvdi 2022 GV70</t>
         </is>
       </c>
       <c r="P457" s="2" t="n"/>
@@ -28927,7 +28887,7 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D458" s="4" t="inlineStr">
@@ -28985,7 +28945,7 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D459" s="4" t="inlineStr">
@@ -29005,7 +28965,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>ID4A</t>
+          <t>ID47(NCF29A1X)</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -29013,23 +28973,19 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I459" s="2" t="inlineStr">
-        <is>
-          <t>81996-T6500, 81995-T6000</t>
-        </is>
-      </c>
+      <c r="I459" s="2" t="n"/>
       <c r="J459" s="2" t="n"/>
       <c r="K459" s="2" t="n"/>
       <c r="L459" s="2" t="inlineStr">
         <is>
-          <t>95440-ARAA0[5버튼], 95440-ARAB0[5버튼], 95440-ARBA0, 95440-ARBB0, 95440-ARDA0[7버튼], 95440-ARDB0</t>
+          <t>95440-AR000[6버튼], 95440-AR001[6버튼], 95440-AR011[8버튼]</t>
         </is>
       </c>
       <c r="M459" s="2" t="n"/>
       <c r="N459" s="2" t="n"/>
       <c r="O459" s="2" t="inlineStr">
         <is>
-          <t>hellowcar 제네시스GV70 페이스리프트</t>
+          <t>mykeysupply 2022-2024</t>
         </is>
       </c>
       <c r="P459" s="2" t="n"/>
@@ -29047,7 +29003,7 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D460" s="4" t="inlineStr">
@@ -29104,12 +29060,12 @@
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>제네시스 일렉트리파이드 GV70 (JK1 EV)</t>
+          <t>제네시스 GV70 (JK1)</t>
         </is>
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D461" s="4" t="inlineStr">
@@ -29129,7 +29085,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>ID47</t>
+          <t>ID4A</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -29139,21 +29095,21 @@
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
-          <t>81996-AR000</t>
+          <t>81996-T6500, 81995-T6000</t>
         </is>
       </c>
       <c r="J461" s="2" t="n"/>
       <c r="K461" s="2" t="n"/>
       <c r="L461" s="2" t="inlineStr">
         <is>
-          <t>95440-DS000[6버튼], 95440-DS010[8버튼]</t>
+          <t>95440-ARAA0[5버튼], 95440-ARAB0[5버튼], 95440-ARBA0, 95440-ARBB0, 95440-ARDA0[7버튼], 95440-ARDB0</t>
         </is>
       </c>
       <c r="M461" s="2" t="n"/>
       <c r="N461" s="2" t="n"/>
       <c r="O461" s="2" t="inlineStr">
         <is>
-          <t>remotesandkeys 2023 GV70 Electrified DS010 ID47, transponderisland 2023-2025 DS010, noblekeysupply DS000</t>
+          <t>hellowcar 제네시스GV70 페이스리프트</t>
         </is>
       </c>
       <c r="P461" s="2" t="n"/>
@@ -29171,7 +29127,7 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D462" s="4" t="inlineStr">
@@ -29233,7 +29189,7 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D463" s="4" t="inlineStr">
@@ -29295,7 +29251,7 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D464" s="4" t="inlineStr">
@@ -29313,36 +29269,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G464" s="13" t="inlineStr">
-        <is>
-          <t>ID47[95440-DS010 키, ~2025.1]</t>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
         <is>
-          <t>스마트키,카드키</t>
-        </is>
-      </c>
-      <c r="I464" s="2" t="n"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>81996-AR000</t>
+        </is>
+      </c>
       <c r="J464" s="2" t="n"/>
-      <c r="K464" s="2" t="inlineStr">
-        <is>
-          <t>95440-DSBA0, 95440-DSBB0, 95440-DSDA0, 95440-DSDB0</t>
-        </is>
-      </c>
+      <c r="K464" s="2" t="n"/>
       <c r="L464" s="2" t="inlineStr">
         <is>
-          <t>95440-DS010[~2025.1]</t>
+          <t>95440-DS000[6버튼], 95440-DS010[8버튼]</t>
         </is>
       </c>
       <c r="M464" s="2" t="n"/>
-      <c r="N464" s="13" t="n"/>
+      <c r="N464" s="2" t="n"/>
       <c r="O464" s="2" t="inlineStr">
         <is>
-          <t>hyundaimotorgroup GV70 전동화 부분변경 출시, shop.genesis.com Electrified GV70 스마트 카드 키</t>
-        </is>
-      </c>
-      <c r="P464" s="13" t="n"/>
+          <t>remotesandkeys 2023 GV70 Electrified DS010 ID47, transponderisland 2023-2025 DS010, noblekeysupply DS000</t>
+        </is>
+      </c>
+      <c r="P464" s="2" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -29375,9 +29331,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G465" s="8" t="inlineStr">
-        <is>
-          <t>ID4A[부분변경, 추정]</t>
+      <c r="G465" s="13" t="inlineStr">
+        <is>
+          <t>ID47[95440-DS010 키, ~2025.1]</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -29392,7 +29348,11 @@
           <t>95440-DSBA0, 95440-DSBB0, 95440-DSDA0, 95440-DSDB0</t>
         </is>
       </c>
-      <c r="L465" s="2" t="n"/>
+      <c r="L465" s="2" t="inlineStr">
+        <is>
+          <t>95440-DS010[~2025.1]</t>
+        </is>
+      </c>
       <c r="M465" s="2" t="n"/>
       <c r="N465" s="13" t="n"/>
       <c r="O465" s="2" t="inlineStr">
@@ -29400,11 +29360,7 @@
           <t>hyundaimotorgroup GV70 전동화 부분변경 출시, shop.genesis.com Electrified GV70 스마트 카드 키</t>
         </is>
       </c>
-      <c r="P465" s="8" t="inlineStr">
-        <is>
-          <t>부분변경(2025.1) 스마트키 품번·칩 원문 없음 — GV70 부분변경(ID4A) 기준 추정</t>
-        </is>
-      </c>
+      <c r="P465" s="13" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -29419,7 +29375,7 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D466" s="4" t="inlineStr">
@@ -29439,7 +29395,7 @@
       </c>
       <c r="G466" s="8" t="inlineStr">
         <is>
-          <t>ID4A[추정]</t>
+          <t>ID4A[부분변경, 추정]</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
@@ -29464,7 +29420,7 @@
       </c>
       <c r="P466" s="8" t="inlineStr">
         <is>
-          <t>부분변경 스마트키 품번·칩 원문 없음 — GV70 부분변경(ID4A) 기준 추정</t>
+          <t>부분변경(2025.1) 스마트키 품번·칩 원문 없음 — GV70 부분변경(ID4A) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -29476,12 +29432,12 @@
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>제네시스 GV60 (JW1)</t>
+          <t>제네시스 일렉트리파이드 GV70 (JK1 EV)</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D467" s="4" t="inlineStr">
@@ -29499,32 +29455,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G467" s="2" t="inlineStr">
-        <is>
-          <t>ID47(NCF2952X)</t>
+      <c r="G467" s="8" t="inlineStr">
+        <is>
+          <t>ID4A[추정]</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>스마트키,카드키</t>
         </is>
       </c>
       <c r="I467" s="2" t="n"/>
       <c r="J467" s="2" t="n"/>
-      <c r="K467" s="2" t="n"/>
-      <c r="L467" s="2" t="inlineStr">
-        <is>
-          <t>95440-CU100[8버튼], 95440-CU110[8버튼], 95440-CU130[8버튼], 95440-CU200[6버튼], 95440-CU300[8버튼], 95440-CU310</t>
-        </is>
-      </c>
+      <c r="K467" s="2" t="inlineStr">
+        <is>
+          <t>95440-DSBA0, 95440-DSBB0, 95440-DSDA0, 95440-DSDB0</t>
+        </is>
+      </c>
+      <c r="L467" s="2" t="n"/>
       <c r="M467" s="2" t="n"/>
-      <c r="N467" s="2" t="n"/>
+      <c r="N467" s="13" t="n"/>
       <c r="O467" s="2" t="inlineStr">
         <is>
-          <t>abkeys CU110/CU300 ID47, uhs-hardware CU110 ID47</t>
-        </is>
-      </c>
-      <c r="P467" s="2" t="n"/>
+          <t>hyundaimotorgroup GV70 전동화 부분변경 출시, shop.genesis.com Electrified GV70 스마트 카드 키</t>
+        </is>
+      </c>
+      <c r="P467" s="8" t="inlineStr">
+        <is>
+          <t>부분변경 스마트키 품번·칩 원문 없음 — GV70 부분변경(ID4A) 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -29539,7 +29499,7 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D468" s="4" t="inlineStr">
@@ -29579,7 +29539,7 @@
       <c r="N468" s="2" t="n"/>
       <c r="O468" s="2" t="inlineStr">
         <is>
-          <t>mk3 GV60 2022 CU300</t>
+          <t>abkeys CU110/CU300 ID47, uhs-hardware CU110 ID47</t>
         </is>
       </c>
       <c r="P468" s="2" t="n"/>
@@ -29597,7 +29557,7 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D469" s="4" t="inlineStr">
@@ -29637,7 +29597,7 @@
       <c r="N469" s="2" t="n"/>
       <c r="O469" s="2" t="inlineStr">
         <is>
-          <t>americankeysupply 23-24, sffobsinc 2023-2025 CU200</t>
+          <t>mk3 GV60 2022 CU300</t>
         </is>
       </c>
       <c r="P469" s="2" t="n"/>
@@ -29655,7 +29615,7 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D470" s="4" t="inlineStr">
@@ -29695,7 +29655,7 @@
       <c r="N470" s="2" t="n"/>
       <c r="O470" s="2" t="inlineStr">
         <is>
-          <t>dkey1 2023-2024 CU130</t>
+          <t>americankeysupply 23-24, sffobsinc 2023-2025 CU200</t>
         </is>
       </c>
       <c r="P470" s="2" t="n"/>
@@ -29713,7 +29673,7 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D471" s="4" t="inlineStr">
@@ -29753,7 +29713,7 @@
       <c r="N471" s="2" t="n"/>
       <c r="O471" s="2" t="inlineStr">
         <is>
-          <t>locksmithkeyless 2025 GV60 CU130/CU100, 위키 Genesis GV60</t>
+          <t>dkey1 2023-2024 CU130</t>
         </is>
       </c>
       <c r="P471" s="2" t="n"/>
@@ -29771,7 +29731,7 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D472" s="4" t="inlineStr">
@@ -29789,9 +29749,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G472" s="8" t="inlineStr">
-        <is>
-          <t>ID4A[추정]</t>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>ID47(NCF2952X)</t>
         </is>
       </c>
       <c r="H472" s="2" t="inlineStr">
@@ -29804,21 +29764,75 @@
       <c r="K472" s="2" t="n"/>
       <c r="L472" s="2" t="inlineStr">
         <is>
-          <t>95440-CU260[6버튼]</t>
+          <t>95440-CU100[8버튼], 95440-CU110[8버튼], 95440-CU130[8버튼], 95440-CU200[6버튼], 95440-CU300[8버튼], 95440-CU310</t>
         </is>
       </c>
       <c r="M472" s="2" t="n"/>
-      <c r="N472" s="13" t="n"/>
+      <c r="N472" s="2" t="n"/>
       <c r="O472" s="2" t="inlineStr">
         <is>
+          <t>locksmithkeyless 2025 GV60 CU130/CU100, 위키 Genesis GV60</t>
+        </is>
+      </c>
+      <c r="P472" s="2" t="n"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>제네시스</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>제네시스 GV60 (JW1)</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D473" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E473" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F473" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>ID4A(NCF29A1M)</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="n"/>
+      <c r="J473" s="2" t="n"/>
+      <c r="K473" s="2" t="n"/>
+      <c r="L473" s="2" t="inlineStr">
+        <is>
+          <t>95440-CU260[6버튼], FCC TQ8-FOB-4F75M44</t>
+        </is>
+      </c>
+      <c r="M473" s="2" t="n"/>
+      <c r="N473" s="2" t="n"/>
+      <c r="O473" s="2" t="inlineStr">
+        <is>
           <t>royalkeysupply 2026 GV60 CU260</t>
         </is>
       </c>
-      <c r="P472" s="8" t="inlineStr">
-        <is>
-          <t>부분변경 스마트키(95440-CU260) 칩 원문 없음 — 같은 키 모델(FCC TQ8-FOB-4F75M44)을 쓰는 G70·GV80 부분변경 ID4A 기준 추정</t>
-        </is>
-      </c>
+      <c r="P473" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P464"/>
@@ -29832,7 +29846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -30102,185 +30116,199 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>- 코나 N 95440-I3450(ID47), 일렉트리파이드 GV70 95440-DS000·DS010(ID47), GV80 쿠페 95440-T6AA0(ID4A) 품번을 새로 확인.</t>
+          <t>- 스타렉스 2004-2005: 'ID60, ID4C 자료 상충' → 2006년형(2005.7~, 11·12인승)부터 이모빌라이저 기본 적용(한국일보) — 2004년식은 해당 없음, 2005년식은 2005.6 이전·2005.7 이후 두 행. 4C는 해외 카탈로그 표기라 뺌(국내 순정 81996-4A250은 4D60).</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr"/>
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>- 제네시스 GV60 2026: 부분변경 스마트키 95440-CU260의 FCC TQ8-FOB-4F75M44는 G70·GV70·GV80 부분변경과 같은 키 모듈 — HITAG AES ID4A(NCF29A1M)(americankeysupply·keyinnovations) 확인.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>※ 조사하며 확인된 주요 사항</t>
+          <t>- 코나 N 95440-I3450(ID47), 일렉트리파이드 GV70 95440-DS000·DS010(ID47), GV80 쿠페 95440-T6AA0(ID4A) 품번을 새로 확인.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>- 연식별 검색 기록은 research/hyundai/yearly.md, 예전 파일 내용은 research/hyundai/old_rows.tsv에 있습니다.</t>
-        </is>
-      </c>
+      <c r="A43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>- 아반떼 XD는 2005년형(2004.7.1)부터, 싼타페 SM은 2005년형(2004.8.11)부터, 스타렉스는 뉴 스타렉스(2004.1.29)부터 이모빌라이저가 기본 적용됐습니다. 베르나 트랜스폼(2009.6)은 원가절감으로 이모빌라이저가 빠졌습니다.</t>
+          <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>- 아반떼 HD 리모컨은 2008년형까지 447MHz, 2009년형부터 433MHz입니다. 싼타페 CM 스마트키 95440-2B800과 베라크루즈 스마트키는 한국형 447MHz입니다.</t>
+          <t>- 연식별 검색 기록은 research/hyundai/yearly.md, 예전 파일 내용은 research/hyundai/old_rows.tsv에 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>- 그랜드 스타렉스·포터2는 이모빌라이저 사양과 비사양이 공존합니다(키·폴딩키 품번이 따로 있음).</t>
+          <t>- 아반떼 XD는 2005년형(2004.7.1)부터, 싼타페 SM은 2005년형(2004.8.11)부터, 스타렉스는 2006년형(2005.7 출시)부터 11·12인승에 이모빌라이저가 기본 적용됐습니다(한국일보 2005.7.3 '오토파일'). 베르나 트랜스폼(2009.6)은 원가절감으로 이모빌라이저가 빠졌습니다.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>- 칩 세대 흐름: ID46(Hitag2, ~2015년경) → ID8A(DST-AES, LF·AD·i30 PD·i40 후기) / ID47(Hitag3, IG·TL·TM·코나·제네시스) → ID4A(Hitag AES, GN7·DN8 디 엣지·MX5·아이오닉5·제네시스 부분변경) / ID6A(아반떼 CN7·캐스퍼·포터2 일렉트릭).</t>
+          <t>- 아반떼 HD 리모컨은 2008년형까지 447MHz, 2009년형부터 433MHz입니다. 싼타페 CM 스마트키 95440-2B800과 베라크루즈 스마트키는 한국형 447MHz입니다.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="n"/>
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>- 그랜드 스타렉스·포터2는 이모빌라이저 사양과 비사양이 공존합니다(키·폴딩키 품번이 따로 있음).</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
+          <t>- 칩 세대 흐름: ID46(Hitag2, ~2015년경) → ID8A(DST-AES, LF·AD·i30 PD·i40 후기) / ID47(Hitag3, IG·TL·TM·코나·제네시스) → ID4A(Hitag AES, GN7·DN8 디 엣지·MX5·아이오닉5·제네시스 부분변경) / ID6A(아반떼 CN7·캐스퍼·포터2 일렉트릭).</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
-        </is>
-      </c>
+      <c r="A50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
+          <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
+          <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
+          <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+          <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
+          <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="n"/>
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>※ 칩 ID 코드 뜻</t>
+          <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
-        </is>
-      </c>
+      <c r="A58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
+          <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
+          <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
+          <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
+          <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
+          <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
+          <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="14" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>※ 행 구분 규칙</t>
-        </is>
-      </c>
-    </row>
     <row r="67">
-      <c r="A67" s="14" t="inlineStr">
-        <is>
-          <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
-        </is>
-      </c>
+      <c r="A67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>※ 행 구분 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>

--- a/현대_트랜스폰더_칩코드_DB.xlsx
+++ b/현대_트랜스폰더_칩코드_DB.xlsx
@@ -29853,438 +29853,438 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr"/>
+      <c r="A2" s="14" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>- 예전 현대 파일(컬럼 10개, 칩·세부ID·부품번호가 섞인 구조)을 버리고 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같은 컬럼으로 새로 작성했습니다. 칩코드 뒤에 '키종류'를 추가했습니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '현대 쏘나타', '제네시스 G80'처럼 브랜드와 모델명을 함께 검색 가능). 제네시스 브랜드 독립(2015.11) 이후 모델은 '제네시스', 그 이전 현대 제네시스(BH·DH)·제네시스 쿠페는 '현대'입니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다. 예전 파일에서 연식을 나누지 않고 한 줄로 적었던 모델(예: 2006-2010)은 조사 대상에서 뺐습니다(에쿠스·i20·갤로퍼·테라칸·트라제 XG·라비타·클릭·마이티 등).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>- 연식은 실제 국내 판매(출시일) 기준입니다. 풀체인지가 있는 해는 전·후 세대가 각각 한 행씩 있습니다. 후속 없이 단종된 모델의 마지막 연식은 '2019(단종)' 형식입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 카드키는 그랜저 HG·IG, 제네시스 DH의 카드형 스마트키입니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434/447MHz)만 적었습니다. 미국형 315MHz 키(예: 95440-3Q000·95440-3M220·95440-2M350·95440-2V100·95440-4Z200, FCC SY5HMFNA04)는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>- 스마트키에 딸린 비상키(블랭킹키)는 '키블레이드(부품번호)' 칸에 적었습니다. 키리모컨 일체형(81996-4H100 등)은 '폴딩키(부품번호)' 칸에 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템' 칸은 현대모비스 품번이 확인된 차종만 적었습니다(그랜드 스타렉스·포터2 이모빌라이저 모듈 95420-D4000·95420-4F500, 포터2 안테나 95440-4F100).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. hellowcar·partsro(현대모비스 공식 부품몰)는 적용 기간이 적힌 국내 순정 품번의 근거이고, 칩 종류는 대부분 해외 키 판매처(abkeys·mk3·remotesandkeys 등)의 같은 품번 설명을 근거로 했습니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr"/>
+      <c r="A14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값 — 실물 키·VIN으로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — 아반떼 J2(2000) 1행.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>- 주황색으로 남은 행(재조사 후 23행): 부분변경 신형 스마트키 칩 원문이 아직 없는 경우(아이오닉6 2025~, 일렉트리파이드 G80 2024~, 일렉트리파이드 GV70 2025~, GV60 2026, 포터2 LPG 스마트키, 포터2 일렉트릭 CN000), 스타렉스 2004-2005(순정 4D60 키 vs 해외 카탈로그 4C), 베르나 LC(이모빌라이저키 품번이 없어 미적용 추정).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>- 전환 연식은 칩코드 칸에 전·후를 함께 적었습니다(예: 쏘나타 DN8 2023 = ID47(NCF29A1X)[~2023.2], ID4A(NCF29A1M)[디 엣지, 2023.3~]).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>- 칩코드 추가 뜻: ID4C = Texas 4C(고정 코드, 스타렉스 2004-2006 해외 자료), 해당 없음 = 그 연식 국내형에 이모빌라이저가 없음.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr"/>
+      <c r="A21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>※ 예전 현대 파일에서 바로잡은 주요 오류</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>- 쏘나타 LF(2014-2019): ID47 → ID8A(DST-AES). 95440-C1001·C1500 모두 8A.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>- 쏘나타 DN8 2019-2022: ID4A → ID47(NCF29A1X). ID4A는 디 엣지(2023.3~)부터.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>- 아반떼 AD(2015-2020): ID47 → ID8A. 아반떼 CN7·아반떼 N·아이오닉6: ID4A → ID6A. 더 뉴 아반떼(95440-AA500)·아이오닉6(KL000)은 FCC NYOMBEC7FOB2208(MBEC 계열 = CN7 AA000·캐스퍼와 같은 6A 계열)이고 auto-keys·keyshop-online·abkeys가 6A로 일치. 일부 판매처(remotesandkeys)의 '4A' 표기는 같은 키를 4A·6A로 섞어 적어 따르지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>- 투싼 NX4 부분변경(더 뉴 투싼, 2023.11~): 스마트키가 95440-N95xx(ID4A)로 바뀜 — 처음 작성 때 ID47로 잘못 이어 적었던 것을 정정.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>- 그랜저 GN7: 스마트키 품번 95440-BY000 → 95440-N1xxx(N1000·N1050·N1110 등).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>- 제네시스 DH 2013-2014: 'BH 전자장비 유지, ID46(95440-3M220)' → DH는 출시(2013.11)부터 95440-B1200BLH ID47. 95440-3M220은 미국형 315MHz.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>- 제네시스 BH: 95440-3M220(미국형) → 국내 95440-3M010·3M020·3M030. 제네시스 쿠페: 95440-2M350·2M300·3V021(미국형) → 국내 95440-2M050·2M420.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>- 싼타페 DM 2016-2018·맥스크루즈 2016-2019: 'ID46 또는 ID47' → ID46(95440-2W500·B8100 모두 PCF7952A). 싼타페 DM 95440-4Z200은 미국형.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>- 싼타페 SM 2000-2002: 4D60 → 국내 이모빌라이저는 2005년형(2004.8.11)부터 적용, 그 이전은 해당 없음.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>- 투싼 TL: 'ID6E-MA 또는 ID47' → ID47(NCF2952X).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>- 스타리아: ID4A → ID47(NCF29A1X).</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>- 그랜드 스타렉스 2007-2011·포터2 2004-2015: '4D60 또는 미탑재' → 국내 이모빌라이저 사양 키는 ID46(그랜드 스타렉스 블랭킹키 81996-2H010 = 아반떼 HD 공용, 포터2 81996-4F020 = ID46 키블레이드).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>- 베라크루즈 2013-2015: '수출형 ix55 확인 불가' → 국내 판매가 2015년까지 이어짐(95440-3J560 ID46).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>- i40: 품번별로 칩이 다름 — 95440-3Z000(2011.12.15~2012.4.2)은 TMS37126(DST80, ID6E-MA), 3Z001·3Z002 이후는 DST-AES(8A).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>- 그랜저 TG 스마트키 95440-3L100은 TIRIS DST80(ID6E-MA), 이모빌라이저키 81996-3L010은 ID46.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>- 쏘나타 EF·그랜저 XG·싼타페 SM(2005년형~): 현대모비스 순정 이모빌라이저키 81996-38010(4D60). 베르나 MC: 81996-1E010(ID46, 트랜스폼 2009.6부터 이모빌라이저 삭제). 투싼 JM: 81996-2E010(ID46). 스타렉스: 81996-4A250(4D60).</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>- 포터2 스마트키는 2024 포터II LPG(2023.12~)부터(95440-4FGA0). 2020-2023 디젤에는 스마트키가 없어 예전 파일의 95440-4FGA0 기재는 오류.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>- 스타렉스 2004-2005: 'ID60, ID4C 자료 상충' → 2006년형(2005.7~, 11·12인승)부터 이모빌라이저 기본 적용(한국일보) — 2004년식은 해당 없음, 2005년식은 2005.6 이전·2005.7 이후 두 행. 4C는 해외 카탈로그 표기라 뺌(국내 순정 81996-4A250은 4D60).</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>- 제네시스 GV60 2026: 부분변경 스마트키 95440-CU260의 FCC TQ8-FOB-4F75M44는 G70·GV70·GV80 부분변경과 같은 키 모듈 — HITAG AES ID4A(NCF29A1M)(americankeysupply·keyinnovations) 확인.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>- 코나 N 95440-I3450(ID47), 일렉트리파이드 GV70 95440-DS000·DS010(ID47), GV80 쿠페 95440-T6AA0(ID4A) 품번을 새로 확인.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr"/>
+      <c r="A43" s="14" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>- 연식별 검색 기록은 research/hyundai/yearly.md, 예전 파일 내용은 research/hyundai/old_rows.tsv에 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>- 아반떼 XD는 2005년형(2004.7.1)부터, 싼타페 SM은 2005년형(2004.8.11)부터, 스타렉스는 2006년형(2005.7 출시)부터 11·12인승에 이모빌라이저가 기본 적용됐습니다(한국일보 2005.7.3 '오토파일'). 베르나 트랜스폼(2009.6)은 원가절감으로 이모빌라이저가 빠졌습니다.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>- 아반떼 HD 리모컨은 2008년형까지 447MHz, 2009년형부터 433MHz입니다. 싼타페 CM 스마트키 95440-2B800과 베라크루즈 스마트키는 한국형 447MHz입니다.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>- 그랜드 스타렉스·포터2는 이모빌라이저 사양과 비사양이 공존합니다(키·폴딩키 품번이 따로 있음).</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>- 칩 세대 흐름: ID46(Hitag2, ~2015년경) → ID8A(DST-AES, LF·AD·i30 PD·i40 후기) / ID47(Hitag3, IG·TL·TM·코나·제네시스) → ID4A(Hitag AES, GN7·DN8 디 엣지·MX5·아이오닉5·제네시스 부분변경) / ID6A(아반떼 CN7·캐스퍼·포터2 일렉트릭).</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="n"/>
+      <c r="A50" s="14" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n"/>
+      <c r="A58" s="14" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="14" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="14" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="14" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="A64" s="14" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="14" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>

--- a/현대_트랜스폰더_칩코드_DB.xlsx
+++ b/현대_트랜스폰더_칩코드_DB.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K2" s="2" t="n"/>
@@ -748,7 +748,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K3" s="2" t="n"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K4" s="2" t="n"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K6" s="2" t="n"/>
@@ -996,7 +996,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>HYN14R</t>
+          <t>HYN14R, HY15[ILCO]</t>
         </is>
       </c>
       <c r="K7" s="2" t="n"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>HYN14R</t>
+          <t>HYN14R, HY15[ILCO]</t>
         </is>
       </c>
       <c r="K8" s="2" t="n"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>HYN14R</t>
+          <t>HYN14R, HY15[ILCO]</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>HYN14R</t>
+          <t>HYN14R, HY15[ILCO]</t>
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>HYN14R</t>
+          <t>HYN14R, HY15[ILCO]</t>
         </is>
       </c>
       <c r="K11" s="2" t="n"/>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>HYN14R</t>
+          <t>HYN14R, HY15[ILCO]</t>
         </is>
       </c>
       <c r="K12" s="2" t="n"/>
@@ -1414,7 +1414,11 @@
           <t>81996-3S020</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -1480,7 +1484,11 @@
           <t>81996-3S020</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -1546,7 +1554,11 @@
           <t>81996-3S020</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -1612,7 +1624,11 @@
           <t>81996-3S020</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -1678,7 +1694,11 @@
           <t>81996-3S020</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -1744,7 +1764,11 @@
           <t>81996-3S020</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1834,11 @@
           <t>81999-2S040</t>
         </is>
       </c>
-      <c r="J19" s="2" t="n"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -1876,7 +1904,11 @@
           <t>81999-2S040</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -1942,7 +1974,11 @@
           <t>81999-2S040</t>
         </is>
       </c>
-      <c r="J21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -2008,7 +2044,11 @@
           <t>81999-2S040</t>
         </is>
       </c>
-      <c r="J22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -2074,7 +2114,11 @@
           <t>81999-2S040</t>
         </is>
       </c>
-      <c r="J23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -2140,7 +2184,11 @@
           <t>81999-2S040</t>
         </is>
       </c>
-      <c r="J24" s="2" t="n"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
@@ -2206,7 +2254,11 @@
           <t>81996-M5000</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], KK10[ILCO]</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -2268,7 +2320,11 @@
           <t>81996-M5000</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], KK10[ILCO]</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -2330,7 +2386,11 @@
           <t>81996-M5000, 81996-N9000</t>
         </is>
       </c>
-      <c r="J27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], KK10[ILCO]</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -2392,7 +2452,11 @@
           <t>81996-M5000, 81996-N9000</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], KK10[ILCO]</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -2454,7 +2518,11 @@
           <t>81996-N9000, 81996-AA540</t>
         </is>
       </c>
-      <c r="J29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -2516,7 +2584,11 @@
           <t>81996-N9000, 81996-AA540</t>
         </is>
       </c>
-      <c r="J30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
@@ -2578,7 +2650,11 @@
           <t>81996-AA540</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -2640,7 +2716,11 @@
           <t>81996-AA540</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -2702,7 +2782,11 @@
           <t>81996-AA540</t>
         </is>
       </c>
-      <c r="J33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -2766,7 +2850,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K34" s="2" t="n"/>
@@ -2832,7 +2916,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K35" s="2" t="n"/>
@@ -2898,7 +2982,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K36" s="2" t="n"/>
@@ -2964,7 +3048,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K37" s="2" t="n"/>
@@ -3030,7 +3114,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K38" s="2" t="n"/>
@@ -3096,7 +3180,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K39" s="2" t="n"/>
@@ -3160,7 +3244,11 @@
           <t>81996-3L010</t>
         </is>
       </c>
-      <c r="J40" s="2" t="n"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>HY20[ILCO]</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -3226,7 +3314,11 @@
           <t>81996-3L010</t>
         </is>
       </c>
-      <c r="J41" s="2" t="n"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>HY20[ILCO]</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
@@ -3292,7 +3384,11 @@
           <t>81996-3L010</t>
         </is>
       </c>
-      <c r="J42" s="2" t="n"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>HY20[ILCO]</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
@@ -3358,7 +3454,11 @@
           <t>81996-3L010</t>
         </is>
       </c>
-      <c r="J43" s="2" t="n"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>HY20[ILCO]</t>
+        </is>
+      </c>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3424,7 +3524,11 @@
           <t>81996-3L010</t>
         </is>
       </c>
-      <c r="J44" s="2" t="n"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>HY20[ILCO]</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
@@ -3490,7 +3594,11 @@
           <t>81996-3L010</t>
         </is>
       </c>
-      <c r="J45" s="2" t="n"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>HY20[ILCO]</t>
+        </is>
+      </c>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
@@ -3556,7 +3664,11 @@
           <t>81996-3L010</t>
         </is>
       </c>
-      <c r="J46" s="2" t="n"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>HY20[ILCO]</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
@@ -3622,7 +3734,11 @@
           <t>81996-3V040, 81996-3N700</t>
         </is>
       </c>
-      <c r="J47" s="2" t="n"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
@@ -3684,7 +3800,11 @@
           <t>81996-3V040, 81996-3N700</t>
         </is>
       </c>
-      <c r="J48" s="2" t="n"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
@@ -3746,7 +3866,11 @@
           <t>81996-3V040, 81996-3N700</t>
         </is>
       </c>
-      <c r="J49" s="2" t="n"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -3808,7 +3932,11 @@
           <t>81996-3V040, 81996-3N700</t>
         </is>
       </c>
-      <c r="J50" s="2" t="n"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
           <t>95443-3V000</t>
@@ -3874,7 +4002,11 @@
           <t>81996-3V040, 81996-3N700</t>
         </is>
       </c>
-      <c r="J51" s="2" t="n"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
           <t>95443-3V000</t>
@@ -3940,7 +4072,11 @@
           <t>81996-3V040, 81996-3N700</t>
         </is>
       </c>
-      <c r="J52" s="2" t="n"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
           <t>95443-3V000</t>
@@ -4204,7 +4340,11 @@
           <t>81999-G8100, 81996-M5000</t>
         </is>
       </c>
-      <c r="J56" s="2" t="n"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], KK10[ILCO]</t>
+        </is>
+      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
           <t>95443-G80004X[~2019.10], 95443-G85504X[더 뉴 그랜저], 95443-G8510[더 뉴 그랜저]</t>
@@ -4270,7 +4410,11 @@
           <t>81999-G8100, 81996-M5000</t>
         </is>
       </c>
-      <c r="J57" s="2" t="n"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], KK10[ILCO]</t>
+        </is>
+      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
           <t>95443-G80004X[~2019.10], 95443-G85504X[더 뉴 그랜저], 95443-G8510[더 뉴 그랜저]</t>
@@ -4336,7 +4480,11 @@
           <t>81999-G8100, 81996-M5000</t>
         </is>
       </c>
-      <c r="J58" s="2" t="n"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], KK10[ILCO]</t>
+        </is>
+      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
           <t>95443-G80004X[~2019.10], 95443-G85504X[더 뉴 그랜저], 95443-G8510[더 뉴 그랜저]</t>
@@ -4402,7 +4550,11 @@
           <t>81999-G8100, 81996-M5000</t>
         </is>
       </c>
-      <c r="J59" s="2" t="n"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], KK10[ILCO]</t>
+        </is>
+      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
           <t>95443-G80004X[~2019.10], 95443-G85504X[더 뉴 그랜저], 95443-G8510[더 뉴 그랜저]</t>
@@ -4468,7 +4620,11 @@
           <t>81996-KL010, 81995-N1000</t>
         </is>
       </c>
-      <c r="J60" s="2" t="n"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
@@ -4530,7 +4686,11 @@
           <t>81996-KL010, 81995-N1000</t>
         </is>
       </c>
-      <c r="J61" s="2" t="n"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
@@ -4592,7 +4752,11 @@
           <t>81996-KL010, 81995-N1000</t>
         </is>
       </c>
-      <c r="J62" s="2" t="n"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
@@ -4654,7 +4818,11 @@
           <t>81996-KL010, 81995-N1000</t>
         </is>
       </c>
-      <c r="J63" s="2" t="n"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
@@ -4716,7 +4884,11 @@
           <t>81996-KL010, 81995-N1000</t>
         </is>
       </c>
-      <c r="J64" s="2" t="n"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
@@ -5224,7 +5396,11 @@
           <t>81996-2H010[이모빌라이저키], 81996-2H000[칩 없음, 2006.11~]</t>
         </is>
       </c>
-      <c r="J74" s="2" t="n"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="2" t="inlineStr">
@@ -5286,7 +5462,11 @@
           <t>81996-2H010[이모빌라이저키], 81996-2H000[칩 없음, 2006.11~]</t>
         </is>
       </c>
-      <c r="J75" s="2" t="n"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="2" t="inlineStr">
@@ -5348,7 +5528,11 @@
           <t>81996-2H010[이모빌라이저키], 81996-2H000[칩 없음, 2006.11~]</t>
         </is>
       </c>
-      <c r="J76" s="2" t="n"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="n"/>
       <c r="M76" s="2" t="inlineStr">
@@ -5410,7 +5594,11 @@
           <t>81996-2H010[이모빌라이저키], 81996-2H000[칩 없음], 81996-2H020[스마트키용]</t>
         </is>
       </c>
-      <c r="J77" s="2" t="n"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K77" s="2" t="n"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -5476,7 +5664,11 @@
           <t>81996-2H010[이모빌라이저키], 81996-2H000[칩 없음], 81996-2H020[스마트키용]</t>
         </is>
       </c>
-      <c r="J78" s="2" t="n"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
@@ -5728,7 +5920,11 @@
           <t>81996-B4520</t>
         </is>
       </c>
-      <c r="J82" s="2" t="n"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
@@ -5794,7 +5990,11 @@
           <t>81996-B4520</t>
         </is>
       </c>
-      <c r="J83" s="2" t="n"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K83" s="2" t="n"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
@@ -5860,7 +6060,11 @@
           <t>81996-B4520</t>
         </is>
       </c>
-      <c r="J84" s="2" t="n"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K84" s="2" t="n"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
@@ -5926,7 +6130,11 @@
           <t>81996-B4520</t>
         </is>
       </c>
-      <c r="J85" s="2" t="n"/>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K85" s="2" t="n"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
@@ -5992,7 +6200,11 @@
           <t>81996-B4520</t>
         </is>
       </c>
-      <c r="J86" s="2" t="n"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K86" s="2" t="n"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
@@ -6058,7 +6270,11 @@
           <t>81996-B4520</t>
         </is>
       </c>
-      <c r="J87" s="2" t="n"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K87" s="2" t="n"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
@@ -6124,7 +6340,11 @@
           <t>81996-B4520</t>
         </is>
       </c>
-      <c r="J88" s="2" t="n"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K88" s="2" t="n"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
@@ -6190,7 +6410,11 @@
           <t>81996-B4520</t>
         </is>
       </c>
-      <c r="J89" s="2" t="n"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K89" s="2" t="n"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
@@ -6256,7 +6480,11 @@
           <t>81996-B4520</t>
         </is>
       </c>
-      <c r="J90" s="2" t="n"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>HY15[ILCO]</t>
+        </is>
+      </c>
       <c r="K90" s="2" t="n"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
@@ -6508,7 +6736,11 @@
           <t>81999-G3020, 81996-AA540, 81995-AA500</t>
         </is>
       </c>
-      <c r="J94" s="2" t="n"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K94" s="2" t="n"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
@@ -6570,7 +6802,11 @@
           <t>81996-AA540, 81995-AA500</t>
         </is>
       </c>
-      <c r="J95" s="2" t="n"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K95" s="2" t="n"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
@@ -6632,7 +6868,11 @@
           <t>81996-AA540, 81995-AA500</t>
         </is>
       </c>
-      <c r="J96" s="2" t="n"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K96" s="2" t="n"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
@@ -6694,7 +6934,11 @@
           <t>81996-AA540, 81995-AA500</t>
         </is>
       </c>
-      <c r="J97" s="2" t="n"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K97" s="2" t="n"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
@@ -6930,7 +7174,11 @@
           <t>81996-AA540</t>
         </is>
       </c>
-      <c r="J101" s="2" t="n"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K101" s="2" t="n"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
@@ -6992,7 +7240,11 @@
           <t>81996-AA540</t>
         </is>
       </c>
-      <c r="J102" s="2" t="n"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K102" s="2" t="n"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
@@ -7054,7 +7306,11 @@
           <t>81996-AA540</t>
         </is>
       </c>
-      <c r="J103" s="2" t="n"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K103" s="2" t="n"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
@@ -9462,7 +9718,11 @@
           <t>81996-3Z020</t>
         </is>
       </c>
-      <c r="J143" s="2" t="n"/>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K143" s="2" t="n"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
@@ -9524,7 +9784,11 @@
           <t>81996-3Z020</t>
         </is>
       </c>
-      <c r="J144" s="2" t="n"/>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K144" s="2" t="n"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
@@ -9586,7 +9850,11 @@
           <t>81996-3Z020</t>
         </is>
       </c>
-      <c r="J145" s="2" t="n"/>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K145" s="2" t="n"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
@@ -9648,7 +9916,11 @@
           <t>81996-3Z020</t>
         </is>
       </c>
-      <c r="J146" s="2" t="n"/>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K146" s="2" t="n"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
@@ -9710,7 +9982,11 @@
           <t>81996-3Z020</t>
         </is>
       </c>
-      <c r="J147" s="2" t="n"/>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K147" s="2" t="n"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
@@ -9772,7 +10048,11 @@
           <t>81996-3Z020</t>
         </is>
       </c>
-      <c r="J148" s="2" t="n"/>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K148" s="2" t="n"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
@@ -9834,7 +10114,11 @@
           <t>81996-3Z020</t>
         </is>
       </c>
-      <c r="J149" s="2" t="n"/>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K149" s="2" t="n"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
@@ -9896,7 +10180,11 @@
           <t>81996-3Z020</t>
         </is>
       </c>
-      <c r="J150" s="2" t="n"/>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K150" s="2" t="n"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
@@ -9958,7 +10246,11 @@
           <t>81996-3Z020</t>
         </is>
       </c>
-      <c r="J151" s="2" t="n"/>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K151" s="2" t="n"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
@@ -10020,7 +10312,11 @@
           <t>81996-3Z020</t>
         </is>
       </c>
-      <c r="J152" s="2" t="n"/>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K152" s="2" t="n"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
@@ -10822,7 +11118,11 @@
           <t>81996-3N700</t>
         </is>
       </c>
-      <c r="J165" s="2" t="n"/>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K165" s="2" t="n"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
@@ -10884,7 +11184,11 @@
           <t>81996-3N700</t>
         </is>
       </c>
-      <c r="J166" s="2" t="n"/>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K166" s="2" t="n"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
@@ -10946,7 +11250,11 @@
           <t>81996-3N700</t>
         </is>
       </c>
-      <c r="J167" s="2" t="n"/>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K167" s="2" t="n"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
@@ -11008,7 +11316,11 @@
           <t>81996-3N700</t>
         </is>
       </c>
-      <c r="J168" s="2" t="n"/>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K168" s="2" t="n"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
@@ -11442,7 +11754,11 @@
           <t>81996-B1000</t>
         </is>
       </c>
-      <c r="J175" s="2" t="n"/>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO], KIA9[Silca]</t>
+        </is>
+      </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
           <t>95443-B1000</t>
@@ -11508,7 +11824,11 @@
           <t>81996-B1000</t>
         </is>
       </c>
-      <c r="J176" s="2" t="n"/>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO], KIA9[Silca]</t>
+        </is>
+      </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
           <t>95443-B1000</t>
@@ -11574,7 +11894,11 @@
           <t>81996-B1000, 81996-B1010</t>
         </is>
       </c>
-      <c r="J177" s="2" t="n"/>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO], KIA9[Silca]</t>
+        </is>
+      </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
           <t>95443-B1000, 95443-B1010</t>
@@ -11892,7 +12216,11 @@
           <t>81996-2M020</t>
         </is>
       </c>
-      <c r="J182" s="2" t="n"/>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>HY15R[ILCO], HY17[ILCO]</t>
+        </is>
+      </c>
       <c r="K182" s="2" t="n"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
@@ -11958,7 +12286,11 @@
           <t>81996-2M020</t>
         </is>
       </c>
-      <c r="J183" s="2" t="n"/>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>HY15R[ILCO], HY17[ILCO]</t>
+        </is>
+      </c>
       <c r="K183" s="2" t="n"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
@@ -12024,7 +12356,11 @@
           <t>81996-2M020</t>
         </is>
       </c>
-      <c r="J184" s="2" t="n"/>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>HY15R[ILCO], HY17[ILCO]</t>
+        </is>
+      </c>
       <c r="K184" s="2" t="n"/>
       <c r="L184" s="2" t="inlineStr">
         <is>
@@ -12090,7 +12426,11 @@
           <t>81996-2M020</t>
         </is>
       </c>
-      <c r="J185" s="2" t="n"/>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>HY15R[ILCO], HY17[ILCO]</t>
+        </is>
+      </c>
       <c r="K185" s="2" t="n"/>
       <c r="L185" s="2" t="inlineStr">
         <is>
@@ -12156,7 +12496,11 @@
           <t>81996-2M020</t>
         </is>
       </c>
-      <c r="J186" s="2" t="n"/>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>HY15R[ILCO], HY17[ILCO]</t>
+        </is>
+      </c>
       <c r="K186" s="2" t="n"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
@@ -12222,7 +12566,11 @@
           <t>81996-2M020</t>
         </is>
       </c>
-      <c r="J187" s="2" t="n"/>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>HY15R[ILCO], HY17[ILCO]</t>
+        </is>
+      </c>
       <c r="K187" s="2" t="n"/>
       <c r="L187" s="2" t="inlineStr">
         <is>
@@ -12722,7 +13070,11 @@
           <t>81996-S1030</t>
         </is>
       </c>
-      <c r="J195" s="2" t="n"/>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K195" s="2" t="n"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
@@ -12784,7 +13136,11 @@
           <t>81996-S1030</t>
         </is>
       </c>
-      <c r="J196" s="2" t="n"/>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K196" s="2" t="n"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
@@ -12846,7 +13202,11 @@
           <t>81996-S1030</t>
         </is>
       </c>
-      <c r="J197" s="2" t="n"/>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K197" s="2" t="n"/>
       <c r="L197" s="2" t="inlineStr">
         <is>
@@ -13314,7 +13674,11 @@
           <t>81996-KL010</t>
         </is>
       </c>
-      <c r="J205" s="2" t="n"/>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K205" s="2" t="n"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
@@ -13376,7 +13740,11 @@
           <t>81996-KL010</t>
         </is>
       </c>
-      <c r="J206" s="2" t="n"/>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K206" s="2" t="n"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
@@ -13438,7 +13806,11 @@
           <t>81996-KL010</t>
         </is>
       </c>
-      <c r="J207" s="2" t="n"/>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K207" s="2" t="n"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
@@ -13500,7 +13872,11 @@
           <t>81996-KL010</t>
         </is>
       </c>
-      <c r="J208" s="2" t="n"/>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K208" s="2" t="n"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
@@ -13566,7 +13942,11 @@
           <t>81996-KL010</t>
         </is>
       </c>
-      <c r="J209" s="2" t="n"/>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K209" s="2" t="n"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
@@ -13902,7 +14282,7 @@
       <c r="I216" s="2" t="n"/>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K216" s="2" t="n"/>
@@ -13964,7 +14344,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K217" s="2" t="n"/>
@@ -14026,7 +14406,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>HYN7</t>
+          <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
         </is>
       </c>
       <c r="K218" s="2" t="n"/>
@@ -14642,7 +15022,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J227" s="2" t="n"/>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K227" s="2" t="n"/>
       <c r="L227" s="2" t="inlineStr">
         <is>
@@ -14704,7 +15088,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J228" s="2" t="n"/>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K228" s="2" t="n"/>
       <c r="L228" s="2" t="inlineStr">
         <is>
@@ -14766,7 +15154,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J229" s="2" t="n"/>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K229" s="2" t="n"/>
       <c r="L229" s="2" t="inlineStr">
         <is>
@@ -14828,7 +15220,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J230" s="2" t="n"/>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K230" s="2" t="n"/>
       <c r="L230" s="2" t="inlineStr">
         <is>
@@ -14890,7 +15286,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J231" s="2" t="n"/>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K231" s="2" t="n"/>
       <c r="L231" s="2" t="inlineStr">
         <is>
@@ -14952,7 +15352,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J232" s="2" t="n"/>
+      <c r="J232" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K232" s="2" t="n"/>
       <c r="L232" s="2" t="inlineStr">
         <is>
@@ -15014,7 +15418,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J233" s="2" t="n"/>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K233" s="2" t="n"/>
       <c r="L233" s="2" t="inlineStr">
         <is>
@@ -15200,7 +15608,11 @@
           <t>81996-S1020, 81996-S1030</t>
         </is>
       </c>
-      <c r="J236" s="2" t="n"/>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K236" s="2" t="n"/>
       <c r="L236" s="2" t="inlineStr">
         <is>
@@ -15262,7 +15674,11 @@
           <t>81996-S1020, 81996-S1030</t>
         </is>
       </c>
-      <c r="J237" s="2" t="n"/>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K237" s="2" t="n"/>
       <c r="L237" s="2" t="inlineStr">
         <is>
@@ -15324,7 +15740,11 @@
           <t>81996-S1030</t>
         </is>
       </c>
-      <c r="J238" s="2" t="n"/>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K238" s="2" t="n"/>
       <c r="L238" s="2" t="inlineStr">
         <is>
@@ -15386,7 +15806,11 @@
           <t>81996-S1030</t>
         </is>
       </c>
-      <c r="J239" s="2" t="n"/>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K239" s="2" t="n"/>
       <c r="L239" s="2" t="inlineStr">
         <is>
@@ -15448,7 +15872,11 @@
           <t>81996-KL010</t>
         </is>
       </c>
-      <c r="J240" s="2" t="n"/>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K240" s="2" t="n"/>
       <c r="L240" s="2" t="inlineStr">
         <is>
@@ -15510,7 +15938,11 @@
           <t>81996-KL010</t>
         </is>
       </c>
-      <c r="J241" s="2" t="n"/>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K241" s="2" t="n"/>
       <c r="L241" s="2" t="inlineStr">
         <is>
@@ -15572,7 +16004,11 @@
           <t>81996-KL010</t>
         </is>
       </c>
-      <c r="J242" s="2" t="n"/>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K242" s="2" t="n"/>
       <c r="L242" s="2" t="inlineStr">
         <is>
@@ -15634,7 +16070,11 @@
           <t>81996-KL010</t>
         </is>
       </c>
-      <c r="J243" s="2" t="n"/>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>HY18[ILCO]</t>
+        </is>
+      </c>
       <c r="K243" s="2" t="n"/>
       <c r="L243" s="2" t="inlineStr">
         <is>
@@ -15944,7 +16384,11 @@
           <t>81996-S1020, 81996-S1030</t>
         </is>
       </c>
-      <c r="J248" s="2" t="n"/>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K248" s="2" t="n"/>
       <c r="L248" s="2" t="inlineStr">
         <is>
@@ -16006,7 +16450,11 @@
           <t>81996-S1030</t>
         </is>
       </c>
-      <c r="J249" s="2" t="n"/>
+      <c r="J249" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K249" s="2" t="n"/>
       <c r="L249" s="2" t="inlineStr">
         <is>
@@ -16068,7 +16516,11 @@
           <t>81996-S1030</t>
         </is>
       </c>
-      <c r="J250" s="2" t="n"/>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K250" s="2" t="n"/>
       <c r="L250" s="2" t="inlineStr">
         <is>
@@ -17060,7 +17512,11 @@
           <t>81996-D3300</t>
         </is>
       </c>
-      <c r="J266" s="2" t="n"/>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K266" s="2" t="n"/>
       <c r="L266" s="2" t="inlineStr">
         <is>
@@ -17122,7 +17578,11 @@
           <t>81996-D3300</t>
         </is>
       </c>
-      <c r="J267" s="2" t="n"/>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K267" s="2" t="n"/>
       <c r="L267" s="2" t="inlineStr">
         <is>
@@ -17184,7 +17644,11 @@
           <t>81996-D3300</t>
         </is>
       </c>
-      <c r="J268" s="2" t="n"/>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K268" s="2" t="n"/>
       <c r="L268" s="2" t="inlineStr">
         <is>
@@ -17246,7 +17710,11 @@
           <t>81996-D3300</t>
         </is>
       </c>
-      <c r="J269" s="2" t="n"/>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K269" s="2" t="n"/>
       <c r="L269" s="2" t="inlineStr">
         <is>
@@ -17308,7 +17776,11 @@
           <t>81996-D3300</t>
         </is>
       </c>
-      <c r="J270" s="2" t="n"/>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K270" s="2" t="n"/>
       <c r="L270" s="2" t="inlineStr">
         <is>
@@ -17370,7 +17842,11 @@
           <t>81996-D3300</t>
         </is>
       </c>
-      <c r="J271" s="2" t="n"/>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K271" s="2" t="n"/>
       <c r="L271" s="2" t="inlineStr">
         <is>
@@ -18576,7 +19052,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J290" s="2" t="n"/>
+      <c r="J290" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K290" s="2" t="n"/>
       <c r="L290" s="2" t="inlineStr">
         <is>
@@ -18638,7 +19118,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J291" s="2" t="n"/>
+      <c r="J291" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K291" s="2" t="n"/>
       <c r="L291" s="2" t="inlineStr">
         <is>
@@ -18700,7 +19184,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J292" s="2" t="n"/>
+      <c r="J292" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K292" s="2" t="n"/>
       <c r="L292" s="2" t="inlineStr">
         <is>
@@ -18762,7 +19250,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J293" s="2" t="n"/>
+      <c r="J293" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K293" s="2" t="n"/>
       <c r="L293" s="2" t="inlineStr">
         <is>
@@ -18824,7 +19316,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J294" s="2" t="n"/>
+      <c r="J294" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K294" s="2" t="n"/>
       <c r="L294" s="2" t="inlineStr">
         <is>
@@ -18886,7 +19382,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J295" s="2" t="n"/>
+      <c r="J295" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K295" s="2" t="n"/>
       <c r="L295" s="2" t="inlineStr">
         <is>
@@ -18948,7 +19448,11 @@
           <t>81996-2W040</t>
         </is>
       </c>
-      <c r="J296" s="2" t="n"/>
+      <c r="J296" s="2" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO], HYN17R[Silca], HY-19[JMA]</t>
+        </is>
+      </c>
       <c r="K296" s="2" t="n"/>
       <c r="L296" s="2" t="inlineStr">
         <is>
@@ -19010,7 +19514,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J297" s="2" t="n"/>
+      <c r="J297" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K297" s="2" t="n"/>
       <c r="L297" s="2" t="inlineStr">
         <is>
@@ -19072,7 +19580,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J298" s="2" t="n"/>
+      <c r="J298" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K298" s="2" t="n"/>
       <c r="L298" s="2" t="inlineStr">
         <is>
@@ -19134,7 +19646,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J299" s="2" t="n"/>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K299" s="2" t="n"/>
       <c r="L299" s="2" t="inlineStr">
         <is>
@@ -19196,7 +19712,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J300" s="2" t="n"/>
+      <c r="J300" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K300" s="2" t="n"/>
       <c r="L300" s="2" t="inlineStr">
         <is>
@@ -19258,7 +19778,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J301" s="2" t="n"/>
+      <c r="J301" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K301" s="2" t="n"/>
       <c r="L301" s="2" t="inlineStr">
         <is>
@@ -19320,7 +19844,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J302" s="2" t="n"/>
+      <c r="J302" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K302" s="2" t="n"/>
       <c r="L302" s="2" t="inlineStr">
         <is>
@@ -19382,7 +19910,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J303" s="2" t="n"/>
+      <c r="J303" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K303" s="2" t="n"/>
       <c r="L303" s="2" t="inlineStr">
         <is>
@@ -19444,7 +19976,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J304" s="2" t="n"/>
+      <c r="J304" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K304" s="2" t="n"/>
       <c r="L304" s="2" t="inlineStr">
         <is>
@@ -19506,7 +20042,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J305" s="2" t="n"/>
+      <c r="J305" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K305" s="2" t="n"/>
       <c r="L305" s="2" t="inlineStr">
         <is>
@@ -19568,7 +20108,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J306" s="2" t="n"/>
+      <c r="J306" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K306" s="2" t="n"/>
       <c r="L306" s="2" t="inlineStr">
         <is>
@@ -20094,7 +20638,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J315" s="2" t="n"/>
+      <c r="J315" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K315" s="2" t="n"/>
       <c r="L315" s="2" t="inlineStr">
         <is>
@@ -20156,7 +20704,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J316" s="2" t="n"/>
+      <c r="J316" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K316" s="2" t="n"/>
       <c r="L316" s="2" t="inlineStr">
         <is>
@@ -20218,7 +20770,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J317" s="2" t="n"/>
+      <c r="J317" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K317" s="2" t="n"/>
       <c r="L317" s="2" t="inlineStr">
         <is>
@@ -20280,7 +20836,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J318" s="2" t="n"/>
+      <c r="J318" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K318" s="2" t="n"/>
       <c r="L318" s="2" t="inlineStr">
         <is>
@@ -20342,7 +20902,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J319" s="2" t="n"/>
+      <c r="J319" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K319" s="2" t="n"/>
       <c r="L319" s="2" t="inlineStr">
         <is>
@@ -20404,7 +20968,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J320" s="2" t="n"/>
+      <c r="J320" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K320" s="2" t="n"/>
       <c r="L320" s="2" t="inlineStr">
         <is>
@@ -20466,7 +21034,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J321" s="2" t="n"/>
+      <c r="J321" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K321" s="2" t="n"/>
       <c r="L321" s="2" t="inlineStr">
         <is>
@@ -20528,7 +21100,11 @@
           <t>81996-J9020</t>
         </is>
       </c>
-      <c r="J322" s="2" t="n"/>
+      <c r="J322" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K322" s="2" t="n"/>
       <c r="L322" s="2" t="inlineStr">
         <is>
@@ -21150,7 +21726,7 @@
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
-          <t>HY22</t>
+          <t>HY22, LXP90[ILCO], KK10[ILCO]</t>
         </is>
       </c>
       <c r="K332" s="2" t="n"/>
@@ -21216,7 +21792,7 @@
       </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>HY22</t>
+          <t>HY22, LXP90[ILCO], KK10[ILCO]</t>
         </is>
       </c>
       <c r="K333" s="2" t="n"/>
@@ -21282,7 +21858,7 @@
       </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
-          <t>HY22</t>
+          <t>HY22, LXP90[ILCO], KK10[ILCO]</t>
         </is>
       </c>
       <c r="K334" s="2" t="n"/>
@@ -21348,7 +21924,7 @@
       </c>
       <c r="J335" s="2" t="inlineStr">
         <is>
-          <t>HY22</t>
+          <t>HY22, LXP90[ILCO], KK10[ILCO]</t>
         </is>
       </c>
       <c r="K335" s="2" t="n"/>
@@ -21414,7 +21990,7 @@
       </c>
       <c r="J336" s="2" t="inlineStr">
         <is>
-          <t>HY22</t>
+          <t>HY22, LXP90[ILCO], KK10[ILCO]</t>
         </is>
       </c>
       <c r="K336" s="2" t="n"/>
@@ -21480,7 +22056,7 @@
       </c>
       <c r="J337" s="2" t="inlineStr">
         <is>
-          <t>HY22</t>
+          <t>HY22, LXP90[ILCO], KK10[ILCO]</t>
         </is>
       </c>
       <c r="K337" s="2" t="n"/>
@@ -21546,7 +22122,7 @@
       </c>
       <c r="J338" s="2" t="inlineStr">
         <is>
-          <t>HY22</t>
+          <t>HY22, LXP90[ILCO], KK10[ILCO]</t>
         </is>
       </c>
       <c r="K338" s="2" t="n"/>
@@ -21612,7 +22188,7 @@
       </c>
       <c r="J339" s="2" t="inlineStr">
         <is>
-          <t>HY22</t>
+          <t>HY22, LXP90[ILCO], KK10[ILCO]</t>
         </is>
       </c>
       <c r="K339" s="2" t="n"/>
@@ -21676,7 +22252,11 @@
           <t>81996-AA540</t>
         </is>
       </c>
-      <c r="J340" s="2" t="n"/>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K340" s="2" t="n"/>
       <c r="L340" s="2" t="inlineStr">
         <is>
@@ -21738,7 +22318,11 @@
           <t>81996-AA540</t>
         </is>
       </c>
-      <c r="J341" s="2" t="n"/>
+      <c r="J341" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K341" s="2" t="n"/>
       <c r="L341" s="2" t="inlineStr">
         <is>
@@ -23184,7 +23768,11 @@
           <t>81996-L1100, 81996-M5000</t>
         </is>
       </c>
-      <c r="J366" s="2" t="n"/>
+      <c r="J366" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], KK10[ILCO]</t>
+        </is>
+      </c>
       <c r="K366" s="2" t="n"/>
       <c r="L366" s="2" t="inlineStr">
         <is>
@@ -23250,7 +23838,11 @@
           <t>81996-L1100, 81996-M5000</t>
         </is>
       </c>
-      <c r="J367" s="2" t="n"/>
+      <c r="J367" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], KK10[ILCO]</t>
+        </is>
+      </c>
       <c r="K367" s="2" t="n"/>
       <c r="L367" s="2" t="inlineStr">
         <is>
@@ -23316,7 +23908,11 @@
           <t>81996-M5000, 81996-AA540</t>
         </is>
       </c>
-      <c r="J368" s="2" t="n"/>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], KK10[ILCO], KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K368" s="2" t="n"/>
       <c r="L368" s="2" t="inlineStr">
         <is>
@@ -23382,7 +23978,11 @@
           <t>81996-AA540</t>
         </is>
       </c>
-      <c r="J369" s="2" t="n"/>
+      <c r="J369" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K369" s="2" t="n"/>
       <c r="L369" s="2" t="inlineStr">
         <is>
@@ -23448,7 +24048,11 @@
           <t>81996-AA540</t>
         </is>
       </c>
-      <c r="J370" s="2" t="n"/>
+      <c r="J370" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K370" s="2" t="n"/>
       <c r="L370" s="2" t="inlineStr">
         <is>
@@ -23514,7 +24118,11 @@
           <t>81996-AA540</t>
         </is>
       </c>
-      <c r="J371" s="2" t="n"/>
+      <c r="J371" s="2" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K371" s="2" t="n"/>
       <c r="L371" s="2" t="inlineStr">
         <is>
@@ -29853,438 +30461,438 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr"/>
+      <c r="A2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>- 예전 현대 파일(컬럼 10개, 칩·세부ID·부품번호가 섞인 구조)을 버리고 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같은 컬럼으로 새로 작성했습니다. 칩코드 뒤에 '키종류'를 추가했습니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '현대 쏘나타', '제네시스 G80'처럼 브랜드와 모델명을 함께 검색 가능). 제네시스 브랜드 독립(2015.11) 이후 모델은 '제네시스', 그 이전 현대 제네시스(BH·DH)·제네시스 쿠페는 '현대'입니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다. 예전 파일에서 연식을 나누지 않고 한 줄로 적었던 모델(예: 2006-2010)은 조사 대상에서 뺐습니다(에쿠스·i20·갤로퍼·테라칸·트라제 XG·라비타·클릭·마이티 등).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>- 연식은 실제 국내 판매(출시일) 기준입니다. 풀체인지가 있는 해는 전·후 세대가 각각 한 행씩 있습니다. 후속 없이 단종된 모델의 마지막 연식은 '2019(단종)' 형식입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 카드키는 그랜저 HG·IG, 제네시스 DH의 카드형 스마트키입니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434/447MHz)만 적었습니다. 미국형 315MHz 키(예: 95440-3Q000·95440-3M220·95440-2M350·95440-2V100·95440-4Z200, FCC SY5HMFNA04)는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>- 스마트키에 딸린 비상키(블랭킹키)는 '키블레이드(부품번호)' 칸에 적었습니다. 키리모컨 일체형(81996-4H100 등)은 '폴딩키(부품번호)' 칸에 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템' 칸은 현대모비스 품번이 확인된 차종만 적었습니다(그랜드 스타렉스·포터2 이모빌라이저 모듈 95420-D4000·95420-4F500, 포터2 안테나 95440-4F100).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. hellowcar·partsro(현대모비스 공식 부품몰)는 적용 기간이 적힌 국내 순정 품번의 근거이고, 칩 종류는 대부분 해외 키 판매처(abkeys·mk3·remotesandkeys 등)의 같은 품번 설명을 근거로 했습니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr"/>
+      <c r="A14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값 — 실물 키·VIN으로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — 아반떼 J2(2000) 1행.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>- 주황색으로 남은 행(재조사 후 23행): 부분변경 신형 스마트키 칩 원문이 아직 없는 경우(아이오닉6 2025~, 일렉트리파이드 G80 2024~, 일렉트리파이드 GV70 2025~, GV60 2026, 포터2 LPG 스마트키, 포터2 일렉트릭 CN000), 스타렉스 2004-2005(순정 4D60 키 vs 해외 카탈로그 4C), 베르나 LC(이모빌라이저키 품번이 없어 미적용 추정).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>- 전환 연식은 칩코드 칸에 전·후를 함께 적었습니다(예: 쏘나타 DN8 2023 = ID47(NCF29A1X)[~2023.2], ID4A(NCF29A1M)[디 엣지, 2023.3~]).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>- 칩코드 추가 뜻: ID4C = Texas 4C(고정 코드, 스타렉스 2004-2006 해외 자료), 해당 없음 = 그 연식 국내형에 이모빌라이저가 없음.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr"/>
+      <c r="A21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>※ 예전 현대 파일에서 바로잡은 주요 오류</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>- 쏘나타 LF(2014-2019): ID47 → ID8A(DST-AES). 95440-C1001·C1500 모두 8A.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>- 쏘나타 DN8 2019-2022: ID4A → ID47(NCF29A1X). ID4A는 디 엣지(2023.3~)부터.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>- 아반떼 AD(2015-2020): ID47 → ID8A. 아반떼 CN7·아반떼 N·아이오닉6: ID4A → ID6A. 더 뉴 아반떼(95440-AA500)·아이오닉6(KL000)은 FCC NYOMBEC7FOB2208(MBEC 계열 = CN7 AA000·캐스퍼와 같은 6A 계열)이고 auto-keys·keyshop-online·abkeys가 6A로 일치. 일부 판매처(remotesandkeys)의 '4A' 표기는 같은 키를 4A·6A로 섞어 적어 따르지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>- 투싼 NX4 부분변경(더 뉴 투싼, 2023.11~): 스마트키가 95440-N95xx(ID4A)로 바뀜 — 처음 작성 때 ID47로 잘못 이어 적었던 것을 정정.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>- 그랜저 GN7: 스마트키 품번 95440-BY000 → 95440-N1xxx(N1000·N1050·N1110 등).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>- 제네시스 DH 2013-2014: 'BH 전자장비 유지, ID46(95440-3M220)' → DH는 출시(2013.11)부터 95440-B1200BLH ID47. 95440-3M220은 미국형 315MHz.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>- 제네시스 BH: 95440-3M220(미국형) → 국내 95440-3M010·3M020·3M030. 제네시스 쿠페: 95440-2M350·2M300·3V021(미국형) → 국내 95440-2M050·2M420.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>- 싼타페 DM 2016-2018·맥스크루즈 2016-2019: 'ID46 또는 ID47' → ID46(95440-2W500·B8100 모두 PCF7952A). 싼타페 DM 95440-4Z200은 미국형.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>- 싼타페 SM 2000-2002: 4D60 → 국내 이모빌라이저는 2005년형(2004.8.11)부터 적용, 그 이전은 해당 없음.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>- 투싼 TL: 'ID6E-MA 또는 ID47' → ID47(NCF2952X).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>- 스타리아: ID4A → ID47(NCF29A1X).</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>- 그랜드 스타렉스 2007-2011·포터2 2004-2015: '4D60 또는 미탑재' → 국내 이모빌라이저 사양 키는 ID46(그랜드 스타렉스 블랭킹키 81996-2H010 = 아반떼 HD 공용, 포터2 81996-4F020 = ID46 키블레이드).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>- 베라크루즈 2013-2015: '수출형 ix55 확인 불가' → 국내 판매가 2015년까지 이어짐(95440-3J560 ID46).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>- i40: 품번별로 칩이 다름 — 95440-3Z000(2011.12.15~2012.4.2)은 TMS37126(DST80, ID6E-MA), 3Z001·3Z002 이후는 DST-AES(8A).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>- 그랜저 TG 스마트키 95440-3L100은 TIRIS DST80(ID6E-MA), 이모빌라이저키 81996-3L010은 ID46.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>- 쏘나타 EF·그랜저 XG·싼타페 SM(2005년형~): 현대모비스 순정 이모빌라이저키 81996-38010(4D60). 베르나 MC: 81996-1E010(ID46, 트랜스폼 2009.6부터 이모빌라이저 삭제). 투싼 JM: 81996-2E010(ID46). 스타렉스: 81996-4A250(4D60).</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>- 포터2 스마트키는 2024 포터II LPG(2023.12~)부터(95440-4FGA0). 2020-2023 디젤에는 스마트키가 없어 예전 파일의 95440-4FGA0 기재는 오류.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>- 스타렉스 2004-2005: 'ID60, ID4C 자료 상충' → 2006년형(2005.7~, 11·12인승)부터 이모빌라이저 기본 적용(한국일보) — 2004년식은 해당 없음, 2005년식은 2005.6 이전·2005.7 이후 두 행. 4C는 해외 카탈로그 표기라 뺌(국내 순정 81996-4A250은 4D60).</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>- 제네시스 GV60 2026: 부분변경 스마트키 95440-CU260의 FCC TQ8-FOB-4F75M44는 G70·GV70·GV80 부분변경과 같은 키 모듈 — HITAG AES ID4A(NCF29A1M)(americankeysupply·keyinnovations) 확인.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>- 코나 N 95440-I3450(ID47), 일렉트리파이드 GV70 95440-DS000·DS010(ID47), GV80 쿠페 95440-T6AA0(ID4A) 품번을 새로 확인.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr"/>
+      <c r="A43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="14" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>- 연식별 검색 기록은 research/hyundai/yearly.md, 예전 파일 내용은 research/hyundai/old_rows.tsv에 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>- 아반떼 XD는 2005년형(2004.7.1)부터, 싼타페 SM은 2005년형(2004.8.11)부터, 스타렉스는 2006년형(2005.7 출시)부터 11·12인승에 이모빌라이저가 기본 적용됐습니다(한국일보 2005.7.3 '오토파일'). 베르나 트랜스폼(2009.6)은 원가절감으로 이모빌라이저가 빠졌습니다.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>- 아반떼 HD 리모컨은 2008년형까지 447MHz, 2009년형부터 433MHz입니다. 싼타페 CM 스마트키 95440-2B800과 베라크루즈 스마트키는 한국형 447MHz입니다.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>- 그랜드 스타렉스·포터2는 이모빌라이저 사양과 비사양이 공존합니다(키·폴딩키 품번이 따로 있음).</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>- 칩 세대 흐름: ID46(Hitag2, ~2015년경) → ID8A(DST-AES, LF·AD·i30 PD·i40 후기) / ID47(Hitag3, IG·TL·TM·코나·제네시스) → ID4A(Hitag AES, GN7·DN8 디 엣지·MX5·아이오닉5·제네시스 부분변경) / ID6A(아반떼 CN7·캐스퍼·포터2 일렉트릭).</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="n"/>
+      <c r="A50" s="10" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="14" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="14" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="14" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="14" t="n"/>
+      <c r="A58" s="10" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="14" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="14" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="14" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="14" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="14" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>

--- a/현대_트랜스폰더_칩코드_DB.xlsx
+++ b/현대_트랜스폰더_칩코드_DB.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -166,6 +166,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -27114,7 +27117,11 @@
       <c r="I418" s="2" t="n"/>
       <c r="J418" s="2" t="n"/>
       <c r="K418" s="2" t="n"/>
-      <c r="L418" s="2" t="n"/>
+      <c r="L418" s="2" t="inlineStr">
+        <is>
+          <t>95440-T1AA0[추정]</t>
+        </is>
+      </c>
       <c r="M418" s="2" t="n"/>
       <c r="N418" s="13" t="n"/>
       <c r="O418" s="2" t="inlineStr">
@@ -27172,7 +27179,11 @@
       <c r="I419" s="2" t="n"/>
       <c r="J419" s="2" t="n"/>
       <c r="K419" s="2" t="n"/>
-      <c r="L419" s="2" t="n"/>
+      <c r="L419" s="2" t="inlineStr">
+        <is>
+          <t>95440-T1AA0[추정]</t>
+        </is>
+      </c>
       <c r="M419" s="2" t="n"/>
       <c r="N419" s="13" t="n"/>
       <c r="O419" s="2" t="inlineStr">
@@ -27230,7 +27241,11 @@
       <c r="I420" s="2" t="n"/>
       <c r="J420" s="2" t="n"/>
       <c r="K420" s="2" t="n"/>
-      <c r="L420" s="2" t="n"/>
+      <c r="L420" s="2" t="inlineStr">
+        <is>
+          <t>95440-T1AA0[추정]</t>
+        </is>
+      </c>
       <c r="M420" s="2" t="n"/>
       <c r="N420" s="13" t="n"/>
       <c r="O420" s="2" t="inlineStr">
@@ -30454,445 +30469,445 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr"/>
+      <c r="A2" s="14" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>- 예전 현대 파일(컬럼 10개, 칩·세부ID·부품번호가 섞인 구조)을 버리고 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같은 컬럼으로 새로 작성했습니다. 칩코드 뒤에 '키종류'를 추가했습니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '현대 쏘나타', '제네시스 G80'처럼 브랜드와 모델명을 함께 검색 가능). 제네시스 브랜드 독립(2015.11) 이후 모델은 '제네시스', 그 이전 현대 제네시스(BH·DH)·제네시스 쿠페는 '현대'입니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다. 예전 파일에서 연식을 나누지 않고 한 줄로 적었던 모델(예: 2006-2010)은 조사 대상에서 뺐습니다(에쿠스·i20·갤로퍼·테라칸·트라제 XG·라비타·클릭·마이티 등).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>- 연식은 실제 국내 판매(출시일) 기준입니다. 풀체인지가 있는 해는 전·후 세대가 각각 한 행씩 있습니다. 후속 없이 단종된 모델의 마지막 연식은 '2019(단종)' 형식입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 카드키는 그랜저 HG·IG, 제네시스 DH의 카드형 스마트키입니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434/447MHz)만 적었습니다. 미국형 315MHz 키(예: 95440-3Q000·95440-3M220·95440-2M350·95440-2V100·95440-4Z200, FCC SY5HMFNA04)는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>- 스마트키에 딸린 비상키(블랭킹키)는 '키블레이드(부품번호)' 칸에 적었습니다. 키리모컨 일체형(81996-4H100 등)은 '폴딩키(부품번호)' 칸에 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템' 칸은 현대모비스 품번이 확인된 차종만 적었습니다(그랜드 스타렉스·포터2 이모빌라이저 모듈 95420-D4000·95420-4F500, 포터2 안테나 95440-4F100).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. hellowcar·partsro(현대모비스 공식 부품몰)는 적용 기간이 적힌 국내 순정 품번의 근거이고, 칩 종류는 대부분 해외 키 판매처(abkeys·mk3·remotesandkeys 등)의 같은 품번 설명을 근거로 했습니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr"/>
+      <c r="A14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값 — 실물 키·VIN으로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — 아반떼 J2(2000) 1행.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>- 주황색으로 남은 행(재조사 후 23행): 부분변경 신형 스마트키 칩 원문이 아직 없는 경우(아이오닉6 2025~, 일렉트리파이드 G80 2024~, 일렉트리파이드 GV70 2025~, GV60 2026, 포터2 LPG 스마트키, 포터2 일렉트릭 CN000), 스타렉스 2004-2005(순정 4D60 키 vs 해외 카탈로그 4C), 베르나 LC(이모빌라이저키 품번이 없어 미적용 추정).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>- 전환 연식은 칩코드 칸에 전·후를 함께 적었습니다(예: 쏘나타 DN8 2023 = ID47(NCF29A1X)[~2023.2], ID4A(NCF29A1M)[디 엣지, 2023.3~]).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>- 칩코드 추가 뜻: ID4C = Texas 4C(고정 코드, 스타렉스 2004-2006 해외 자료), 해당 없음 = 그 연식 국내형에 이모빌라이저가 없음.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr"/>
+      <c r="A21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>※ 예전 현대 파일에서 바로잡은 주요 오류</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>- 쏘나타 LF(2014-2019): ID47 → ID8A(DST-AES). 95440-C1001·C1500 모두 8A.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>- 쏘나타 DN8 2019-2022: ID4A → ID47(NCF29A1X). ID4A는 디 엣지(2023.3~)부터.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>- 아반떼 AD(2015-2020): ID47 → ID8A. 아반떼 CN7·아반떼 N·아이오닉6: ID4A → ID6A. 더 뉴 아반떼(95440-AA500)·아이오닉6(KL000)은 FCC NYOMBEC7FOB2208(MBEC 계열 = CN7 AA000·캐스퍼와 같은 6A 계열)이고 auto-keys·keyshop-online·abkeys가 6A로 일치. 일부 판매처(remotesandkeys)의 '4A' 표기는 같은 키를 4A·6A로 섞어 적어 따르지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>- 투싼 NX4 부분변경(더 뉴 투싼, 2023.11~): 스마트키가 95440-N95xx(ID4A)로 바뀜 — 처음 작성 때 ID47로 잘못 이어 적었던 것을 정정.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>- 그랜저 GN7: 스마트키 품번 95440-BY000 → 95440-N1xxx(N1000·N1050·N1110 등).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>- 제네시스 DH 2013-2014: 'BH 전자장비 유지, ID46(95440-3M220)' → DH는 출시(2013.11)부터 95440-B1200BLH ID47. 95440-3M220은 미국형 315MHz.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>- 제네시스 BH: 95440-3M220(미국형) → 국내 95440-3M010·3M020·3M030. 제네시스 쿠페: 95440-2M350·2M300·3V021(미국형) → 국내 95440-2M050·2M420.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>- 싼타페 DM 2016-2018·맥스크루즈 2016-2019: 'ID46 또는 ID47' → ID46(95440-2W500·B8100 모두 PCF7952A). 싼타페 DM 95440-4Z200은 미국형.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>- 싼타페 SM 2000-2002: 4D60 → 국내 이모빌라이저는 2005년형(2004.8.11)부터 적용, 그 이전은 해당 없음.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>- 투싼 TL: 'ID6E-MA 또는 ID47' → ID47(NCF2952X).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>- 스타리아: ID4A → ID47(NCF29A1X).</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>- 그랜드 스타렉스 2007-2011·포터2 2004-2015: '4D60 또는 미탑재' → 국내 이모빌라이저 사양 키는 ID46(그랜드 스타렉스 블랭킹키 81996-2H010 = 아반떼 HD 공용, 포터2 81996-4F020 = ID46 키블레이드).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>- 베라크루즈 2013-2015: '수출형 ix55 확인 불가' → 국내 판매가 2015년까지 이어짐(95440-3J560 ID46).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>- i40: 품번별로 칩이 다름 — 95440-3Z000(2011.12.15~2012.4.2)은 TMS37126(DST80, ID6E-MA), 3Z001·3Z002 이후는 DST-AES(8A).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>- 그랜저 TG 스마트키 95440-3L100은 TIRIS DST80(ID6E-MA), 이모빌라이저키 81996-3L010은 ID46.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>- 쏘나타 EF·그랜저 XG·싼타페 SM(2005년형~): 현대모비스 순정 이모빌라이저키 81996-38010(4D60). 베르나 MC: 81996-1E010(ID46, 트랜스폼 2009.6부터 이모빌라이저 삭제). 투싼 JM: 81996-2E010(ID46). 스타렉스: 81996-4A250(4D60).</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>- 포터2 스마트키는 2024 포터II LPG(2023.12~)부터(95440-4FGA0). 2020-2023 디젤에는 스마트키가 없어 예전 파일의 95440-4FGA0 기재는 오류.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>- 스타렉스 2004-2005: 'ID60, ID4C 자료 상충' → 2006년형(2005.7~, 11·12인승)부터 이모빌라이저 기본 적용(한국일보) — 2004년식은 해당 없음, 2005년식은 2005.6 이전·2005.7 이후 두 행. 4C는 해외 카탈로그 표기라 뺌(국내 순정 81996-4A250은 4D60).</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>- 제네시스 GV60 2026: 부분변경 스마트키 95440-CU260의 FCC TQ8-FOB-4F75M44는 G70·GV70·GV80 부분변경과 같은 키 모듈 — HITAG AES ID4A(NCF29A1M)(americankeysupply·keyinnovations) 확인.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>- 코나 N 95440-I3450(ID47), 일렉트리파이드 GV70 95440-DS000·DS010(ID47), GV80 쿠페 95440-T6AA0(ID4A) 품번을 새로 확인.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr"/>
+      <c r="A43" s="14" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>- 연식별 검색 기록은 research/hyundai/yearly.md, 예전 파일 내용은 research/hyundai/old_rows.tsv에 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>- 아반떼 XD는 2005년형(2004.7.1)부터, 싼타페 SM은 2005년형(2004.8.11)부터, 스타렉스는 2006년형(2005.7 출시)부터 11·12인승에 이모빌라이저가 기본 적용됐습니다(한국일보 2005.7.3 '오토파일'). 베르나 트랜스폼(2009.6)은 원가절감으로 이모빌라이저가 빠졌습니다.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>- 아반떼 HD 리모컨은 2008년형까지 447MHz, 2009년형부터 433MHz입니다. 싼타페 CM 스마트키 95440-2B800과 베라크루즈 스마트키는 한국형 447MHz입니다.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>- 그랜드 스타렉스·포터2는 이모빌라이저 사양과 비사양이 공존합니다(키·폴딩키 품번이 따로 있음).</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>- 칩 세대 흐름: ID46(Hitag2, ~2015년경) → ID8A(DST-AES, LF·AD·i30 PD·i40 후기) / ID47(Hitag3, IG·TL·TM·코나·제네시스) → ID4A(Hitag AES, GN7·DN8 디 엣지·MX5·아이오닉5·제네시스 부분변경) / ID6A(아반떼 CN7·캐스퍼·포터2 일렉트릭).</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="n"/>
+      <c r="A50" s="14" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="14" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n"/>
+      <c r="A58" s="14" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="14" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="14" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="14" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="A64" s="14" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="14" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
@@ -30919,6 +30934,23 @@
       <c r="A70" s="14" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>- 제네시스 G80 부분변경(24MY) FOB 스마트키 95440-T1AA0(제네시스 부티크) — 일렉트리파이드 G80 부분변경 적용은 미확인이라 [추정]</t>
         </is>
       </c>
     </row>

--- a/현대_트랜스폰더_칩코드_DB.xlsx
+++ b/현대_트랜스폰더_칩코드_DB.xlsx
@@ -4936,7 +4936,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>81996-29000[칩 없음, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J65" s="2" t="n"/>
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="n"/>
@@ -4982,7 +4986,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>81996-29000[칩 없음, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="n"/>
       <c r="K66" s="2" t="n"/>
       <c r="L66" s="2" t="n"/>
@@ -5024,7 +5032,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>81996-29000[칩 없음, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="n"/>
       <c r="K67" s="2" t="n"/>
       <c r="L67" s="2" t="n"/>
@@ -5066,7 +5078,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>81996-29000[칩 없음, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="n"/>
       <c r="K68" s="2" t="n"/>
       <c r="L68" s="2" t="n"/>
@@ -5108,7 +5124,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>81996-29000[칩 없음, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="n"/>
       <c r="K69" s="2" t="n"/>
       <c r="L69" s="2" t="n"/>
@@ -5150,7 +5170,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>81996-29000[칩 없음, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
           <t>HYN6</t>
@@ -5210,7 +5234,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>81996-25010[해외 공용 품번]</t>
+          <t>81996-25010[해외 공용 품번], 81996-29000[칩 없음, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -14114,7 +14138,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I212" s="2" t="n"/>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>81996-38000[칩 없음, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J212" s="2" t="n"/>
       <c r="K212" s="2" t="n"/>
       <c r="L212" s="2" t="n"/>
@@ -14156,7 +14184,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I213" s="2" t="n"/>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>81996-38000[칩 없음, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J213" s="2" t="n"/>
       <c r="K213" s="2" t="n"/>
       <c r="L213" s="2" t="n"/>
@@ -14198,7 +14230,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I214" s="2" t="n"/>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>81996-38000[칩 없음, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J214" s="2" t="n"/>
       <c r="K214" s="2" t="n"/>
       <c r="L214" s="2" t="n"/>
@@ -14240,7 +14276,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I215" s="2" t="n"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>81996-38000[칩 없음, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J215" s="2" t="n"/>
       <c r="K215" s="2" t="n"/>
       <c r="L215" s="2" t="n"/>
@@ -14282,7 +14322,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I216" s="2" t="n"/>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>81996-38000[칩 없음, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
           <t>HYN7, HYN7R[Silca], HY-6D.P1[JMA], HY12[ILCO]</t>
@@ -14342,7 +14386,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>81996-38010[2005년형~]</t>
+          <t>81996-38010[2005년형~], 81996-38000[칩 없음, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -30476,462 +30520,462 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr"/>
+      <c r="A2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>- 예전 현대 파일(컬럼 10개, 칩·세부ID·부품번호가 섞인 구조)을 버리고 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같은 컬럼으로 새로 작성했습니다. 칩코드 뒤에 '키종류'를 추가했습니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '현대 쏘나타', '제네시스 G80'처럼 브랜드와 모델명을 함께 검색 가능). 제네시스 브랜드 독립(2015.11) 이후 모델은 '제네시스', 그 이전 현대 제네시스(BH·DH)·제네시스 쿠페는 '현대'입니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다. 예전 파일에서 연식을 나누지 않고 한 줄로 적었던 모델(예: 2006-2010)은 조사 대상에서 뺐습니다(에쿠스·i20·갤로퍼·테라칸·트라제 XG·라비타·클릭·마이티 등).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>- 연식은 실제 국내 판매(출시일) 기준입니다. 풀체인지가 있는 해는 전·후 세대가 각각 한 행씩 있습니다. 후속 없이 단종된 모델의 마지막 연식은 '2019(단종)' 형식입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 카드키는 그랜저 HG·IG, 제네시스 DH의 카드형 스마트키입니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434/447MHz)만 적었습니다. 미국형 315MHz 키(예: 95440-3Q000·95440-3M220·95440-2M350·95440-2V100·95440-4Z200, FCC SY5HMFNA04)는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>- 스마트키에 딸린 비상키(블랭킹키)는 '키블레이드(부품번호)' 칸에 적었습니다. 키리모컨 일체형(81996-4H100 등)은 '폴딩키(부품번호)' 칸에 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템' 칸은 현대모비스 품번이 확인된 차종만 적었습니다(그랜드 스타렉스·포터2 이모빌라이저 모듈 95420-D4000·95420-4F500, 포터2 안테나 95440-4F100).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. hellowcar·partsro(현대모비스 공식 부품몰)는 적용 기간이 적힌 국내 순정 품번의 근거이고, 칩 종류는 대부분 해외 키 판매처(abkeys·mk3·remotesandkeys 등)의 같은 품번 설명을 근거로 했습니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr"/>
+      <c r="A14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값 — 실물 키·VIN으로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 — 아반떼 J2(2000) 1행.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>- 주황색으로 남은 행(재조사 후 23행): 부분변경 신형 스마트키 칩 원문이 아직 없는 경우(아이오닉6 2025~, 일렉트리파이드 G80 2024~, 일렉트리파이드 GV70 2025~, GV60 2026, 포터2 LPG 스마트키, 포터2 일렉트릭 CN000), 스타렉스 2004-2005(순정 4D60 키 vs 해외 카탈로그 4C), 베르나 LC(이모빌라이저키 품번이 없어 미적용 추정).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>- 전환 연식은 칩코드 칸에 전·후를 함께 적었습니다(예: 쏘나타 DN8 2023 = ID47(NCF29A1X)[~2023.2], ID4A(NCF29A1M)[디 엣지, 2023.3~]).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>- 칩코드 추가 뜻: ID4C = Texas 4C(고정 코드, 스타렉스 2004-2006 해외 자료), 해당 없음 = 그 연식 국내형에 이모빌라이저가 없음.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr"/>
+      <c r="A21" s="15" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>※ 예전 현대 파일에서 바로잡은 주요 오류</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>- 쏘나타 LF(2014-2019): ID47 → ID8A(DST-AES). 95440-C1001·C1500 모두 8A.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>- 쏘나타 DN8 2019-2022: ID4A → ID47(NCF29A1X). ID4A는 디 엣지(2023.3~)부터.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>- 아반떼 AD(2015-2020): ID47 → ID8A. 아반떼 CN7·아반떼 N·아이오닉6: ID4A → ID6A. 더 뉴 아반떼(95440-AA500)·아이오닉6(KL000)은 FCC NYOMBEC7FOB2208(MBEC 계열 = CN7 AA000·캐스퍼와 같은 6A 계열)이고 auto-keys·keyshop-online·abkeys가 6A로 일치. 일부 판매처(remotesandkeys)의 '4A' 표기는 같은 키를 4A·6A로 섞어 적어 따르지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>- 투싼 NX4 부분변경(더 뉴 투싼, 2023.11~): 스마트키가 95440-N95xx(ID4A)로 바뀜 — 처음 작성 때 ID47로 잘못 이어 적었던 것을 정정.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>- 그랜저 GN7: 스마트키 품번 95440-BY000 → 95440-N1xxx(N1000·N1050·N1110 등).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>- 제네시스 DH 2013-2014: 'BH 전자장비 유지, ID46(95440-3M220)' → DH는 출시(2013.11)부터 95440-B1200BLH ID47. 95440-3M220은 미국형 315MHz.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>- 제네시스 BH: 95440-3M220(미국형) → 국내 95440-3M010·3M020·3M030. 제네시스 쿠페: 95440-2M350·2M300·3V021(미국형) → 국내 95440-2M050·2M420.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>- 싼타페 DM 2016-2018·맥스크루즈 2016-2019: 'ID46 또는 ID47' → ID46(95440-2W500·B8100 모두 PCF7952A). 싼타페 DM 95440-4Z200은 미국형.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>- 싼타페 SM 2000-2002: 4D60 → 국내 이모빌라이저는 2005년형(2004.8.11)부터 적용, 그 이전은 해당 없음.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>- 투싼 TL: 'ID6E-MA 또는 ID47' → ID47(NCF2952X).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>- 스타리아: ID4A → ID47(NCF29A1X).</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>- 그랜드 스타렉스 2007-2011·포터2 2004-2015: '4D60 또는 미탑재' → 국내 이모빌라이저 사양 키는 ID46(그랜드 스타렉스 블랭킹키 81996-2H010 = 아반떼 HD 공용, 포터2 81996-4F020 = ID46 키블레이드).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>- 베라크루즈 2013-2015: '수출형 ix55 확인 불가' → 국내 판매가 2015년까지 이어짐(95440-3J560 ID46).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>- i40: 품번별로 칩이 다름 — 95440-3Z000(2011.12.15~2012.4.2)은 TMS37126(DST80, ID6E-MA), 3Z001·3Z002 이후는 DST-AES(8A).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>- 그랜저 TG 스마트키 95440-3L100은 TIRIS DST80(ID6E-MA), 이모빌라이저키 81996-3L010은 ID46.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>- 쏘나타 EF·그랜저 XG·싼타페 SM(2005년형~): 현대모비스 순정 이모빌라이저키 81996-38010(4D60). 베르나 MC: 81996-1E010(ID46, 트랜스폼 2009.6부터 이모빌라이저 삭제). 투싼 JM: 81996-2E010(ID46). 스타렉스: 81996-4A250(4D60).</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>- 포터2 스마트키는 2024 포터II LPG(2023.12~)부터(95440-4FGA0). 2020-2023 디젤에는 스마트키가 없어 예전 파일의 95440-4FGA0 기재는 오류.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>- 스타렉스 2004-2005: 'ID60, ID4C 자료 상충' → 2006년형(2005.7~, 11·12인승)부터 이모빌라이저 기본 적용(한국일보) — 2004년식은 해당 없음, 2005년식은 2005.6 이전·2005.7 이후 두 행. 4C는 해외 카탈로그 표기라 뺌(국내 순정 81996-4A250은 4D60).</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>- 제네시스 GV60 2026: 부분변경 스마트키 95440-CU260의 FCC TQ8-FOB-4F75M44는 G70·GV70·GV80 부분변경과 같은 키 모듈 — HITAG AES ID4A(NCF29A1M)(americankeysupply·keyinnovations) 확인.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>- 코나 N 95440-I3450(ID47), 일렉트리파이드 GV70 95440-DS000·DS010(ID47), GV80 쿠페 95440-T6AA0(ID4A) 품번을 새로 확인.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr"/>
+      <c r="A43" s="15" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="14" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>- 연식별 검색 기록은 research/hyundai/yearly.md, 예전 파일 내용은 research/hyundai/old_rows.tsv에 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>- 아반떼 XD는 2005년형(2004.7.1)부터, 싼타페 SM은 2005년형(2004.8.11)부터, 스타렉스는 2006년형(2005.7 출시)부터 11·12인승에 이모빌라이저가 기본 적용됐습니다(한국일보 2005.7.3 '오토파일'). 베르나 트랜스폼(2009.6)은 원가절감으로 이모빌라이저가 빠졌습니다.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>- 아반떼 HD 리모컨은 2008년형까지 447MHz, 2009년형부터 433MHz입니다. 싼타페 CM 스마트키 95440-2B800과 베라크루즈 스마트키는 한국형 447MHz입니다.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>- 그랜드 스타렉스·포터2는 이모빌라이저 사양과 비사양이 공존합니다(키·폴딩키 품번이 따로 있음).</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>- 칩 세대 흐름: ID46(Hitag2, ~2015년경) → ID8A(DST-AES, LF·AD·i30 PD·i40 후기) / ID47(Hitag3, IG·TL·TM·코나·제네시스) → ID4A(Hitag AES, GN7·DN8 디 엣지·MX5·아이오닉5·제네시스 부분변경) / ID6A(아반떼 CN7·캐스퍼·포터2 일렉트릭).</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="n"/>
+      <c r="A50" s="15" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="14" t="inlineStr">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="14" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="inlineStr">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="14" t="inlineStr">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="14" t="inlineStr">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="14" t="n"/>
+      <c r="A58" s="15" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="inlineStr">
+      <c r="A60" s="15" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="14" t="inlineStr">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="14" t="inlineStr">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="14" t="inlineStr">
+      <c r="A63" s="15" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="14" t="inlineStr">
+      <c r="A64" s="15" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="A65" s="15" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="14" t="inlineStr">
+      <c r="A66" s="15" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="n"/>
+      <c r="A67" s="15" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="14" t="inlineStr">
+      <c r="A68" s="15" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="14" t="inlineStr">
+      <c r="A69" s="15" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="14" t="inlineStr">
+      <c r="A70" s="15" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
